--- a/Watchlist .xlsx
+++ b/Watchlist .xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5608DF72-EAC3-46F3-A60F-6A65A9787D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA878411-5F4C-4766-80D7-1147D5B0ADD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="1950" windowWidth="38175" windowHeight="15240" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
+    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>

--- a/Watchlist .xlsx
+++ b/Watchlist .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA878411-5F4C-4766-80D7-1147D5B0ADD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B95330-4970-45AF-BD1E-E0049152BA67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
   </bookViews>
@@ -275,7 +275,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -313,6 +313,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -347,12 +348,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>99.2</v>
+            <v>78.3</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>1995.0458208000002</v>
+            <v>1574.7186267</v>
           </cell>
         </row>
         <row r="5">
@@ -387,12 +388,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>7.44</v>
+            <v>8.16</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>12572.354291040001</v>
+            <v>13789.033738560001</v>
           </cell>
         </row>
         <row r="5">
@@ -428,12 +429,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>167.35</v>
+            <v>177.4</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>18988.883522699998</v>
+            <v>20129.237746800001</v>
           </cell>
         </row>
         <row r="5">
@@ -464,17 +465,20 @@
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="CoC"/>
+      <sheetName val="DCF"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>41.35</v>
+            <v>35.450000000000003</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>6320.9364066999997</v>
+            <v>5419.0373789000005</v>
           </cell>
         </row>
         <row r="5">
@@ -489,6 +493,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -508,12 +515,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>134.1</v>
+            <v>172</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>2340822.7799999998</v>
+            <v>3002397.5999999996</v>
           </cell>
         </row>
         <row r="6">
@@ -869,6 +876,10 @@
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
+      <c r="M2" s="19">
+        <f>+SUM(M5:M9)</f>
+        <v>-7.864442176608788E-2</v>
+      </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
@@ -938,11 +949,11 @@
       </c>
       <c r="E5" s="9">
         <f>+[1]Main!$J$2</f>
-        <v>99.2</v>
+        <v>78.3</v>
       </c>
       <c r="F5" s="12">
         <f>+[1]Main!$J$4*FX!C2</f>
-        <v>2334.2036103360001</v>
+        <v>1842.4207932389997</v>
       </c>
       <c r="G5" s="12">
         <f>(+[1]Main!$J$6-[1]Main!$J$5)*FX!C2</f>
@@ -950,7 +961,7 @@
       </c>
       <c r="H5" s="12">
         <f>+F5+G5</f>
-        <v>2491.0210503360004</v>
+        <v>1999.2382332389998</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>18</v>
@@ -966,7 +977,7 @@
       </c>
       <c r="M5" s="18">
         <f>+E5/L5-1</f>
-        <v>0</v>
+        <v>-0.21068548387096775</v>
       </c>
       <c r="O5" s="10" t="s">
         <v>33</v>
@@ -991,11 +1002,11 @@
       </c>
       <c r="E6" s="9">
         <f>+[2]Main!$I$2</f>
-        <v>7.44</v>
+        <v>8.16</v>
       </c>
       <c r="F6" s="12">
         <f>+[2]Main!$I$4</f>
-        <v>12572.354291040001</v>
+        <v>13789.033738560001</v>
       </c>
       <c r="G6" s="12">
         <f>+[2]Main!$I$6-[2]Main!$I$5</f>
@@ -1003,7 +1014,7 @@
       </c>
       <c r="H6" s="12">
         <f>+F6+G6</f>
-        <v>13255.281291040001</v>
+        <v>14471.960738560001</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>18</v>
@@ -1019,7 +1030,7 @@
       </c>
       <c r="M6" s="18">
         <f t="shared" ref="M6:M9" si="0">+E6/L6-1</f>
-        <v>0</v>
+        <v>9.6774193548387011E-2</v>
       </c>
       <c r="O6" s="10" t="s">
         <v>36</v>
@@ -1047,11 +1058,11 @@
       </c>
       <c r="E7" s="9">
         <f>+[3]Main!$I$2</f>
-        <v>167.35</v>
+        <v>177.4</v>
       </c>
       <c r="F7" s="12">
         <f>+[3]Main!$I$4</f>
-        <v>18988.883522699998</v>
+        <v>20129.237746800001</v>
       </c>
       <c r="G7" s="12">
         <f>+[3]Main!$I$6-[3]Main!$I$5</f>
@@ -1059,7 +1070,7 @@
       </c>
       <c r="H7" s="12">
         <f>+F7+G7</f>
-        <v>17833.089522699996</v>
+        <v>18973.4437468</v>
       </c>
       <c r="I7" s="17" t="s">
         <v>18</v>
@@ -1075,7 +1086,7 @@
       </c>
       <c r="M7" s="18">
         <f t="shared" si="0"/>
-        <v>-0.15637445178202358</v>
+        <v>-0.10571154912537173</v>
       </c>
       <c r="O7" s="10" t="s">
         <v>35</v>
@@ -1100,11 +1111,11 @@
       </c>
       <c r="E8" s="9">
         <f>+[4]Main!$H$2</f>
-        <v>41.35</v>
+        <v>35.450000000000003</v>
       </c>
       <c r="F8" s="12">
         <f>+[4]Main!$H$4</f>
-        <v>6320.9364066999997</v>
+        <v>5419.0373789000005</v>
       </c>
       <c r="G8" s="12">
         <f>+[4]Main!$H$6-[4]Main!$H$5</f>
@@ -1112,7 +1123,7 @@
       </c>
       <c r="H8" s="12">
         <f>+F8+G8</f>
-        <v>7563.7604066999993</v>
+        <v>6661.861378900001</v>
       </c>
       <c r="I8" s="8" t="s">
         <v>18</v>
@@ -1128,7 +1139,7 @@
       </c>
       <c r="M8" s="18">
         <f t="shared" si="0"/>
-        <v>1.210653753026758E-3</v>
+        <v>-0.14164648910411615</v>
       </c>
       <c r="O8" s="10" t="s">
         <v>34</v>
@@ -1153,11 +1164,11 @@
       </c>
       <c r="E9" s="9">
         <f>+[5]Main!$J$2</f>
-        <v>134.1</v>
+        <v>172</v>
       </c>
       <c r="F9" s="12">
         <f>+[5]Main!$J$5*FX!C3</f>
-        <v>327715.18920000002</v>
+        <v>420335.66399999999</v>
       </c>
       <c r="G9" s="12">
         <f>+([5]Main!$J$7-[5]Main!$J$6)*FX!C3</f>
@@ -1165,7 +1176,7 @@
       </c>
       <c r="H9" s="12">
         <f>+F9+G9</f>
-        <v>285805.62920000002</v>
+        <v>378426.10399999999</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>40</v>
@@ -1181,7 +1192,7 @@
       </c>
       <c r="M9" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.28262490678598073</v>
       </c>
       <c r="O9" s="16" t="s">
         <v>41</v>

--- a/Watchlist .xlsx
+++ b/Watchlist .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B95330-4970-45AF-BD1E-E0049152BA67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{416AC2A1-9AC9-483F-A40E-9796607EDA0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,8 @@
     <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="55">
   <si>
     <t>Watchlist</t>
   </si>
@@ -176,6 +178,39 @@
   </si>
   <si>
     <t>Change</t>
+  </si>
+  <si>
+    <t>Brunello Cuchinelli</t>
+  </si>
+  <si>
+    <t>ITA</t>
+  </si>
+  <si>
+    <t>BC.MI</t>
+  </si>
+  <si>
+    <t>Luxury Apperal</t>
+  </si>
+  <si>
+    <t>20% drop after Short Report</t>
+  </si>
+  <si>
+    <t>Pop Mart</t>
+  </si>
+  <si>
+    <t>9992.HK</t>
+  </si>
+  <si>
+    <t>CHI</t>
+  </si>
+  <si>
+    <t>Toys</t>
+  </si>
+  <si>
+    <t>longs</t>
+  </si>
+  <si>
+    <t>Labubu Hype</t>
   </si>
 </sst>
 </file>
@@ -218,12 +253,10 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -272,14 +305,14 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -290,33 +323,41 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Per cent" xfId="2" builtinId="5"/>
   </cellStyles>
@@ -531,6 +572,84 @@
         <row r="7">
           <cell r="J7">
             <v>75503</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>85.3</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>5799.8605627999996</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>243.84100000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>7.04</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>256.39999999999998</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>340780.2144</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>13765.710999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -1029,7 +1148,7 @@
         <v>7.44</v>
       </c>
       <c r="M6" s="18">
-        <f t="shared" ref="M6:M9" si="0">+E6/L6-1</f>
+        <f t="shared" ref="M6:M11" si="0">+E6/L6-1</f>
         <v>9.6774193548387011E-2</v>
       </c>
       <c r="O6" s="10" t="s">
@@ -1206,22 +1325,109 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="8"/>
+      <c r="B10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="9">
+        <f>+[6]Main!$J$2</f>
+        <v>85.3</v>
+      </c>
+      <c r="F10" s="12">
+        <f>+([6]Main!$J$4)*FX!C2</f>
+        <v>6785.8368584759992</v>
+      </c>
+      <c r="G10" s="12">
+        <f>+([6]Main!$J$6-[6]Main!$J$5)*FX!C2</f>
+        <v>-277.05716999999999</v>
+      </c>
+      <c r="H10" s="12">
+        <f>+F10+G10</f>
+        <v>6508.7796884759991</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="13">
+        <v>45946</v>
+      </c>
+      <c r="K10" s="13">
+        <v>45926</v>
+      </c>
+      <c r="L10" s="9">
+        <v>85.3</v>
+      </c>
+      <c r="M10" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O10" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="P10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q10" s="20" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="11">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="8"/>
+      <c r="B11" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="9">
+        <f>+[7]Main!$I$2</f>
+        <v>256.39999999999998</v>
+      </c>
+      <c r="F11" s="12">
+        <f>+[7]Main!$I$4*FX!C3</f>
+        <v>47709.230016000001</v>
+      </c>
+      <c r="G11" s="12">
+        <f>+([7]Main!$I$6-[7]Main!$I$5)*FX!C3</f>
+        <v>-1927.1995400000001</v>
+      </c>
+      <c r="H11" s="12">
+        <f>+F11+G11</f>
+        <v>45782.030476</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="K11" s="13">
+        <v>45926</v>
+      </c>
+      <c r="L11" s="9">
+        <v>256.39999999999998</v>
+      </c>
+      <c r="M11" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O11" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="P11" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q11" s="20" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="11">
@@ -1861,6 +2067,8 @@
     <hyperlink ref="B7" r:id="rId3" xr:uid="{6A12FCF3-584D-4323-A41F-B970C6FF1200}"/>
     <hyperlink ref="B8" r:id="rId4" display="Virt" xr:uid="{40A4329D-348A-4629-AAFA-B94628070672}"/>
     <hyperlink ref="B9" r:id="rId5" xr:uid="{008C64C3-FE55-425E-8F91-6D7191763AE3}"/>
+    <hyperlink ref="B10" r:id="rId6" xr:uid="{2F35C231-9D4B-4712-94E5-6754F841B088}"/>
+    <hyperlink ref="B11" r:id="rId7" xr:uid="{AED81220-75B7-4217-BDBB-E6654FE09225}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Watchlist .xlsx
+++ b/Watchlist .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{416AC2A1-9AC9-483F-A40E-9796607EDA0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6797E5F0-C20A-4522-9636-9EAC2A04473F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
+    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -308,7 +308,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -322,7 +322,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -348,7 +348,6 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -533,10 +532,10 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1079,7 +1078,7 @@
         <v>156.81744000000003</v>
       </c>
       <c r="H5" s="12">
-        <f>+F5+G5</f>
+        <f t="shared" ref="H5:H11" si="0">+F5+G5</f>
         <v>1999.2382332389998</v>
       </c>
       <c r="I5" s="8" t="s">
@@ -1132,7 +1131,7 @@
         <v>682.92700000000013</v>
       </c>
       <c r="H6" s="12">
-        <f>+F6+G6</f>
+        <f t="shared" si="0"/>
         <v>14471.960738560001</v>
       </c>
       <c r="I6" s="8" t="s">
@@ -1148,7 +1147,7 @@
         <v>7.44</v>
       </c>
       <c r="M6" s="18">
-        <f t="shared" ref="M6:M11" si="0">+E6/L6-1</f>
+        <f t="shared" ref="M6:M11" si="1">+E6/L6-1</f>
         <v>9.6774193548387011E-2</v>
       </c>
       <c r="O6" s="10" t="s">
@@ -1163,7 +1162,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
-        <f t="shared" ref="A7:A47" si="1">+A6+1</f>
+        <f t="shared" ref="A7:A47" si="2">+A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -1188,7 +1187,7 @@
         <v>-1155.7940000000001</v>
       </c>
       <c r="H7" s="12">
-        <f>+F7+G7</f>
+        <f t="shared" si="0"/>
         <v>18973.4437468</v>
       </c>
       <c r="I7" s="17" t="s">
@@ -1204,7 +1203,7 @@
         <v>198.37</v>
       </c>
       <c r="M7" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-0.10571154912537173</v>
       </c>
       <c r="O7" s="10" t="s">
@@ -1216,7 +1215,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -1241,7 +1240,7 @@
         <v>1242.8240000000001</v>
       </c>
       <c r="H8" s="12">
-        <f>+F8+G8</f>
+        <f t="shared" si="0"/>
         <v>6661.861378900001</v>
       </c>
       <c r="I8" s="8" t="s">
@@ -1257,7 +1256,7 @@
         <v>41.3</v>
       </c>
       <c r="M8" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-0.14164648910411615</v>
       </c>
       <c r="O8" s="10" t="s">
@@ -1269,7 +1268,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="B9" s="7" t="s">
@@ -1294,7 +1293,7 @@
         <v>-41909.560000000005</v>
       </c>
       <c r="H9" s="12">
-        <f>+F9+G9</f>
+        <f t="shared" si="0"/>
         <v>378426.10399999999</v>
       </c>
       <c r="I9" s="15" t="s">
@@ -1310,7 +1309,7 @@
         <v>134.1</v>
       </c>
       <c r="M9" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.28262490678598073</v>
       </c>
       <c r="O9" s="16" t="s">
@@ -1322,7 +1321,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
@@ -1347,10 +1346,10 @@
         <v>-277.05716999999999</v>
       </c>
       <c r="H10" s="12">
-        <f>+F10+G10</f>
+        <f t="shared" si="0"/>
         <v>6508.7796884759991</v>
       </c>
-      <c r="I10" s="23" t="s">
+      <c r="I10" s="22" t="s">
         <v>18</v>
       </c>
       <c r="J10" s="13">
@@ -1363,10 +1362,10 @@
         <v>85.3</v>
       </c>
       <c r="M10" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O10" s="22" t="s">
+      <c r="O10" s="21" t="s">
         <v>47</v>
       </c>
       <c r="P10" s="14" t="s">
@@ -1378,10 +1377,10 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="7" t="s">
         <v>49</v>
       </c>
       <c r="C11" s="20" t="s">
@@ -1403,10 +1402,10 @@
         <v>-1927.1995400000001</v>
       </c>
       <c r="H11" s="12">
-        <f>+F11+G11</f>
+        <f t="shared" si="0"/>
         <v>45782.030476</v>
       </c>
-      <c r="I11" s="23" t="s">
+      <c r="I11" s="22" t="s">
         <v>18</v>
       </c>
       <c r="K11" s="13">
@@ -1416,10 +1415,10 @@
         <v>256.39999999999998</v>
       </c>
       <c r="M11" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O11" s="22" t="s">
+      <c r="O11" s="21" t="s">
         <v>52</v>
       </c>
       <c r="P11" s="20" t="s">
@@ -1431,7 +1430,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="B12" s="7"/>
@@ -1442,7 +1441,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
@@ -1453,7 +1452,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="B14" s="7"/>
@@ -1464,7 +1463,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="B15" s="7"/>
@@ -1475,7 +1474,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="F16" s="12"/>
@@ -1485,7 +1484,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="F17" s="12"/>
@@ -1495,7 +1494,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="F18" s="12"/>
@@ -1505,7 +1504,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="F19" s="12"/>
@@ -1515,7 +1514,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="F20" s="12"/>
@@ -1525,7 +1524,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="F21" s="12"/>
@@ -1535,7 +1534,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="F22" s="12"/>
@@ -1545,7 +1544,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="F23" s="12"/>
@@ -1555,7 +1554,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="F24" s="12"/>
@@ -1565,7 +1564,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="F25" s="12"/>
@@ -1575,7 +1574,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="F26" s="12"/>
@@ -1585,7 +1584,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
       <c r="F27" s="12"/>
@@ -1595,7 +1594,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="F28" s="12"/>
@@ -1605,7 +1604,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="F29" s="12"/>
@@ -1615,7 +1614,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
       <c r="F30" s="12"/>
@@ -1625,7 +1624,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="F31" s="12"/>
@@ -1635,7 +1634,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
       <c r="F32" s="12"/>
@@ -1645,7 +1644,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="F33" s="12"/>
@@ -1655,7 +1654,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
       <c r="F34" s="12"/>
@@ -1665,7 +1664,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="F35" s="12"/>
@@ -1675,7 +1674,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>32</v>
       </c>
       <c r="F36" s="12"/>
@@ -1685,7 +1684,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>33</v>
       </c>
       <c r="F37" s="12"/>
@@ -1695,7 +1694,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>34</v>
       </c>
       <c r="F38" s="12"/>
@@ -1705,7 +1704,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>35</v>
       </c>
       <c r="F39" s="12"/>
@@ -1715,7 +1714,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>36</v>
       </c>
       <c r="F40" s="12"/>
@@ -1725,7 +1724,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>37</v>
       </c>
       <c r="F41" s="12"/>
@@ -1735,7 +1734,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>38</v>
       </c>
       <c r="F42" s="12"/>
@@ -1745,7 +1744,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>39</v>
       </c>
       <c r="F43" s="12"/>
@@ -1755,7 +1754,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="F44" s="12"/>
@@ -1765,7 +1764,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>41</v>
       </c>
       <c r="F45" s="12"/>
@@ -1775,7 +1774,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>42</v>
       </c>
       <c r="F46" s="12"/>
@@ -1785,7 +1784,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>43</v>
       </c>
       <c r="F47" s="12"/>

--- a/Watchlist .xlsx
+++ b/Watchlist .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6797E5F0-C20A-4522-9636-9EAC2A04473F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A326EA-C509-43AB-A6D9-C12921C7616A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
   </bookViews>

--- a/Watchlist .xlsx
+++ b/Watchlist .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A326EA-C509-43AB-A6D9-C12921C7616A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EBCB125-763F-4900-BFE6-9874D6A05372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
   </bookViews>
@@ -388,12 +388,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>78.3</v>
+            <v>73.849999999999994</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>1574.7186267</v>
+            <v>1485.2231236499999</v>
           </cell>
         </row>
         <row r="5">
@@ -428,12 +428,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>8.16</v>
+            <v>7.72</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>13789.033738560001</v>
+            <v>13045.50740952</v>
           </cell>
         </row>
         <row r="5">
@@ -469,12 +469,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>177.4</v>
+            <v>178.72</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>20129.237746800001</v>
+            <v>20279.01561504</v>
           </cell>
         </row>
         <row r="5">
@@ -513,12 +513,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>35.450000000000003</v>
+            <v>34.51</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>5419.0373789000005</v>
+            <v>5275.3449914199991</v>
           </cell>
         </row>
         <row r="5">
@@ -532,10 +532,10 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -555,12 +555,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>172</v>
+            <v>177</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>3002397.5999999996</v>
+            <v>3089676.6</v>
           </cell>
         </row>
         <row r="6">
@@ -594,12 +594,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>85.3</v>
+            <v>93</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>5799.8605627999996</v>
+            <v>6323.4118679999992</v>
           </cell>
         </row>
         <row r="5">
@@ -633,12 +633,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>256.39999999999998</v>
+            <v>266.8</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>340780.2144</v>
+            <v>354602.81280000001</v>
           </cell>
         </row>
         <row r="5">
@@ -996,7 +996,7 @@
       </c>
       <c r="M2" s="19">
         <f>+SUM(M5:M9)</f>
-        <v>-7.864442176608788E-2</v>
+        <v>-0.16146352849083656</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
@@ -1067,11 +1067,11 @@
       </c>
       <c r="E5" s="9">
         <f>+[1]Main!$J$2</f>
-        <v>78.3</v>
+        <v>73.849999999999994</v>
       </c>
       <c r="F5" s="12">
         <f>+[1]Main!$J$4*FX!C2</f>
-        <v>1842.4207932389997</v>
+        <v>1737.7110546704998</v>
       </c>
       <c r="G5" s="12">
         <f>(+[1]Main!$J$6-[1]Main!$J$5)*FX!C2</f>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="H5" s="12">
         <f t="shared" ref="H5:H11" si="0">+F5+G5</f>
-        <v>1999.2382332389998</v>
+        <v>1894.5284946704999</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>18</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="M5" s="18">
         <f>+E5/L5-1</f>
-        <v>-0.21068548387096775</v>
+        <v>-0.25554435483870974</v>
       </c>
       <c r="O5" s="10" t="s">
         <v>33</v>
@@ -1120,11 +1120,11 @@
       </c>
       <c r="E6" s="9">
         <f>+[2]Main!$I$2</f>
-        <v>8.16</v>
+        <v>7.72</v>
       </c>
       <c r="F6" s="12">
         <f>+[2]Main!$I$4</f>
-        <v>13789.033738560001</v>
+        <v>13045.50740952</v>
       </c>
       <c r="G6" s="12">
         <f>+[2]Main!$I$6-[2]Main!$I$5</f>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="H6" s="12">
         <f t="shared" si="0"/>
-        <v>14471.960738560001</v>
+        <v>13728.434409519999</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>18</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="M6" s="18">
         <f t="shared" ref="M6:M11" si="1">+E6/L6-1</f>
-        <v>9.6774193548387011E-2</v>
+        <v>3.7634408602150504E-2</v>
       </c>
       <c r="O6" s="10" t="s">
         <v>36</v>
@@ -1176,11 +1176,11 @@
       </c>
       <c r="E7" s="9">
         <f>+[3]Main!$I$2</f>
-        <v>177.4</v>
+        <v>178.72</v>
       </c>
       <c r="F7" s="12">
         <f>+[3]Main!$I$4</f>
-        <v>20129.237746800001</v>
+        <v>20279.01561504</v>
       </c>
       <c r="G7" s="12">
         <f>+[3]Main!$I$6-[3]Main!$I$5</f>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H7" s="12">
         <f t="shared" si="0"/>
-        <v>18973.4437468</v>
+        <v>19123.221615039998</v>
       </c>
       <c r="I7" s="17" t="s">
         <v>18</v>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M7" s="18">
         <f t="shared" si="1"/>
-        <v>-0.10571154912537173</v>
+        <v>-9.9057317134647382E-2</v>
       </c>
       <c r="O7" s="10" t="s">
         <v>35</v>
@@ -1229,11 +1229,11 @@
       </c>
       <c r="E8" s="9">
         <f>+[4]Main!$H$2</f>
-        <v>35.450000000000003</v>
+        <v>34.51</v>
       </c>
       <c r="F8" s="12">
         <f>+[4]Main!$H$4</f>
-        <v>5419.0373789000005</v>
+        <v>5275.3449914199991</v>
       </c>
       <c r="G8" s="12">
         <f>+[4]Main!$H$6-[4]Main!$H$5</f>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="H8" s="12">
         <f t="shared" si="0"/>
-        <v>6661.861378900001</v>
+        <v>6518.1689914199997</v>
       </c>
       <c r="I8" s="8" t="s">
         <v>18</v>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="M8" s="18">
         <f t="shared" si="1"/>
-        <v>-0.14164648910411615</v>
+        <v>-0.16440677966101691</v>
       </c>
       <c r="O8" s="10" t="s">
         <v>34</v>
@@ -1282,11 +1282,11 @@
       </c>
       <c r="E9" s="9">
         <f>+[5]Main!$J$2</f>
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F9" s="12">
         <f>+[5]Main!$J$5*FX!C3</f>
-        <v>420335.66399999999</v>
+        <v>432554.72400000005</v>
       </c>
       <c r="G9" s="12">
         <f>+([5]Main!$J$7-[5]Main!$J$6)*FX!C3</f>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H9" s="12">
         <f t="shared" si="0"/>
-        <v>378426.10399999999</v>
+        <v>390645.16400000005</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>40</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="M9" s="18">
         <f t="shared" si="1"/>
-        <v>0.28262490678598073</v>
+        <v>0.31991051454138697</v>
       </c>
       <c r="O9" s="16" t="s">
         <v>41</v>
@@ -1335,11 +1335,11 @@
       </c>
       <c r="E10" s="9">
         <f>+[6]Main!$J$2</f>
-        <v>85.3</v>
+        <v>93</v>
       </c>
       <c r="F10" s="12">
         <f>+([6]Main!$J$4)*FX!C2</f>
-        <v>6785.8368584759992</v>
+        <v>7398.3918855599986</v>
       </c>
       <c r="G10" s="12">
         <f>+([6]Main!$J$6-[6]Main!$J$5)*FX!C2</f>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="H10" s="12">
         <f t="shared" si="0"/>
-        <v>6508.7796884759991</v>
+        <v>7121.3347155599986</v>
       </c>
       <c r="I10" s="22" t="s">
         <v>18</v>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="M10" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9.0269636576787882E-2</v>
       </c>
       <c r="O10" s="21" t="s">
         <v>47</v>
@@ -1391,11 +1391,11 @@
       </c>
       <c r="E11" s="9">
         <f>+[7]Main!$I$2</f>
-        <v>256.39999999999998</v>
+        <v>266.8</v>
       </c>
       <c r="F11" s="12">
         <f>+[7]Main!$I$4*FX!C3</f>
-        <v>47709.230016000001</v>
+        <v>49644.39379200001</v>
       </c>
       <c r="G11" s="12">
         <f>+([7]Main!$I$6-[7]Main!$I$5)*FX!C3</f>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H11" s="12">
         <f t="shared" si="0"/>
-        <v>45782.030476</v>
+        <v>47717.194252000008</v>
       </c>
       <c r="I11" s="22" t="s">
         <v>18</v>
@@ -1415,8 +1415,8 @@
         <v>256.39999999999998</v>
       </c>
       <c r="M11" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>+E11/L11-1</f>
+        <v>4.0561622464898806E-2</v>
       </c>
       <c r="O11" s="21" t="s">
         <v>52</v>

--- a/Watchlist .xlsx
+++ b/Watchlist .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EBCB125-763F-4900-BFE6-9874D6A05372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD48825-83BC-4B93-9F15-D09595D45F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
   </bookViews>
@@ -24,6 +24,7 @@
     <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
     <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="56">
   <si>
     <t>Watchlist</t>
   </si>
@@ -207,10 +208,13 @@
     <t>Toys</t>
   </si>
   <si>
-    <t>longs</t>
-  </si>
-  <si>
     <t>Labubu Hype</t>
+  </si>
+  <si>
+    <t>EBAY</t>
+  </si>
+  <si>
+    <t>Marketplace</t>
   </si>
 </sst>
 </file>
@@ -220,13 +224,25 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -305,55 +321,64 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" customBuiltin="1"/>
@@ -388,12 +413,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>73.849999999999994</v>
+            <v>87.86</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>1485.2231236499999</v>
+            <v>1766.9831231400001</v>
           </cell>
         </row>
         <row r="5">
@@ -407,8 +432,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -428,12 +453,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>7.72</v>
+            <v>8.59</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>13045.50740952</v>
+            <v>14515.661741940001</v>
           </cell>
         </row>
         <row r="5">
@@ -469,12 +494,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>178.72</v>
+            <v>174.02</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>20279.01561504</v>
+            <v>19745.715629639999</v>
           </cell>
         </row>
         <row r="5">
@@ -649,6 +674,45 @@
         <row r="6">
           <cell r="I6">
             <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>92.17</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>42121.69</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>3750</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>6748</v>
           </cell>
         </row>
       </sheetData>
@@ -996,7 +1060,7 @@
       </c>
       <c r="M2" s="19">
         <f>+SUM(M5:M9)</f>
-        <v>-0.16146352849083656</v>
+        <v>7.3008695334956575E-2</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
@@ -1067,19 +1131,19 @@
       </c>
       <c r="E5" s="9">
         <f>+[1]Main!$J$2</f>
-        <v>73.849999999999994</v>
+        <v>87.86</v>
       </c>
       <c r="F5" s="12">
         <f>+[1]Main!$J$4*FX!C2</f>
-        <v>1737.7110546704998</v>
+        <v>2067.3702540738</v>
       </c>
       <c r="G5" s="12">
         <f>(+[1]Main!$J$6-[1]Main!$J$5)*FX!C2</f>
         <v>156.81744000000003</v>
       </c>
       <c r="H5" s="12">
-        <f t="shared" ref="H5:H11" si="0">+F5+G5</f>
-        <v>1894.5284946704999</v>
+        <f t="shared" ref="H5:H12" si="0">+F5+G5</f>
+        <v>2224.1876940738002</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>18</v>
@@ -1095,7 +1159,7 @@
       </c>
       <c r="M5" s="18">
         <f>+E5/L5-1</f>
-        <v>-0.25554435483870974</v>
+        <v>-0.11431451612903232</v>
       </c>
       <c r="O5" s="10" t="s">
         <v>33</v>
@@ -1120,11 +1184,11 @@
       </c>
       <c r="E6" s="9">
         <f>+[2]Main!$I$2</f>
-        <v>7.72</v>
+        <v>8.59</v>
       </c>
       <c r="F6" s="12">
         <f>+[2]Main!$I$4</f>
-        <v>13045.50740952</v>
+        <v>14515.661741940001</v>
       </c>
       <c r="G6" s="12">
         <f>+[2]Main!$I$6-[2]Main!$I$5</f>
@@ -1132,13 +1196,13 @@
       </c>
       <c r="H6" s="12">
         <f t="shared" si="0"/>
-        <v>13728.434409519999</v>
+        <v>15198.588741940001</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="13">
-        <v>45897</v>
+      <c r="J6" s="27">
+        <v>45958</v>
       </c>
       <c r="K6" s="13">
         <v>45889</v>
@@ -1147,8 +1211,8 @@
         <v>7.44</v>
       </c>
       <c r="M6" s="18">
-        <f t="shared" ref="M6:M11" si="1">+E6/L6-1</f>
-        <v>3.7634408602150504E-2</v>
+        <f t="shared" ref="M6:M10" si="1">+E6/L6-1</f>
+        <v>0.15456989247311825</v>
       </c>
       <c r="O6" s="10" t="s">
         <v>36</v>
@@ -1176,11 +1240,11 @@
       </c>
       <c r="E7" s="9">
         <f>+[3]Main!$I$2</f>
-        <v>178.72</v>
+        <v>174.02</v>
       </c>
       <c r="F7" s="12">
         <f>+[3]Main!$I$4</f>
-        <v>20279.01561504</v>
+        <v>19745.715629639999</v>
       </c>
       <c r="G7" s="12">
         <f>+[3]Main!$I$6-[3]Main!$I$5</f>
@@ -1188,7 +1252,7 @@
       </c>
       <c r="H7" s="12">
         <f t="shared" si="0"/>
-        <v>19123.221615039998</v>
+        <v>18589.921629639997</v>
       </c>
       <c r="I7" s="17" t="s">
         <v>18</v>
@@ -1204,7 +1268,7 @@
       </c>
       <c r="M7" s="18">
         <f t="shared" si="1"/>
-        <v>-9.9057317134647382E-2</v>
+        <v>-0.12275041588949942</v>
       </c>
       <c r="O7" s="10" t="s">
         <v>35</v>
@@ -1247,7 +1311,7 @@
         <v>18</v>
       </c>
       <c r="J8" s="13">
-        <v>45892</v>
+        <v>45953</v>
       </c>
       <c r="K8" s="13">
         <v>45902</v>
@@ -1408,6 +1472,9 @@
       <c r="I11" s="22" t="s">
         <v>18</v>
       </c>
+      <c r="J11" s="13">
+        <v>46078</v>
+      </c>
       <c r="K11" s="13">
         <v>45926</v>
       </c>
@@ -1421,11 +1488,11 @@
       <c r="O11" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="P11" s="20" t="s">
+      <c r="P11" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q11" s="20" t="s">
         <v>53</v>
-      </c>
-      <c r="Q11" s="20" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
@@ -1433,11 +1500,53 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="8"/>
+      <c r="B12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="9">
+        <f>+[8]Main!$H$2</f>
+        <v>92.17</v>
+      </c>
+      <c r="F12" s="12">
+        <f>+[8]Main!$H$4</f>
+        <v>42121.69</v>
+      </c>
+      <c r="G12" s="12">
+        <f>+([8]Main!$H$6-[8]Main!$H$5)</f>
+        <v>2998</v>
+      </c>
+      <c r="H12" s="12">
+        <f t="shared" si="0"/>
+        <v>45119.69</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="25">
+        <v>45959</v>
+      </c>
+      <c r="K12" s="13">
+        <v>45934</v>
+      </c>
+      <c r="L12" s="9">
+        <v>92.17</v>
+      </c>
+      <c r="M12" s="18">
+        <f>+E12/L12-1</f>
+        <v>0</v>
+      </c>
+      <c r="O12" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="P12" s="14" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="11">
@@ -2068,6 +2177,7 @@
     <hyperlink ref="B9" r:id="rId5" xr:uid="{008C64C3-FE55-425E-8F91-6D7191763AE3}"/>
     <hyperlink ref="B10" r:id="rId6" xr:uid="{2F35C231-9D4B-4712-94E5-6754F841B088}"/>
     <hyperlink ref="B11" r:id="rId7" xr:uid="{AED81220-75B7-4217-BDBB-E6654FE09225}"/>
+    <hyperlink ref="B12" r:id="rId8" xr:uid="{B5E94AC4-BA08-461E-866C-8E618213DE8F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Watchlist .xlsx
+++ b/Watchlist .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD48825-83BC-4B93-9F15-D09595D45F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62884A1D-964B-483E-8BEC-8495CC6501C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
   </bookViews>
@@ -25,6 +25,8 @@
     <externalReference r:id="rId8"/>
     <externalReference r:id="rId9"/>
     <externalReference r:id="rId10"/>
+    <externalReference r:id="rId11"/>
+    <externalReference r:id="rId12"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="64">
   <si>
     <t>Watchlist</t>
   </si>
@@ -215,6 +217,30 @@
   </si>
   <si>
     <t>Marketplace</t>
+  </si>
+  <si>
+    <t>Fiserv</t>
+  </si>
+  <si>
+    <t>Scandivian Tobacco</t>
+  </si>
+  <si>
+    <t>STG.CO</t>
+  </si>
+  <si>
+    <t>DEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crash </t>
+  </si>
+  <si>
+    <t>FI</t>
+  </si>
+  <si>
+    <t>Q424</t>
+  </si>
+  <si>
+    <t>DKK/USD</t>
   </si>
 </sst>
 </file>
@@ -224,13 +250,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -321,64 +353,68 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" customBuiltin="1"/>
@@ -432,8 +468,47 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>86.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>6820.9575000000004</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>67.900000000000006</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>5226.3</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -713,6 +788,45 @@
         <row r="6">
           <cell r="H6">
             <v>6748</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>62.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>35080.559000000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1236</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>24840</v>
           </cell>
         </row>
       </sheetData>
@@ -1142,7 +1256,7 @@
         <v>156.81744000000003</v>
       </c>
       <c r="H5" s="12">
-        <f t="shared" ref="H5:H12" si="0">+F5+G5</f>
+        <f t="shared" ref="H5:H14" si="0">+F5+G5</f>
         <v>2224.1876940738002</v>
       </c>
       <c r="I5" s="8" t="s">
@@ -1553,22 +1667,77 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="8"/>
+      <c r="B13" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="9">
+        <f>+[9]Main!$I$2</f>
+        <v>62.5</v>
+      </c>
+      <c r="F13" s="12">
+        <f>+[9]Main!$I$4</f>
+        <v>35080.559000000001</v>
+      </c>
+      <c r="G13" s="12">
+        <f>+[9]Main!$I$6-[9]Main!$I$5</f>
+        <v>23604</v>
+      </c>
+      <c r="H13" s="12">
+        <f t="shared" si="0"/>
+        <v>58684.559000000001</v>
+      </c>
+      <c r="I13" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="P13" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q13" s="28" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="11">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="8"/>
+      <c r="B14" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="9">
+        <f>+[10]Main!$J$2</f>
+        <v>86.5</v>
+      </c>
+      <c r="F14" s="12">
+        <f>+[10]Main!$J$4*FX!C4</f>
+        <v>1091.3532</v>
+      </c>
+      <c r="G14" s="12">
+        <f>+([10]Main!$J$6-[10]Main!$J$5)*FX!C4</f>
+        <v>825.34400000000005</v>
+      </c>
+      <c r="H14" s="12">
+        <f t="shared" si="0"/>
+        <v>1916.6972000000001</v>
+      </c>
+      <c r="I14" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="P14" s="14" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="11">
@@ -1580,6 +1749,7 @@
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>
       <c r="I15" s="8"/>
+      <c r="P15" s="14"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="11">
@@ -2178,6 +2348,7 @@
     <hyperlink ref="B10" r:id="rId6" xr:uid="{2F35C231-9D4B-4712-94E5-6754F841B088}"/>
     <hyperlink ref="B11" r:id="rId7" xr:uid="{AED81220-75B7-4217-BDBB-E6654FE09225}"/>
     <hyperlink ref="B12" r:id="rId8" xr:uid="{B5E94AC4-BA08-461E-866C-8E618213DE8F}"/>
+    <hyperlink ref="B13" r:id="rId9" xr:uid="{393CB23F-6784-4298-AFD5-19F3BDBBFE90}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2222,8 +2393,12 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
+      <c r="B4" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.16</v>
+      </c>
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">

--- a/Watchlist .xlsx
+++ b/Watchlist .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62884A1D-964B-483E-8BEC-8495CC6501C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05BC26B5-8649-4328-BF15-C53CDC931DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="66">
   <si>
     <t>Watchlist</t>
   </si>
@@ -237,10 +237,16 @@
     <t>FI</t>
   </si>
   <si>
-    <t>Q424</t>
-  </si>
-  <si>
     <t>DKK/USD</t>
+  </si>
+  <si>
+    <t>Q323</t>
+  </si>
+  <si>
+    <t>FinTech</t>
+  </si>
+  <si>
+    <t>Tobacco</t>
   </si>
 </sst>
 </file>
@@ -250,13 +256,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -353,67 +365,73 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -816,21 +834,21 @@
         </row>
         <row r="4">
           <cell r="I4">
-            <v>35080.559000000001</v>
+            <v>33615.742937499999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>1236</v>
+            <v>1068</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>24840</v>
+            <v>30199</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1682,18 +1700,31 @@
       </c>
       <c r="F13" s="12">
         <f>+[9]Main!$I$4</f>
-        <v>35080.559000000001</v>
+        <v>33615.742937499999</v>
       </c>
       <c r="G13" s="12">
         <f>+[9]Main!$I$6-[9]Main!$I$5</f>
-        <v>23604</v>
+        <v>29131</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="0"/>
-        <v>58684.559000000001</v>
-      </c>
-      <c r="I13" s="29" t="s">
-        <v>62</v>
+        <v>62746.742937499999</v>
+      </c>
+      <c r="I13" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="K13" s="13">
+        <v>45967</v>
+      </c>
+      <c r="L13" s="9">
+        <v>62.5</v>
+      </c>
+      <c r="M13" s="18">
+        <f>+E13/L13-1</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="31" t="s">
+        <v>64</v>
       </c>
       <c r="P13" s="14" t="s">
         <v>21</v>
@@ -1734,6 +1765,19 @@
       </c>
       <c r="I14" s="29" t="s">
         <v>18</v>
+      </c>
+      <c r="K14" s="13">
+        <v>45967</v>
+      </c>
+      <c r="L14" s="9">
+        <v>86.5</v>
+      </c>
+      <c r="M14" s="18">
+        <f>+E14/L14-1</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="31" t="s">
+        <v>65</v>
       </c>
       <c r="P14" s="14" t="s">
         <v>21</v>
@@ -2394,7 +2438,7 @@
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4" s="3">
         <v>0.16</v>

--- a/Watchlist .xlsx
+++ b/Watchlist .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05BC26B5-8649-4328-BF15-C53CDC931DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4F40FA-4D62-4565-BD2B-F4D5EAC10D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
   </bookViews>
@@ -526,7 +526,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -546,26 +546,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>8.59</v>
+            <v>8.2100000000000009</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>14515.661741940001</v>
+            <v>14115.934196310003</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>2893.0450000000001</v>
+            <v>2993.377</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>3575.9720000000002</v>
+            <v>3537.8890000000001</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -848,7 +848,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="M2" s="19">
         <f>+SUM(M5:M9)</f>
-        <v>7.3008695334956575E-2</v>
+        <v>2.1933426517752319E-2</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
@@ -1316,19 +1316,19 @@
       </c>
       <c r="E6" s="9">
         <f>+[2]Main!$I$2</f>
-        <v>8.59</v>
+        <v>8.2100000000000009</v>
       </c>
       <c r="F6" s="12">
         <f>+[2]Main!$I$4</f>
-        <v>14515.661741940001</v>
+        <v>14115.934196310003</v>
       </c>
       <c r="G6" s="12">
         <f>+[2]Main!$I$6-[2]Main!$I$5</f>
-        <v>682.92700000000013</v>
+        <v>544.51200000000017</v>
       </c>
       <c r="H6" s="12">
         <f t="shared" si="0"/>
-        <v>15198.588741940001</v>
+        <v>14660.446196310004</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>18</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M6" s="18">
         <f t="shared" ref="M6:M10" si="1">+E6/L6-1</f>
-        <v>0.15456989247311825</v>
+        <v>0.103494623655914</v>
       </c>
       <c r="O6" s="10" t="s">
         <v>36</v>
@@ -2393,6 +2393,7 @@
     <hyperlink ref="B11" r:id="rId7" xr:uid="{AED81220-75B7-4217-BDBB-E6654FE09225}"/>
     <hyperlink ref="B12" r:id="rId8" xr:uid="{B5E94AC4-BA08-461E-866C-8E618213DE8F}"/>
     <hyperlink ref="B13" r:id="rId9" xr:uid="{393CB23F-6784-4298-AFD5-19F3BDBBFE90}"/>
+    <hyperlink ref="B14" r:id="rId10" xr:uid="{30A9981A-0AC0-4E59-B3F8-4D7739771C07}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Watchlist .xlsx
+++ b/Watchlist .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4F40FA-4D62-4565-BD2B-F4D5EAC10D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4698C4-BDF8-484C-8561-ED46DABCB7BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
   </bookViews>
@@ -502,6 +502,8 @@
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
+      <sheetName val="KPI"/>
+      <sheetName val="DCF"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -512,21 +514,23 @@
         </row>
         <row r="4">
           <cell r="J4">
-            <v>6820.9575000000004</v>
+            <v>6822.6875</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>67.900000000000006</v>
+            <v>97.5</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>5226.3</v>
+            <v>5104.8999999999996</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -565,7 +569,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1753,15 +1757,15 @@
       </c>
       <c r="F14" s="12">
         <f>+[10]Main!$J$4*FX!C4</f>
-        <v>1091.3532</v>
+        <v>1091.6300000000001</v>
       </c>
       <c r="G14" s="12">
         <f>+([10]Main!$J$6-[10]Main!$J$5)*FX!C4</f>
-        <v>825.34400000000005</v>
+        <v>801.18399999999997</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="0"/>
-        <v>1916.6972000000001</v>
+        <v>1892.8140000000001</v>
       </c>
       <c r="I14" s="29" t="s">
         <v>18</v>

--- a/Watchlist .xlsx
+++ b/Watchlist .xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4698C4-BDF8-484C-8561-ED46DABCB7BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5CC8528-F20E-4389-A643-0069DFE222F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
+    <workbookView xWindow="225" yWindow="3855" windowWidth="38175" windowHeight="15240" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -528,9 +528,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -583,7 +583,7 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
-      <sheetName val="Financials"/>
+      <sheetName val="Model"/>
       <sheetName val="Ratios"/>
       <sheetName val="DCF"/>
     </sheetNames>
@@ -591,17 +591,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>174.02</v>
+            <v>204.5</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>19745.715629639999</v>
+            <v>22942.8633845</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>1155.7940000000001</v>
+            <v>1035.8620000000001</v>
           </cell>
         </row>
         <row r="6">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="M2" s="19">
         <f>+SUM(M5:M9)</f>
-        <v>2.1933426517752319E-2</v>
+        <v>0.17558569248538858</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
@@ -1376,19 +1376,19 @@
       </c>
       <c r="E7" s="9">
         <f>+[3]Main!$I$2</f>
-        <v>174.02</v>
+        <v>204.5</v>
       </c>
       <c r="F7" s="12">
         <f>+[3]Main!$I$4</f>
-        <v>19745.715629639999</v>
+        <v>22942.8633845</v>
       </c>
       <c r="G7" s="12">
         <f>+[3]Main!$I$6-[3]Main!$I$5</f>
-        <v>-1155.7940000000001</v>
+        <v>-1035.8620000000001</v>
       </c>
       <c r="H7" s="12">
         <f t="shared" si="0"/>
-        <v>18589.921629639997</v>
+        <v>21907.001384499999</v>
       </c>
       <c r="I7" s="17" t="s">
         <v>18</v>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="M7" s="18">
         <f t="shared" si="1"/>
-        <v>-0.12275041588949942</v>
+        <v>3.0901850078136839E-2</v>
       </c>
       <c r="O7" s="10" t="s">
         <v>35</v>

--- a/Watchlist .xlsx
+++ b/Watchlist .xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5CC8528-F20E-4389-A643-0069DFE222F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE8FFC6B-032C-4630-B4F0-0EA56CB079C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3855" windowWidth="38175" windowHeight="15240" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
+    <workbookView xWindow="225" yWindow="1560" windowWidth="38175" windowHeight="15240" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,6 @@
     <externalReference r:id="rId9"/>
     <externalReference r:id="rId10"/>
     <externalReference r:id="rId11"/>
-    <externalReference r:id="rId12"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="62">
   <si>
     <t>Watchlist</t>
   </si>
@@ -222,15 +221,6 @@
     <t>Fiserv</t>
   </si>
   <si>
-    <t>Scandivian Tobacco</t>
-  </si>
-  <si>
-    <t>STG.CO</t>
-  </si>
-  <si>
-    <t>DEN</t>
-  </si>
-  <si>
     <t xml:space="preserve">Crash </t>
   </si>
   <si>
@@ -244,9 +234,6 @@
   </si>
   <si>
     <t>FinTech</t>
-  </si>
-  <si>
-    <t>Tobacco</t>
   </si>
 </sst>
 </file>
@@ -368,7 +355,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -424,9 +411,6 @@
     </xf>
     <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -457,6 +441,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -467,12 +452,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>87.86</v>
+            <v>43.24</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>1766.9831231400001</v>
+            <v>869.61473076000004</v>
           </cell>
         </row>
         <row r="5">
@@ -486,51 +471,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="KPI"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>86.5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>6822.6875</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>97.5</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>5104.8999999999996</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -541,6 +483,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -550,12 +493,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>8.2100000000000009</v>
+            <v>5.75</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>14115.934196310003</v>
+            <v>9886.3120132500007</v>
           </cell>
         </row>
         <row r="5">
@@ -569,7 +512,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -580,6 +523,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -591,17 +535,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>204.5</v>
+            <v>127.35</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>22942.8633845</v>
+            <v>14069.968151849998</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>1035.8620000000001</v>
+            <v>1807.202</v>
           </cell>
         </row>
         <row r="6">
@@ -610,9 +554,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -623,6 +567,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -635,12 +580,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>34.51</v>
+            <v>51.9</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>5275.3449914199991</v>
+            <v>7933.6541597999994</v>
           </cell>
         </row>
         <row r="5">
@@ -654,10 +599,10 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -668,6 +613,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -677,12 +623,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>177</v>
+            <v>124.3</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>3089676.6</v>
+            <v>2169755.94</v>
           </cell>
         </row>
         <row r="6">
@@ -696,7 +642,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -707,6 +653,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -716,26 +663,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>93</v>
+            <v>86.1</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>6323.4118679999992</v>
+            <v>5854.2555035999994</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>243.84100000000001</v>
+            <v>203.84100000000001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>7.04</v>
+            <v>396.62300000000005</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -746,6 +693,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -755,12 +703,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>266.8</v>
+            <v>154.19999999999999</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>354602.81280000001</v>
+            <v>204946.60319999998</v>
           </cell>
         </row>
         <row r="5">
@@ -774,7 +722,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -785,6 +733,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -794,26 +743,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>92.17</v>
+            <v>115.31</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>42121.69</v>
+            <v>51658.880000000005</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>3750</v>
+            <v>2919</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>6748</v>
+            <v>6746</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -824,6 +773,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -833,12 +783,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>62.5</v>
+            <v>55.6</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>33615.742937499999</v>
+            <v>29904.564917200001</v>
           </cell>
         </row>
         <row r="5">
@@ -852,7 +802,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1175,7 +1125,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2564A331-3821-4718-A769-006CA9DC39E7}">
-  <dimension ref="A1:Q131"/>
+  <dimension ref="A1:Q130"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.5703125" style="9" customWidth="1"/>
@@ -1194,10 +1144,7 @@
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="19">
-        <f>+SUM(M5:M9)</f>
-        <v>0.17558569248538858</v>
-      </c>
+      <c r="M2" s="19"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
@@ -1267,19 +1214,19 @@
       </c>
       <c r="E5" s="9">
         <f>+[1]Main!$J$2</f>
-        <v>87.86</v>
+        <v>43.24</v>
       </c>
       <c r="F5" s="12">
         <f>+[1]Main!$J$4*FX!C2</f>
-        <v>2067.3702540738</v>
+        <v>1017.4492349892</v>
       </c>
       <c r="G5" s="12">
         <f>(+[1]Main!$J$6-[1]Main!$J$5)*FX!C2</f>
         <v>156.81744000000003</v>
       </c>
       <c r="H5" s="12">
-        <f t="shared" ref="H5:H14" si="0">+F5+G5</f>
-        <v>2224.1876940738002</v>
+        <f t="shared" ref="H5:H13" si="0">+F5+G5</f>
+        <v>1174.2666749892001</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>18</v>
@@ -1295,7 +1242,7 @@
       </c>
       <c r="M5" s="18">
         <f>+E5/L5-1</f>
-        <v>-0.11431451612903232</v>
+        <v>-0.56411290322580643</v>
       </c>
       <c r="O5" s="10" t="s">
         <v>33</v>
@@ -1320,11 +1267,11 @@
       </c>
       <c r="E6" s="9">
         <f>+[2]Main!$I$2</f>
-        <v>8.2100000000000009</v>
+        <v>5.75</v>
       </c>
       <c r="F6" s="12">
         <f>+[2]Main!$I$4</f>
-        <v>14115.934196310003</v>
+        <v>9886.3120132500007</v>
       </c>
       <c r="G6" s="12">
         <f>+[2]Main!$I$6-[2]Main!$I$5</f>
@@ -1332,7 +1279,7 @@
       </c>
       <c r="H6" s="12">
         <f t="shared" si="0"/>
-        <v>14660.446196310004</v>
+        <v>10430.824013250001</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>18</v>
@@ -1348,7 +1295,7 @@
       </c>
       <c r="M6" s="18">
         <f t="shared" ref="M6:M10" si="1">+E6/L6-1</f>
-        <v>0.103494623655914</v>
+        <v>-0.22715053763440862</v>
       </c>
       <c r="O6" s="10" t="s">
         <v>36</v>
@@ -1362,7 +1309,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
-        <f t="shared" ref="A7:A47" si="2">+A6+1</f>
+        <f t="shared" ref="A7:A46" si="2">+A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -1376,19 +1323,19 @@
       </c>
       <c r="E7" s="9">
         <f>+[3]Main!$I$2</f>
-        <v>204.5</v>
+        <v>127.35</v>
       </c>
       <c r="F7" s="12">
         <f>+[3]Main!$I$4</f>
-        <v>22942.8633845</v>
+        <v>14069.968151849998</v>
       </c>
       <c r="G7" s="12">
         <f>+[3]Main!$I$6-[3]Main!$I$5</f>
-        <v>-1035.8620000000001</v>
+        <v>-1807.202</v>
       </c>
       <c r="H7" s="12">
         <f t="shared" si="0"/>
-        <v>21907.001384499999</v>
+        <v>12262.766151849999</v>
       </c>
       <c r="I7" s="17" t="s">
         <v>18</v>
@@ -1404,7 +1351,7 @@
       </c>
       <c r="M7" s="18">
         <f t="shared" si="1"/>
-        <v>3.0901850078136839E-2</v>
+        <v>-0.35801784544033877</v>
       </c>
       <c r="O7" s="10" t="s">
         <v>35</v>
@@ -1429,11 +1376,11 @@
       </c>
       <c r="E8" s="9">
         <f>+[4]Main!$H$2</f>
-        <v>34.51</v>
+        <v>51.9</v>
       </c>
       <c r="F8" s="12">
         <f>+[4]Main!$H$4</f>
-        <v>5275.3449914199991</v>
+        <v>7933.6541597999994</v>
       </c>
       <c r="G8" s="12">
         <f>+[4]Main!$H$6-[4]Main!$H$5</f>
@@ -1441,7 +1388,7 @@
       </c>
       <c r="H8" s="12">
         <f t="shared" si="0"/>
-        <v>6518.1689914199997</v>
+        <v>9176.478159799999</v>
       </c>
       <c r="I8" s="8" t="s">
         <v>18</v>
@@ -1457,7 +1404,7 @@
       </c>
       <c r="M8" s="18">
         <f t="shared" si="1"/>
-        <v>-0.16440677966101691</v>
+        <v>0.2566585956416465</v>
       </c>
       <c r="O8" s="10" t="s">
         <v>34</v>
@@ -1482,11 +1429,11 @@
       </c>
       <c r="E9" s="9">
         <f>+[5]Main!$J$2</f>
-        <v>177</v>
+        <v>124.3</v>
       </c>
       <c r="F9" s="12">
         <f>+[5]Main!$J$5*FX!C3</f>
-        <v>432554.72400000005</v>
+        <v>303765.83160000003</v>
       </c>
       <c r="G9" s="12">
         <f>+([5]Main!$J$7-[5]Main!$J$6)*FX!C3</f>
@@ -1494,7 +1441,7 @@
       </c>
       <c r="H9" s="12">
         <f t="shared" si="0"/>
-        <v>390645.16400000005</v>
+        <v>261856.27160000004</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>40</v>
@@ -1510,7 +1457,7 @@
       </c>
       <c r="M9" s="18">
         <f t="shared" si="1"/>
-        <v>0.31991051454138697</v>
+        <v>-7.30797912005966E-2</v>
       </c>
       <c r="O9" s="16" t="s">
         <v>41</v>
@@ -1535,19 +1482,19 @@
       </c>
       <c r="E10" s="9">
         <f>+[6]Main!$J$2</f>
-        <v>93</v>
+        <v>86.1</v>
       </c>
       <c r="F10" s="12">
         <f>+([6]Main!$J$4)*FX!C2</f>
-        <v>7398.3918855599986</v>
+        <v>6849.4789392119992</v>
       </c>
       <c r="G10" s="12">
         <f>+([6]Main!$J$6-[6]Main!$J$5)*FX!C2</f>
-        <v>-277.05716999999999</v>
+        <v>225.55494000000004</v>
       </c>
       <c r="H10" s="12">
         <f t="shared" si="0"/>
-        <v>7121.3347155599986</v>
+        <v>7075.0338792119992</v>
       </c>
       <c r="I10" s="22" t="s">
         <v>18</v>
@@ -1563,7 +1510,7 @@
       </c>
       <c r="M10" s="18">
         <f t="shared" si="1"/>
-        <v>9.0269636576787882E-2</v>
+        <v>9.3786635404453644E-3</v>
       </c>
       <c r="O10" s="21" t="s">
         <v>47</v>
@@ -1591,11 +1538,11 @@
       </c>
       <c r="E11" s="9">
         <f>+[7]Main!$I$2</f>
-        <v>266.8</v>
+        <v>154.19999999999999</v>
       </c>
       <c r="F11" s="12">
         <f>+[7]Main!$I$4*FX!C3</f>
-        <v>49644.39379200001</v>
+        <v>28692.524448</v>
       </c>
       <c r="G11" s="12">
         <f>+([7]Main!$I$6-[7]Main!$I$5)*FX!C3</f>
@@ -1603,7 +1550,7 @@
       </c>
       <c r="H11" s="12">
         <f t="shared" si="0"/>
-        <v>47717.194252000008</v>
+        <v>26765.324907999999</v>
       </c>
       <c r="I11" s="22" t="s">
         <v>18</v>
@@ -1619,7 +1566,7 @@
       </c>
       <c r="M11" s="18">
         <f>+E11/L11-1</f>
-        <v>4.0561622464898806E-2</v>
+        <v>-0.39859594383775354</v>
       </c>
       <c r="O11" s="21" t="s">
         <v>52</v>
@@ -1647,19 +1594,19 @@
       </c>
       <c r="E12" s="9">
         <f>+[8]Main!$H$2</f>
-        <v>92.17</v>
+        <v>115.31</v>
       </c>
       <c r="F12" s="12">
         <f>+[8]Main!$H$4</f>
-        <v>42121.69</v>
+        <v>51658.880000000005</v>
       </c>
       <c r="G12" s="12">
         <f>+([8]Main!$H$6-[8]Main!$H$5)</f>
-        <v>2998</v>
+        <v>3827</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="0"/>
-        <v>45119.69</v>
+        <v>55485.880000000005</v>
       </c>
       <c r="I12" s="24" t="s">
         <v>18</v>
@@ -1675,7 +1622,7 @@
       </c>
       <c r="M12" s="18">
         <f>+E12/L12-1</f>
-        <v>0</v>
+        <v>0.25105782792665732</v>
       </c>
       <c r="O12" s="26" t="s">
         <v>55</v>
@@ -1693,18 +1640,18 @@
         <v>56</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D13" s="28" t="s">
         <v>24</v>
       </c>
       <c r="E13" s="9">
         <f>+[9]Main!$I$2</f>
-        <v>62.5</v>
+        <v>55.6</v>
       </c>
       <c r="F13" s="12">
         <f>+[9]Main!$I$4</f>
-        <v>33615.742937499999</v>
+        <v>29904.564917200001</v>
       </c>
       <c r="G13" s="12">
         <f>+[9]Main!$I$6-[9]Main!$I$5</f>
@@ -1712,10 +1659,10 @@
       </c>
       <c r="H13" s="12">
         <f t="shared" si="0"/>
-        <v>62746.742937499999</v>
-      </c>
-      <c r="I13" s="30" t="s">
-        <v>63</v>
+        <v>59035.564917199998</v>
+      </c>
+      <c r="I13" s="29" t="s">
+        <v>60</v>
       </c>
       <c r="K13" s="13">
         <v>45967</v>
@@ -1725,16 +1672,16 @@
       </c>
       <c r="M13" s="18">
         <f>+E13/L13-1</f>
-        <v>0</v>
-      </c>
-      <c r="O13" s="31" t="s">
-        <v>64</v>
+        <v>-0.11039999999999994</v>
+      </c>
+      <c r="O13" s="30" t="s">
+        <v>61</v>
       </c>
       <c r="P13" s="14" t="s">
         <v>21</v>
       </c>
       <c r="Q13" s="28" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
@@ -1742,62 +1689,22 @@
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="9">
-        <f>+[10]Main!$J$2</f>
-        <v>86.5</v>
-      </c>
-      <c r="F14" s="12">
-        <f>+[10]Main!$J$4*FX!C4</f>
-        <v>1091.6300000000001</v>
-      </c>
-      <c r="G14" s="12">
-        <f>+([10]Main!$J$6-[10]Main!$J$5)*FX!C4</f>
-        <v>801.18399999999997</v>
-      </c>
-      <c r="H14" s="12">
-        <f t="shared" si="0"/>
-        <v>1892.8140000000001</v>
-      </c>
-      <c r="I14" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="K14" s="13">
-        <v>45967</v>
-      </c>
-      <c r="L14" s="9">
-        <v>86.5</v>
-      </c>
-      <c r="M14" s="18">
-        <f>+E14/L14-1</f>
-        <v>0</v>
-      </c>
-      <c r="O14" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="P14" s="14" t="s">
-        <v>21</v>
-      </c>
+      <c r="B14" s="7"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="8"/>
+      <c r="P14" s="14"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="11">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="B15" s="7"/>
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>
       <c r="I15" s="8"/>
-      <c r="P15" s="14"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="11">
@@ -2110,10 +2017,7 @@
       <c r="I46" s="8"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A47" s="11">
-        <f t="shared" si="2"/>
-        <v>43</v>
-      </c>
+      <c r="A47" s="11"/>
       <c r="F47" s="12"/>
       <c r="G47" s="12"/>
       <c r="H47" s="12"/>
@@ -2121,9 +2025,6 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="11"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="12"/>
       <c r="I48" s="8"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
@@ -2168,7 +2069,6 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="11"/>
-      <c r="I59" s="8"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="11"/>
@@ -2382,9 +2282,6 @@
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A130" s="11"/>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A131" s="11"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2397,7 +2294,6 @@
     <hyperlink ref="B11" r:id="rId7" xr:uid="{AED81220-75B7-4217-BDBB-E6654FE09225}"/>
     <hyperlink ref="B12" r:id="rId8" xr:uid="{B5E94AC4-BA08-461E-866C-8E618213DE8F}"/>
     <hyperlink ref="B13" r:id="rId9" xr:uid="{393CB23F-6784-4298-AFD5-19F3BDBBFE90}"/>
-    <hyperlink ref="B14" r:id="rId10" xr:uid="{30A9981A-0AC0-4E59-B3F8-4D7739771C07}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2443,7 +2339,7 @@
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="28" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C4" s="3">
         <v>0.16</v>

--- a/Watchlist .xlsx
+++ b/Watchlist .xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE8FFC6B-032C-4630-B4F0-0EA56CB079C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1A41BE-BE24-48BC-9310-69AB7D3AABDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="1560" windowWidth="38175" windowHeight="15240" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
+    <workbookView xWindow="225" yWindow="1950" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
-    <sheet name="FX" sheetId="2" r:id="rId2"/>
+    <sheet name="Portfolio" sheetId="3" r:id="rId2"/>
+    <sheet name="FX" sheetId="2" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
@@ -26,6 +26,7 @@
     <externalReference r:id="rId9"/>
     <externalReference r:id="rId10"/>
     <externalReference r:id="rId11"/>
+    <externalReference r:id="rId12"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="69">
   <si>
     <t>Watchlist</t>
   </si>
@@ -234,6 +235,27 @@
   </si>
   <si>
     <t>FinTech</t>
+  </si>
+  <si>
+    <t>Buy-In</t>
+  </si>
+  <si>
+    <t>BAT</t>
+  </si>
+  <si>
+    <t>Crocs</t>
+  </si>
+  <si>
+    <t>PayPal</t>
+  </si>
+  <si>
+    <t>Scandinavian Tobacco</t>
+  </si>
+  <si>
+    <t>Porsche SE</t>
+  </si>
+  <si>
+    <t>Frosta AG</t>
   </si>
 </sst>
 </file>
@@ -471,8 +493,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -512,7 +534,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -554,9 +576,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -599,10 +621,10 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -642,7 +664,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -682,7 +704,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -722,7 +744,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -762,7 +784,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -802,7 +824,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2300,6 +2322,268 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8328D887-56C2-45D2-86E7-3AD60D640181}">
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O1" s="10"/>
+    </row>
+    <row r="2" spans="1:17" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="19"/>
+      <c r="O2" s="10"/>
+    </row>
+    <row r="3" spans="1:17" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="O3" s="10"/>
+    </row>
+    <row r="4" spans="1:17" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="11">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="M5" s="18"/>
+      <c r="O5" s="10"/>
+    </row>
+    <row r="6" spans="1:17" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="11">
+        <f>+A5+1</f>
+        <v>2</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="13"/>
+      <c r="M6" s="18"/>
+      <c r="O6" s="10"/>
+    </row>
+    <row r="7" spans="1:17" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="11">
+        <f t="shared" ref="A7:A14" si="0">+A6+1</f>
+        <v>3</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="M7" s="18"/>
+      <c r="O7" s="10"/>
+    </row>
+    <row r="8" spans="1:17" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="11">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="M8" s="18"/>
+      <c r="O8" s="10"/>
+    </row>
+    <row r="9" spans="1:17" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="11">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="M9" s="18"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="14"/>
+    </row>
+    <row r="10" spans="1:17" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="11">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="M10" s="18"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="20"/>
+    </row>
+    <row r="11" spans="1:17" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="11">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="M11" s="18"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="20"/>
+    </row>
+    <row r="12" spans="1:17" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="11">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="13"/>
+      <c r="M12" s="18"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="14"/>
+    </row>
+    <row r="13" spans="1:17" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="11">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="29"/>
+      <c r="K13" s="13"/>
+      <c r="M13" s="18"/>
+      <c r="O13" s="30"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="28"/>
+    </row>
+    <row r="14" spans="1:17" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="11">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="8"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="14"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{1794CFC6-2AEA-4E11-A9BA-3889D0D75F94}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03B2DF4B-01E2-41F7-B53D-8680A3262A00}">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/Watchlist .xlsx
+++ b/Watchlist .xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FC492C-98BA-428B-9515-477FD33BCDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA0E0DC-229D-4AAF-93F4-BA88D4939769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -55,8 +55,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={7016EAAF-06C2-4B4E-B159-DD4D4D50A028}</author>
+  </authors>
+  <commentList>
+    <comment ref="L4" authorId="0" shapeId="0" xr:uid="{7016EAAF-06C2-4B4E-B159-DD4D4D50A028}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Average Price</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="98">
   <si>
     <t>Watchlist</t>
   </si>
@@ -333,21 +351,46 @@
   <si>
     <t>Automobil</t>
   </si>
+  <si>
+    <t>in Euro</t>
+  </si>
+  <si>
+    <t>Food</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
+  <si>
+    <t>n.a.</t>
+  </si>
+  <si>
+    <t>ASML</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -449,6 +492,11 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arials"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -469,79 +517,98 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="16" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="17" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -564,6 +631,48 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Quarters"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>66.3</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>1333.3824387</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>315.70799999999997</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>449.74</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -600,9 +709,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
       <sheetData sheetId="4">
         <row r="4">
           <cell r="J4">
@@ -610,46 +719,6 @@
           </cell>
         </row>
       </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>55.6</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>29904.564917200001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1068</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>30199</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -693,9 +762,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
       <sheetData sheetId="4">
         <row r="4">
           <cell r="J4">
@@ -703,7 +772,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="5"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -746,9 +815,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
       <sheetData sheetId="4">
         <row r="4">
           <cell r="J4">
@@ -971,60 +1040,18 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
-      <sheetName val="Quarters"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>43.24</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>869.61473076000004</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>315.70799999999997</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>449.74</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
       <sheetName val="Model"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>5.75</v>
+            <v>4.42</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>9886.3120132500007</v>
+            <v>7599.5650606200006</v>
           </cell>
         </row>
         <row r="5">
@@ -1044,7 +1071,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1061,12 +1088,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>114.34</v>
+            <v>110.86</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>12398.796003380001</v>
+            <v>12021.43191302</v>
           </cell>
         </row>
         <row r="5">
@@ -1088,7 +1115,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1106,12 +1133,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>51.9</v>
+            <v>59.96</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>7933.6541597999994</v>
+            <v>9165.7399503199995</v>
           </cell>
         </row>
         <row r="5">
@@ -1134,6 +1161,46 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>111</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>1937593.7999999998</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>374857</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="J7">
+            <v>75503</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -1149,22 +1216,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>124.3</v>
+            <v>81.2</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>5521.0864911999997</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>2169755.94</v>
+            <v>203.84100000000001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>374857</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="J7">
-            <v>75503</v>
+            <v>396.62300000000005</v>
           </cell>
         </row>
       </sheetData>
@@ -1188,23 +1255,23 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="J2">
-            <v>86.1</v>
+          <cell r="I2">
+            <v>160.9</v>
           </cell>
         </row>
         <row r="4">
-          <cell r="J4">
-            <v>5854.2555035999994</v>
+          <cell r="I4">
+            <v>213851.54640000002</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="J5">
-            <v>203.84100000000001</v>
+          <cell r="I5">
+            <v>13765.710999999999</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="J6">
-            <v>396.62300000000005</v>
+          <cell r="I6">
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -1228,23 +1295,23 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="I2">
-            <v>154.19999999999999</v>
+          <cell r="H2">
+            <v>107.58</v>
           </cell>
         </row>
         <row r="4">
-          <cell r="I4">
-            <v>204946.60319999998</v>
+          <cell r="H4">
+            <v>48195.839999999997</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="I5">
-            <v>13765.710999999999</v>
+          <cell r="H5">
+            <v>2919</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="I6">
-            <v>0</v>
+          <cell r="H6">
+            <v>6746</v>
           </cell>
         </row>
       </sheetData>
@@ -1268,23 +1335,23 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="H2">
-            <v>115.31</v>
+          <cell r="I2">
+            <v>50.7</v>
           </cell>
         </row>
         <row r="4">
-          <cell r="H4">
-            <v>51658.880000000005</v>
+          <cell r="I4">
+            <v>27269.090670900005</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="H5">
-            <v>2919</v>
+          <cell r="I5">
+            <v>1068</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="H6">
-            <v>6746</v>
+          <cell r="I6">
+            <v>30199</v>
           </cell>
         </row>
       </sheetData>
@@ -1292,6 +1359,12 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Oscar Settje" id="{4E634C5A-9FB4-4BCE-BEA8-F22D7E8CCFF9}" userId="7ff36870b9739543" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1609,10 +1682,18 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="L4" dT="2026-07-26T16:51:02.57" personId="{4E634C5A-9FB4-4BCE-BEA8-F22D7E8CCFF9}" id="{7016EAAF-06C2-4B4E-B159-DD4D4D50A028}">
+    <text>Average Price</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2564A331-3821-4718-A769-006CA9DC39E7}">
   <dimension ref="A1:Q130"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="3.5703125" style="9" customWidth="1"/>
     <col min="2" max="2" width="20" style="9" customWidth="1"/>
@@ -1621,18 +1702,18 @@
     <col min="16" max="16384" width="9.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
       <c r="M2" s="19"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -1685,7 +1766,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17">
       <c r="A5" s="11">
         <v>1</v>
       </c>
@@ -1699,20 +1780,20 @@
         <v>16</v>
       </c>
       <c r="E5" s="9">
-        <f>+[2]Main!$J$2</f>
-        <v>43.24</v>
+        <f>+[1]Main!$J$2</f>
+        <v>66.3</v>
       </c>
       <c r="F5" s="12">
-        <f>+[2]Main!$J$4*FX!C2</f>
-        <v>1017.4492349892</v>
+        <f>+[1]Main!$J$4*FX!C2</f>
+        <v>1560.0574532789999</v>
       </c>
       <c r="G5" s="12">
-        <f>(+[2]Main!$J$6-[2]Main!$J$5)*FX!C2</f>
+        <f>(+[1]Main!$J$6-[1]Main!$J$5)*FX!C2</f>
         <v>156.81744000000003</v>
       </c>
       <c r="H5" s="12">
         <f t="shared" ref="H5:H13" si="0">+F5+G5</f>
-        <v>1174.2666749892001</v>
+        <v>1716.8748932789999</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>18</v>
@@ -1728,7 +1809,7 @@
       </c>
       <c r="M5" s="18">
         <f>+E5/L5-1</f>
-        <v>-0.56411290322580643</v>
+        <v>-0.33165322580645162</v>
       </c>
       <c r="O5" s="10" t="s">
         <v>33</v>
@@ -1737,7 +1818,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17">
       <c r="A6" s="11">
         <f>+A5+1</f>
         <v>2</v>
@@ -1752,20 +1833,20 @@
         <v>24</v>
       </c>
       <c r="E6" s="9">
-        <f>+[3]Main!$I$2</f>
-        <v>5.75</v>
+        <f>+[2]Main!$I$2</f>
+        <v>4.42</v>
       </c>
       <c r="F6" s="12">
-        <f>+[3]Main!$I$4</f>
-        <v>9886.3120132500007</v>
+        <f>+[2]Main!$I$4</f>
+        <v>7599.5650606200006</v>
       </c>
       <c r="G6" s="12">
-        <f>+[3]Main!$I$6-[3]Main!$I$5</f>
+        <f>+[2]Main!$I$6-[2]Main!$I$5</f>
         <v>544.51200000000017</v>
       </c>
       <c r="H6" s="12">
         <f t="shared" si="0"/>
-        <v>10430.824013250001</v>
+        <v>8144.0770606200003</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>18</v>
@@ -1781,7 +1862,7 @@
       </c>
       <c r="M6" s="18">
         <f t="shared" ref="M6:M10" si="1">+E6/L6-1</f>
-        <v>-0.22715053763440862</v>
+        <v>-0.40591397849462374</v>
       </c>
       <c r="O6" s="10" t="s">
         <v>36</v>
@@ -1793,7 +1874,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17">
       <c r="A7" s="11">
         <f t="shared" ref="A7:A46" si="2">+A6+1</f>
         <v>3</v>
@@ -1808,20 +1889,20 @@
         <v>29</v>
       </c>
       <c r="E7" s="9">
-        <f>+[4]Main!$I$2</f>
-        <v>114.34</v>
+        <f>+[3]Main!$I$2</f>
+        <v>110.86</v>
       </c>
       <c r="F7" s="12">
-        <f>+[4]Main!$I$4</f>
-        <v>12398.796003380001</v>
+        <f>+[3]Main!$I$4</f>
+        <v>12021.43191302</v>
       </c>
       <c r="G7" s="12">
-        <f>+[4]Main!$I$6-[4]Main!$I$5</f>
+        <f>+[3]Main!$I$6-[3]Main!$I$5</f>
         <v>-1514.729</v>
       </c>
       <c r="H7" s="12">
         <f t="shared" si="0"/>
-        <v>10884.067003380002</v>
+        <v>10506.702913020001</v>
       </c>
       <c r="I7" s="17" t="s">
         <v>18</v>
@@ -1837,7 +1918,7 @@
       </c>
       <c r="M7" s="18">
         <f t="shared" si="1"/>
-        <v>-0.42360235922770584</v>
+        <v>-0.44114533447597926</v>
       </c>
       <c r="O7" s="10" t="s">
         <v>35</v>
@@ -1846,7 +1927,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17">
       <c r="A8" s="11">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -1861,20 +1942,20 @@
         <v>24</v>
       </c>
       <c r="E8" s="9">
-        <f>+[5]Main!$H$2</f>
-        <v>51.9</v>
+        <f>+[4]Main!$H$2</f>
+        <v>59.96</v>
       </c>
       <c r="F8" s="12">
-        <f>+[5]Main!$H$4</f>
-        <v>7933.6541597999994</v>
+        <f>+[4]Main!$H$4</f>
+        <v>9165.7399503199995</v>
       </c>
       <c r="G8" s="12">
-        <f>+[5]Main!$H$6-[5]Main!$H$5</f>
+        <f>+[4]Main!$H$6-[4]Main!$H$5</f>
         <v>1242.8240000000001</v>
       </c>
       <c r="H8" s="12">
         <f t="shared" si="0"/>
-        <v>9176.478159799999</v>
+        <v>10408.56395032</v>
       </c>
       <c r="I8" s="8" t="s">
         <v>18</v>
@@ -1890,7 +1971,7 @@
       </c>
       <c r="M8" s="18">
         <f t="shared" si="1"/>
-        <v>0.2566585956416465</v>
+        <v>0.45181598062954009</v>
       </c>
       <c r="O8" s="10" t="s">
         <v>34</v>
@@ -1899,7 +1980,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17">
       <c r="A9" s="11">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -1914,20 +1995,20 @@
         <v>39</v>
       </c>
       <c r="E9" s="9">
-        <f>+[6]Main!$J$2</f>
-        <v>124.3</v>
+        <f>+[5]Main!$J$2</f>
+        <v>111</v>
       </c>
       <c r="F9" s="12">
-        <f>+[6]Main!$J$5*FX!C3</f>
-        <v>303765.83160000003</v>
+        <f>+[5]Main!$J$5*FX!C3</f>
+        <v>271263.13199999998</v>
       </c>
       <c r="G9" s="12">
-        <f>+([6]Main!$J$7-[6]Main!$J$6)*FX!C3</f>
+        <f>+([5]Main!$J$7-[5]Main!$J$6)*FX!C3</f>
         <v>-41909.560000000005</v>
       </c>
       <c r="H9" s="12">
         <f t="shared" si="0"/>
-        <v>261856.27160000004</v>
+        <v>229353.57199999999</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>40</v>
@@ -1943,7 +2024,7 @@
       </c>
       <c r="M9" s="18">
         <f t="shared" si="1"/>
-        <v>-7.30797912005966E-2</v>
+        <v>-0.17225950782997757</v>
       </c>
       <c r="O9" s="16" t="s">
         <v>41</v>
@@ -1952,7 +2033,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17">
       <c r="A10" s="11">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -1967,20 +2048,20 @@
         <v>45</v>
       </c>
       <c r="E10" s="9">
-        <f>+[7]Main!$J$2</f>
-        <v>86.1</v>
+        <f>+[6]Main!$J$2</f>
+        <v>81.2</v>
       </c>
       <c r="F10" s="12">
-        <f>+([7]Main!$J$4)*FX!C2</f>
-        <v>6849.4789392119992</v>
+        <f>+([6]Main!$J$4)*FX!C2</f>
+        <v>6459.6711947039994</v>
       </c>
       <c r="G10" s="12">
-        <f>+([7]Main!$J$6-[7]Main!$J$5)*FX!C2</f>
+        <f>+([6]Main!$J$6-[6]Main!$J$5)*FX!C2</f>
         <v>225.55494000000004</v>
       </c>
       <c r="H10" s="12">
         <f t="shared" si="0"/>
-        <v>7075.0338792119992</v>
+        <v>6685.2261347039994</v>
       </c>
       <c r="I10" s="22" t="s">
         <v>18</v>
@@ -1996,7 +2077,7 @@
       </c>
       <c r="M10" s="18">
         <f t="shared" si="1"/>
-        <v>9.3786635404453644E-3</v>
+        <v>-4.8065650644783076E-2</v>
       </c>
       <c r="O10" s="21" t="s">
         <v>47</v>
@@ -2008,7 +2089,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17">
       <c r="A11" s="11">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -2023,20 +2104,20 @@
         <v>51</v>
       </c>
       <c r="E11" s="9">
-        <f>+[8]Main!$I$2</f>
-        <v>154.19999999999999</v>
+        <f>+[7]Main!$I$2</f>
+        <v>160.9</v>
       </c>
       <c r="F11" s="12">
-        <f>+[8]Main!$I$4*FX!C3</f>
-        <v>28692.524448</v>
+        <f>+[7]Main!$I$4*FX!C3</f>
+        <v>29939.216496000005</v>
       </c>
       <c r="G11" s="12">
-        <f>+([8]Main!$I$6-[8]Main!$I$5)*FX!C3</f>
+        <f>+([7]Main!$I$6-[7]Main!$I$5)*FX!C3</f>
         <v>-1927.1995400000001</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" si="0"/>
-        <v>26765.324907999999</v>
+        <v>28012.016956000003</v>
       </c>
       <c r="I11" s="22" t="s">
         <v>18</v>
@@ -2052,7 +2133,7 @@
       </c>
       <c r="M11" s="18">
         <f>+E11/L11-1</f>
-        <v>-0.39859594383775354</v>
+        <v>-0.37246489859594378</v>
       </c>
       <c r="O11" s="21" t="s">
         <v>52</v>
@@ -2064,7 +2145,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17">
       <c r="A12" s="11">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -2079,20 +2160,20 @@
         <v>24</v>
       </c>
       <c r="E12" s="9">
-        <f>+[9]Main!$H$2</f>
-        <v>115.31</v>
+        <f>+[8]Main!$H$2</f>
+        <v>107.58</v>
       </c>
       <c r="F12" s="12">
-        <f>+[9]Main!$H$4</f>
-        <v>51658.880000000005</v>
+        <f>+[8]Main!$H$4</f>
+        <v>48195.839999999997</v>
       </c>
       <c r="G12" s="12">
-        <f>+([9]Main!$H$6-[9]Main!$H$5)</f>
+        <f>+([8]Main!$H$6-[8]Main!$H$5)</f>
         <v>3827</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="0"/>
-        <v>55485.880000000005</v>
+        <v>52022.84</v>
       </c>
       <c r="I12" s="24" t="s">
         <v>18</v>
@@ -2108,7 +2189,7 @@
       </c>
       <c r="M12" s="18">
         <f>+E12/L12-1</f>
-        <v>0.25105782792665732</v>
+        <v>0.16719105999783013</v>
       </c>
       <c r="O12" s="26" t="s">
         <v>55</v>
@@ -2117,7 +2198,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17">
       <c r="A13" s="11">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -2132,20 +2213,20 @@
         <v>24</v>
       </c>
       <c r="E13" s="9">
-        <f>+[10]Main!$I$2</f>
-        <v>55.6</v>
+        <f>+[9]Main!$I$2</f>
+        <v>50.7</v>
       </c>
       <c r="F13" s="12">
-        <f>+[10]Main!$I$4</f>
-        <v>29904.564917200001</v>
+        <f>+[9]Main!$I$4</f>
+        <v>27269.090670900005</v>
       </c>
       <c r="G13" s="12">
-        <f>+[10]Main!$I$6-[10]Main!$I$5</f>
+        <f>+[9]Main!$I$6-[9]Main!$I$5</f>
         <v>29131</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="0"/>
-        <v>59035.564917199998</v>
+        <v>56400.090670900005</v>
       </c>
       <c r="I13" s="29" t="s">
         <v>60</v>
@@ -2158,7 +2239,7 @@
       </c>
       <c r="M13" s="18">
         <f>+E13/L13-1</f>
-        <v>-0.11039999999999994</v>
+        <v>-0.18879999999999997</v>
       </c>
       <c r="O13" s="30" t="s">
         <v>61</v>
@@ -2170,19 +2251,21 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17">
       <c r="A14" s="11">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="B14" s="7"/>
+      <c r="B14" s="7" t="s">
+        <v>97</v>
+      </c>
       <c r="F14" s="12"/>
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
       <c r="I14" s="8"/>
       <c r="P14" s="14"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17">
       <c r="A15" s="11">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -2191,8 +2274,12 @@
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>
       <c r="I15" s="8"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="M15" s="19">
+        <f>+AVERAGE(M5:M13)</f>
+        <v>-0.14903283946893209</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="11">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -2202,7 +2289,7 @@
       <c r="H16" s="12"/>
       <c r="I16" s="8"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9">
       <c r="A17" s="11">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -2212,7 +2299,7 @@
       <c r="H17" s="12"/>
       <c r="I17" s="8"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9">
       <c r="A18" s="11">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -2222,7 +2309,7 @@
       <c r="H18" s="12"/>
       <c r="I18" s="8"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9">
       <c r="A19" s="11">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -2232,7 +2319,7 @@
       <c r="H19" s="12"/>
       <c r="I19" s="8"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9">
       <c r="A20" s="11">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -2242,7 +2329,7 @@
       <c r="H20" s="12"/>
       <c r="I20" s="8"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9">
       <c r="A21" s="11">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -2252,7 +2339,7 @@
       <c r="H21" s="12"/>
       <c r="I21" s="8"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9">
       <c r="A22" s="11">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -2262,7 +2349,7 @@
       <c r="H22" s="12"/>
       <c r="I22" s="8"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9">
       <c r="A23" s="11">
         <f t="shared" si="2"/>
         <v>19</v>
@@ -2272,7 +2359,7 @@
       <c r="H23" s="12"/>
       <c r="I23" s="8"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9">
       <c r="A24" s="11">
         <f t="shared" si="2"/>
         <v>20</v>
@@ -2282,7 +2369,7 @@
       <c r="H24" s="12"/>
       <c r="I24" s="8"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9">
       <c r="A25" s="11">
         <f t="shared" si="2"/>
         <v>21</v>
@@ -2292,7 +2379,7 @@
       <c r="H25" s="12"/>
       <c r="I25" s="8"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9">
       <c r="A26" s="11">
         <f t="shared" si="2"/>
         <v>22</v>
@@ -2302,7 +2389,7 @@
       <c r="H26" s="12"/>
       <c r="I26" s="8"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9">
       <c r="A27" s="11">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -2312,7 +2399,7 @@
       <c r="H27" s="12"/>
       <c r="I27" s="8"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9">
       <c r="A28" s="11">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -2322,7 +2409,7 @@
       <c r="H28" s="12"/>
       <c r="I28" s="8"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9">
       <c r="A29" s="11">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -2332,7 +2419,7 @@
       <c r="H29" s="12"/>
       <c r="I29" s="8"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9">
       <c r="A30" s="11">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -2342,7 +2429,7 @@
       <c r="H30" s="12"/>
       <c r="I30" s="8"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9">
       <c r="A31" s="11">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -2352,7 +2439,7 @@
       <c r="H31" s="12"/>
       <c r="I31" s="8"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9">
       <c r="A32" s="11">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -2362,7 +2449,7 @@
       <c r="H32" s="12"/>
       <c r="I32" s="8"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9">
       <c r="A33" s="11">
         <f t="shared" si="2"/>
         <v>29</v>
@@ -2372,7 +2459,7 @@
       <c r="H33" s="12"/>
       <c r="I33" s="8"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9">
       <c r="A34" s="11">
         <f t="shared" si="2"/>
         <v>30</v>
@@ -2382,7 +2469,7 @@
       <c r="H34" s="12"/>
       <c r="I34" s="8"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9">
       <c r="A35" s="11">
         <f t="shared" si="2"/>
         <v>31</v>
@@ -2392,7 +2479,7 @@
       <c r="H35" s="12"/>
       <c r="I35" s="8"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9">
       <c r="A36" s="11">
         <f t="shared" si="2"/>
         <v>32</v>
@@ -2402,7 +2489,7 @@
       <c r="H36" s="12"/>
       <c r="I36" s="8"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9">
       <c r="A37" s="11">
         <f t="shared" si="2"/>
         <v>33</v>
@@ -2412,7 +2499,7 @@
       <c r="H37" s="12"/>
       <c r="I37" s="8"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9">
       <c r="A38" s="11">
         <f t="shared" si="2"/>
         <v>34</v>
@@ -2422,7 +2509,7 @@
       <c r="H38" s="12"/>
       <c r="I38" s="8"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9">
       <c r="A39" s="11">
         <f t="shared" si="2"/>
         <v>35</v>
@@ -2432,7 +2519,7 @@
       <c r="H39" s="12"/>
       <c r="I39" s="8"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9">
       <c r="A40" s="11">
         <f t="shared" si="2"/>
         <v>36</v>
@@ -2442,7 +2529,7 @@
       <c r="H40" s="12"/>
       <c r="I40" s="8"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9">
       <c r="A41" s="11">
         <f t="shared" si="2"/>
         <v>37</v>
@@ -2452,7 +2539,7 @@
       <c r="H41" s="12"/>
       <c r="I41" s="8"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9">
       <c r="A42" s="11">
         <f t="shared" si="2"/>
         <v>38</v>
@@ -2462,7 +2549,7 @@
       <c r="H42" s="12"/>
       <c r="I42" s="8"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9">
       <c r="A43" s="11">
         <f t="shared" si="2"/>
         <v>39</v>
@@ -2472,7 +2559,7 @@
       <c r="H43" s="12"/>
       <c r="I43" s="8"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9">
       <c r="A44" s="11">
         <f t="shared" si="2"/>
         <v>40</v>
@@ -2482,7 +2569,7 @@
       <c r="H44" s="12"/>
       <c r="I44" s="8"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9">
       <c r="A45" s="11">
         <f t="shared" si="2"/>
         <v>41</v>
@@ -2492,7 +2579,7 @@
       <c r="H45" s="12"/>
       <c r="I45" s="8"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9">
       <c r="A46" s="11">
         <f t="shared" si="2"/>
         <v>42</v>
@@ -2502,271 +2589,271 @@
       <c r="H46" s="12"/>
       <c r="I46" s="8"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9">
       <c r="A47" s="11"/>
       <c r="F47" s="12"/>
       <c r="G47" s="12"/>
       <c r="H47" s="12"/>
       <c r="I47" s="8"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9">
       <c r="A48" s="11"/>
       <c r="I48" s="8"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9">
       <c r="A49" s="11"/>
       <c r="I49" s="8"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9">
       <c r="A50" s="11"/>
       <c r="I50" s="8"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9">
       <c r="A51" s="11"/>
       <c r="I51" s="8"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9">
       <c r="A52" s="11"/>
       <c r="I52" s="8"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9">
       <c r="A53" s="11"/>
       <c r="I53" s="8"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9">
       <c r="A54" s="11"/>
       <c r="I54" s="8"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9">
       <c r="A55" s="11"/>
       <c r="I55" s="8"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9">
       <c r="A56" s="11"/>
       <c r="I56" s="8"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9">
       <c r="A57" s="11"/>
       <c r="I57" s="8"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9">
       <c r="A58" s="11"/>
       <c r="I58" s="8"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9">
       <c r="A59" s="11"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9">
       <c r="A60" s="11"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9">
       <c r="A61" s="11"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9">
       <c r="A62" s="11"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9">
       <c r="A63" s="11"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9">
       <c r="A64" s="11"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:1">
       <c r="A65" s="11"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:1">
       <c r="A66" s="11"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:1">
       <c r="A67" s="11"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:1">
       <c r="A68" s="11"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:1">
       <c r="A69" s="11"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:1">
       <c r="A70" s="11"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:1">
       <c r="A71" s="11"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:1">
       <c r="A72" s="11"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:1">
       <c r="A73" s="11"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:1">
       <c r="A74" s="11"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:1">
       <c r="A75" s="11"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:1">
       <c r="A76" s="11"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:1">
       <c r="A77" s="11"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:1">
       <c r="A78" s="11"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:1">
       <c r="A79" s="11"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:1">
       <c r="A80" s="11"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:1">
       <c r="A81" s="11"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:1">
       <c r="A82" s="11"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:1">
       <c r="A83" s="11"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:1">
       <c r="A84" s="11"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:1">
       <c r="A85" s="11"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:1">
       <c r="A86" s="11"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:1">
       <c r="A87" s="11"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:1">
       <c r="A88" s="11"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:1">
       <c r="A89" s="11"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:1">
       <c r="A90" s="11"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:1">
       <c r="A91" s="11"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:1">
       <c r="A92" s="11"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:1">
       <c r="A93" s="11"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:1">
       <c r="A94" s="11"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:1">
       <c r="A95" s="11"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:1">
       <c r="A96" s="11"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:1">
       <c r="A97" s="11"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:1">
       <c r="A98" s="11"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:1">
       <c r="A99" s="11"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:1">
       <c r="A100" s="11"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:1">
       <c r="A101" s="11"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:1">
       <c r="A102" s="11"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:1">
       <c r="A103" s="11"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:1">
       <c r="A104" s="11"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:1">
       <c r="A105" s="11"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:1">
       <c r="A106" s="11"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:1">
       <c r="A107" s="11"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:1">
       <c r="A108" s="11"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:1">
       <c r="A109" s="11"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:1">
       <c r="A110" s="11"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:1">
       <c r="A111" s="11"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:1">
       <c r="A112" s="11"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:1">
       <c r="A113" s="11"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:1">
       <c r="A114" s="11"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:1">
       <c r="A115" s="11"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:1">
       <c r="A116" s="11"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:1">
       <c r="A117" s="11"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:1">
       <c r="A118" s="11"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:1">
       <c r="A119" s="11"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:1">
       <c r="A120" s="11"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:1">
       <c r="A121" s="11"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:1">
       <c r="A122" s="11"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:1">
       <c r="A123" s="11"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:1">
       <c r="A124" s="11"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:1">
       <c r="A125" s="11"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:1">
       <c r="A126" s="11"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:1">
       <c r="A127" s="11"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:1">
       <c r="A128" s="11"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:1">
       <c r="A129" s="11"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:1">
       <c r="A130" s="11"/>
     </row>
   </sheetData>
@@ -2786,31 +2873,31 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8328D887-56C2-45D2-86E7-3AD60D640181}">
-  <dimension ref="A1:R14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8328D887-56C2-45D2-86E7-3AD60D640181}">
+  <dimension ref="A1:S14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" s="9" customFormat="1" ht="12.75">
       <c r="A1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="10"/>
-    </row>
-    <row r="2" spans="1:18" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="P1" s="10"/>
+    </row>
+    <row r="2" spans="1:19" s="9" customFormat="1" ht="12.75">
       <c r="A2" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="M2" s="19"/>
-      <c r="O2" s="10"/>
-    </row>
-    <row r="3" spans="1:18" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="O3" s="10"/>
-    </row>
-    <row r="4" spans="1:18" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="N2" s="19"/>
+      <c r="P2" s="10"/>
+    </row>
+    <row r="3" spans="1:19" s="9" customFormat="1" ht="12.75">
+      <c r="P3" s="10"/>
+    </row>
+    <row r="4" spans="1:19" s="9" customFormat="1" ht="12.75">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -2848,23 +2935,26 @@
         <v>62</v>
       </c>
       <c r="M4" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="O4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="P4" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="Q4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="5" t="s">
+      <c r="R4" s="6"/>
+      <c r="S4" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" s="9" customFormat="1" ht="12.75">
       <c r="A5" s="11">
         <v>1</v>
       </c>
@@ -2878,38 +2968,54 @@
         <v>80</v>
       </c>
       <c r="E5" s="9">
-        <f>+[1]Main!$H$3</f>
+        <f>+[10]Main!$H$3</f>
         <v>46.15</v>
       </c>
       <c r="F5" s="12">
-        <f>+[1]Main!$H$5*FX!C11</f>
+        <f>+[10]Main!$H$5*FX!C11</f>
         <v>118088.15849999999</v>
       </c>
       <c r="G5" s="12">
-        <f>+([1]Main!$H$7-[1]Main!$H$6)*FX!C11</f>
+        <f>+([10]Main!$H$7-[10]Main!$H$6)*FX!C11</f>
         <v>36554.31</v>
       </c>
       <c r="H5" s="12">
-        <f>+F5+G5</f>
+        <f t="shared" ref="H5:H11" si="0">+F5+G5</f>
         <v>154642.46849999999</v>
       </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="M5" s="18"/>
-      <c r="N5" s="33">
-        <f>+[1]DCF!$J$4</f>
+      <c r="I5" s="42" t="s">
+        <v>95</v>
+      </c>
+      <c r="J5" s="41">
+        <v>46233</v>
+      </c>
+      <c r="K5" s="13">
+        <v>45509</v>
+      </c>
+      <c r="L5" s="38">
+        <v>32.515099999999997</v>
+      </c>
+      <c r="M5" s="38">
+        <f>+FX!C11*Portfolio!E5</f>
+        <v>53.995499999999993</v>
+      </c>
+      <c r="N5" s="18">
+        <f>+M5/L5-1</f>
+        <v>0.66062844647563734</v>
+      </c>
+      <c r="O5" s="33">
+        <f>+[10]DCF!$J$4</f>
         <v>42.245377497915634</v>
       </c>
-      <c r="O5" s="34">
-        <f>+N5/E5-1</f>
+      <c r="P5" s="34">
+        <f>+O5/E5-1</f>
         <v>-8.4607204812228942E-2</v>
       </c>
-      <c r="P5" s="35" t="s">
+      <c r="Q5" s="35" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" s="9" customFormat="1" ht="12.75">
       <c r="A6" s="11">
         <f>+A5+1</f>
         <v>2</v>
@@ -2936,28 +3042,44 @@
         <v>1060.3471999999999</v>
       </c>
       <c r="H6" s="12">
-        <f>+F6+G6</f>
+        <f t="shared" si="0"/>
         <v>7022.0714153216004</v>
       </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="13"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="33">
+      <c r="I6" s="45" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="44">
+        <v>46240</v>
+      </c>
+      <c r="K6" s="13">
+        <v>45764</v>
+      </c>
+      <c r="L6" s="39">
+        <v>75.48</v>
+      </c>
+      <c r="M6" s="39">
+        <f>+FX!C12*Portfolio!E6</f>
+        <v>119.97920000000001</v>
+      </c>
+      <c r="N6" s="18">
+        <f t="shared" ref="N6:N11" si="1">+M6/L6-1</f>
+        <v>0.58954954954954952</v>
+      </c>
+      <c r="O6" s="33">
         <f>+[11]DCF!$J$4</f>
         <v>149.81272597413047</v>
       </c>
-      <c r="O6" s="34">
-        <f>+N6/E6-1</f>
+      <c r="P6" s="34">
+        <f>+O6/E6-1</f>
         <v>9.8817118777544843E-2</v>
       </c>
-      <c r="P6" s="35" t="s">
+      <c r="Q6" s="35" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" s="9" customFormat="1" ht="12.75">
       <c r="A7" s="11">
-        <f t="shared" ref="A7:A14" si="0">+A6+1</f>
+        <f t="shared" ref="A7:A14" si="2">+A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -2982,28 +3104,44 @@
         <v>58.96</v>
       </c>
       <c r="H7" s="12">
-        <f>+F7+G7</f>
+        <f t="shared" si="0"/>
         <v>43024.554353043997</v>
       </c>
-      <c r="I7" s="17"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="M7" s="18"/>
-      <c r="N7" s="33">
+      <c r="I7" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="13">
+        <v>46231</v>
+      </c>
+      <c r="K7" s="13">
+        <v>45755</v>
+      </c>
+      <c r="L7" s="38">
+        <v>53.947499999999998</v>
+      </c>
+      <c r="M7" s="38">
+        <f>+E7*FX!C12</f>
+        <v>48.707999999999998</v>
+      </c>
+      <c r="N7" s="18">
+        <f t="shared" si="1"/>
+        <v>-9.7122202140970337E-2</v>
+      </c>
+      <c r="O7" s="33">
         <f>+[12]DCF!$J$4</f>
         <v>93.627712741650726</v>
       </c>
-      <c r="O7" s="34">
-        <f>+N7/E7-1</f>
+      <c r="P7" s="34">
+        <f>+O7/E7-1</f>
         <v>0.69155759244174742</v>
       </c>
-      <c r="P7" s="35" t="s">
+      <c r="Q7" s="35" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" s="9" customFormat="1" ht="12.75">
       <c r="A8" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -3028,28 +3166,44 @@
         <v>618.42300000000012</v>
       </c>
       <c r="H8" s="12">
-        <f>+F8+G8</f>
+        <f t="shared" si="0"/>
         <v>1334.9661000000001</v>
       </c>
-      <c r="I8" s="8"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="M8" s="18"/>
-      <c r="N8" s="33">
-        <f ca="1">+[13]DCF!$J$4</f>
+      <c r="I8" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" s="41">
+        <v>46260</v>
+      </c>
+      <c r="K8" s="13">
+        <v>45972</v>
+      </c>
+      <c r="L8" s="38">
+        <v>11.895</v>
+      </c>
+      <c r="M8" s="38">
+        <f>+E8*FX!C13</f>
+        <v>9.1</v>
+      </c>
+      <c r="N8" s="18">
+        <f t="shared" si="1"/>
+        <v>-0.23497267759562845</v>
+      </c>
+      <c r="O8" s="33">
+        <f>+[13]DCF!$J$4</f>
         <v>110.50341825100335</v>
       </c>
-      <c r="O8" s="34">
-        <f ca="1">+N8/E8-1</f>
+      <c r="P8" s="34">
+        <f>+O8/E8-1</f>
         <v>0.57862026072861927</v>
       </c>
-      <c r="P8" s="35" t="s">
+      <c r="Q8" s="35" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" s="9" customFormat="1" ht="12.75">
       <c r="A9" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="B9" s="7" t="s">
@@ -3074,26 +3228,42 @@
         <v>5880</v>
       </c>
       <c r="H9" s="12">
-        <f>+F9+G9</f>
+        <f t="shared" si="0"/>
         <v>17817.625</v>
       </c>
-      <c r="I9" s="15"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="36" t="s">
-        <v>90</v>
+      <c r="I9" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="K9" s="13">
+        <v>45084</v>
+      </c>
+      <c r="L9" s="39">
+        <v>56.9</v>
+      </c>
+      <c r="M9" s="9">
+        <f>+[14]Main!$I$3</f>
+        <v>38.979999999999997</v>
+      </c>
+      <c r="N9" s="18">
+        <f t="shared" si="1"/>
+        <v>-0.3149384885764499</v>
       </c>
       <c r="O9" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="P9" s="35" t="s">
+      <c r="P9" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q9" s="35" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" s="9" customFormat="1" ht="12.75">
       <c r="A10" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
@@ -3118,27 +3288,45 @@
         <v>15.463999999999999</v>
       </c>
       <c r="H10" s="12">
-        <f>+F10+G10</f>
+        <f t="shared" si="0"/>
         <v>706.94269699999995</v>
       </c>
-      <c r="I10" s="22"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="M10" s="18"/>
-      <c r="N10" s="33">
-        <f ca="1">+[15]DCF!$J$3</f>
+      <c r="I10" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="J10" s="41">
+        <v>46186</v>
+      </c>
+      <c r="K10" s="13">
+        <v>45698</v>
+      </c>
+      <c r="L10" s="39">
+        <v>74.495000000000005</v>
+      </c>
+      <c r="M10" s="9">
+        <f>+[15]Main!$H$2</f>
+        <v>101.5</v>
+      </c>
+      <c r="N10" s="18">
+        <f t="shared" si="1"/>
+        <v>0.36250755084233832</v>
+      </c>
+      <c r="O10" s="33">
+        <f>+[15]DCF!$J$3</f>
         <v>97.40723155701005</v>
       </c>
-      <c r="O10" s="34">
-        <f ca="1">+N10/E10-1</f>
+      <c r="P10" s="34">
+        <f>+O10/E10-1</f>
         <v>-4.0322841802856613E-2</v>
       </c>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="20"/>
-    </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="Q10" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="R10" s="20"/>
+    </row>
+    <row r="11" spans="1:19" s="9" customFormat="1" ht="12.75">
       <c r="A11" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="B11" s="7" t="s">
@@ -3163,27 +3351,45 @@
         <v>8249</v>
       </c>
       <c r="H11" s="12">
-        <f>+F11+G11</f>
+        <f t="shared" si="0"/>
         <v>38323.960383600002</v>
       </c>
-      <c r="I11" s="22"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="M11" s="18"/>
-      <c r="N11" s="9">
-        <f ca="1">+[16]DCF!$J$4</f>
+      <c r="I11" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="J11" s="44">
+        <v>46231</v>
+      </c>
+      <c r="K11" s="13">
+        <v>45580</v>
+      </c>
+      <c r="L11" s="39">
+        <v>226.89</v>
+      </c>
+      <c r="M11" s="9">
+        <f>+[16]Main!$H$2</f>
+        <v>245.3</v>
+      </c>
+      <c r="N11" s="18">
+        <f t="shared" si="1"/>
+        <v>8.1140640839173273E-2</v>
+      </c>
+      <c r="O11" s="9">
+        <f>+[16]DCF!$J$4</f>
         <v>339.64481512044307</v>
       </c>
-      <c r="O11" s="34">
-        <f ca="1">+N11/E11-1</f>
+      <c r="P11" s="34">
+        <f>+O11/E11-1</f>
         <v>0.3846099271114678</v>
       </c>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="20"/>
-    </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="Q11" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="R11" s="20"/>
+    </row>
+    <row r="12" spans="1:19" s="9" customFormat="1" ht="12.75">
       <c r="A12" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="B12" s="7"/>
@@ -3195,13 +3401,13 @@
       <c r="I12" s="24"/>
       <c r="J12" s="25"/>
       <c r="K12" s="13"/>
-      <c r="M12" s="18"/>
-      <c r="O12" s="26"/>
-      <c r="P12" s="14"/>
-    </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="N12" s="18"/>
+      <c r="P12" s="26"/>
+      <c r="Q12" s="14"/>
+    </row>
+    <row r="13" spans="1:19" s="9" customFormat="1" ht="12.75">
       <c r="A13" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
@@ -3212,14 +3418,14 @@
       <c r="H13" s="12"/>
       <c r="I13" s="29"/>
       <c r="K13" s="13"/>
-      <c r="M13" s="18"/>
-      <c r="O13" s="30"/>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="28"/>
-    </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="N13" s="18"/>
+      <c r="P13" s="30"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="28"/>
+    </row>
+    <row r="14" spans="1:19" s="9" customFormat="1" ht="12.75">
       <c r="A14" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="B14" s="7"/>
@@ -3227,8 +3433,8 @@
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
       <c r="I14" s="8"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="14"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="14"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3242,19 +3448,20 @@
     <hyperlink ref="B5" r:id="rId7" xr:uid="{91117BF7-0788-4B43-ADAF-699E0F21AEC2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId8"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03B2DF4B-01E2-41F7-B53D-8680A3262A00}">
   <dimension ref="A1:CB334"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.140625" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:80">
       <c r="A1" s="7" t="s">
         <v>3</v>
       </c>
@@ -3338,7 +3545,7 @@
       <c r="CA1" s="31"/>
       <c r="CB1" s="31"/>
     </row>
-    <row r="2" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:80">
       <c r="A2" s="3"/>
       <c r="B2" s="31" t="s">
         <v>2</v>
@@ -3424,7 +3631,7 @@
       <c r="CA2" s="31"/>
       <c r="CB2" s="31"/>
     </row>
-    <row r="3" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:80">
       <c r="A3" s="3"/>
       <c r="B3" s="31" t="s">
         <v>42</v>
@@ -3510,7 +3717,7 @@
       <c r="CA3" s="31"/>
       <c r="CB3" s="31"/>
     </row>
-    <row r="4" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:80">
       <c r="A4" s="3"/>
       <c r="B4" s="31" t="s">
         <v>59</v>
@@ -3596,7 +3803,7 @@
       <c r="CA4" s="31"/>
       <c r="CB4" s="31"/>
     </row>
-    <row r="5" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:80">
       <c r="A5" s="3"/>
       <c r="B5" s="31"/>
       <c r="C5" s="31"/>
@@ -3678,7 +3885,7 @@
       <c r="CA5" s="31"/>
       <c r="CB5" s="31"/>
     </row>
-    <row r="6" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:80">
       <c r="A6" s="1"/>
       <c r="B6" s="31"/>
       <c r="C6" s="31"/>
@@ -3760,7 +3967,7 @@
       <c r="CA6" s="31"/>
       <c r="CB6" s="31"/>
     </row>
-    <row r="7" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:80">
       <c r="B7" s="31"/>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
@@ -3841,7 +4048,7 @@
       <c r="CA7" s="31"/>
       <c r="CB7" s="31"/>
     </row>
-    <row r="8" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:80">
       <c r="B8" s="31"/>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
@@ -3922,7 +4129,7 @@
       <c r="CA8" s="31"/>
       <c r="CB8" s="31"/>
     </row>
-    <row r="9" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:80">
       <c r="B9" s="31"/>
       <c r="C9" s="31"/>
       <c r="D9" s="31"/>
@@ -4003,7 +4210,7 @@
       <c r="CA9" s="31"/>
       <c r="CB9" s="31"/>
     </row>
-    <row r="10" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:80">
       <c r="B10" s="32" t="s">
         <v>81</v>
       </c>
@@ -4086,7 +4293,7 @@
       <c r="CA10" s="31"/>
       <c r="CB10" s="31"/>
     </row>
-    <row r="11" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:80">
       <c r="B11" s="31" t="s">
         <v>82</v>
       </c>
@@ -4171,7 +4378,7 @@
       <c r="CA11" s="31"/>
       <c r="CB11" s="31"/>
     </row>
-    <row r="12" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:80">
       <c r="B12" s="31" t="s">
         <v>83</v>
       </c>
@@ -4256,7 +4463,7 @@
       <c r="CA12" s="31"/>
       <c r="CB12" s="31"/>
     </row>
-    <row r="13" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:80">
       <c r="B13" s="31" t="s">
         <v>84</v>
       </c>
@@ -4341,7 +4548,7 @@
       <c r="CA13" s="31"/>
       <c r="CB13" s="31"/>
     </row>
-    <row r="14" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:80">
       <c r="B14" s="31"/>
       <c r="C14" s="31"/>
       <c r="D14" s="31"/>
@@ -4422,7 +4629,7 @@
       <c r="CA14" s="31"/>
       <c r="CB14" s="31"/>
     </row>
-    <row r="15" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:80">
       <c r="B15" s="31"/>
       <c r="C15" s="31"/>
       <c r="D15" s="31"/>
@@ -4503,7 +4710,7 @@
       <c r="CA15" s="31"/>
       <c r="CB15" s="31"/>
     </row>
-    <row r="16" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:80">
       <c r="B16" s="31"/>
       <c r="C16" s="31"/>
       <c r="D16" s="31"/>
@@ -4584,7 +4791,7 @@
       <c r="CA16" s="31"/>
       <c r="CB16" s="31"/>
     </row>
-    <row r="17" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:80">
       <c r="B17" s="31"/>
       <c r="C17" s="31"/>
       <c r="D17" s="31"/>
@@ -4665,7 +4872,7 @@
       <c r="CA17" s="31"/>
       <c r="CB17" s="31"/>
     </row>
-    <row r="18" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:80">
       <c r="B18" s="31"/>
       <c r="C18" s="31"/>
       <c r="D18" s="31"/>
@@ -4746,7 +4953,7 @@
       <c r="CA18" s="31"/>
       <c r="CB18" s="31"/>
     </row>
-    <row r="19" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:80">
       <c r="B19" s="31"/>
       <c r="C19" s="31"/>
       <c r="D19" s="31"/>
@@ -4827,7 +5034,7 @@
       <c r="CA19" s="31"/>
       <c r="CB19" s="31"/>
     </row>
-    <row r="20" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:80">
       <c r="B20" s="31"/>
       <c r="C20" s="31"/>
       <c r="D20" s="31"/>
@@ -4908,7 +5115,7 @@
       <c r="CA20" s="31"/>
       <c r="CB20" s="31"/>
     </row>
-    <row r="21" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:80">
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
       <c r="D21" s="31"/>
@@ -4989,7 +5196,7 @@
       <c r="CA21" s="31"/>
       <c r="CB21" s="31"/>
     </row>
-    <row r="22" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:80">
       <c r="B22" s="31"/>
       <c r="C22" s="31"/>
       <c r="D22" s="31"/>
@@ -5070,7 +5277,7 @@
       <c r="CA22" s="31"/>
       <c r="CB22" s="31"/>
     </row>
-    <row r="23" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:80">
       <c r="B23" s="31"/>
       <c r="C23" s="31"/>
       <c r="D23" s="31"/>
@@ -5151,7 +5358,7 @@
       <c r="CA23" s="31"/>
       <c r="CB23" s="31"/>
     </row>
-    <row r="24" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:80">
       <c r="B24" s="31"/>
       <c r="C24" s="31"/>
       <c r="D24" s="31"/>
@@ -5232,7 +5439,7 @@
       <c r="CA24" s="31"/>
       <c r="CB24" s="31"/>
     </row>
-    <row r="25" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:80">
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
@@ -5313,7 +5520,7 @@
       <c r="CA25" s="31"/>
       <c r="CB25" s="31"/>
     </row>
-    <row r="26" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:80">
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
@@ -5394,7 +5601,7 @@
       <c r="CA26" s="31"/>
       <c r="CB26" s="31"/>
     </row>
-    <row r="27" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:80">
       <c r="B27" s="31"/>
       <c r="C27" s="31"/>
       <c r="D27" s="31"/>
@@ -5475,7 +5682,7 @@
       <c r="CA27" s="31"/>
       <c r="CB27" s="31"/>
     </row>
-    <row r="28" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:80">
       <c r="B28" s="31"/>
       <c r="C28" s="31"/>
       <c r="D28" s="31"/>
@@ -5556,7 +5763,7 @@
       <c r="CA28" s="31"/>
       <c r="CB28" s="31"/>
     </row>
-    <row r="29" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:80">
       <c r="B29" s="31"/>
       <c r="C29" s="31"/>
       <c r="D29" s="31"/>
@@ -5637,7 +5844,7 @@
       <c r="CA29" s="31"/>
       <c r="CB29" s="31"/>
     </row>
-    <row r="30" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:80">
       <c r="B30" s="31"/>
       <c r="C30" s="31"/>
       <c r="D30" s="31"/>
@@ -5718,7 +5925,7 @@
       <c r="CA30" s="31"/>
       <c r="CB30" s="31"/>
     </row>
-    <row r="31" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:80">
       <c r="B31" s="31"/>
       <c r="C31" s="31"/>
       <c r="D31" s="31"/>
@@ -5799,7 +6006,7 @@
       <c r="CA31" s="31"/>
       <c r="CB31" s="31"/>
     </row>
-    <row r="32" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:80">
       <c r="B32" s="31"/>
       <c r="C32" s="31"/>
       <c r="D32" s="31"/>
@@ -5880,7 +6087,7 @@
       <c r="CA32" s="31"/>
       <c r="CB32" s="31"/>
     </row>
-    <row r="33" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:80">
       <c r="B33" s="31"/>
       <c r="C33" s="31"/>
       <c r="D33" s="31"/>
@@ -5961,7 +6168,7 @@
       <c r="CA33" s="31"/>
       <c r="CB33" s="31"/>
     </row>
-    <row r="34" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:80">
       <c r="B34" s="31"/>
       <c r="C34" s="31"/>
       <c r="D34" s="31"/>
@@ -6042,7 +6249,7 @@
       <c r="CA34" s="31"/>
       <c r="CB34" s="31"/>
     </row>
-    <row r="35" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:80">
       <c r="B35" s="31"/>
       <c r="C35" s="31"/>
       <c r="D35" s="31"/>
@@ -6123,7 +6330,7 @@
       <c r="CA35" s="31"/>
       <c r="CB35" s="31"/>
     </row>
-    <row r="36" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:80">
       <c r="B36" s="31"/>
       <c r="C36" s="31"/>
       <c r="D36" s="31"/>
@@ -6204,7 +6411,7 @@
       <c r="CA36" s="31"/>
       <c r="CB36" s="31"/>
     </row>
-    <row r="37" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:80">
       <c r="B37" s="31"/>
       <c r="C37" s="31"/>
       <c r="D37" s="31"/>
@@ -6285,7 +6492,7 @@
       <c r="CA37" s="31"/>
       <c r="CB37" s="31"/>
     </row>
-    <row r="38" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:80">
       <c r="B38" s="31"/>
       <c r="C38" s="31"/>
       <c r="D38" s="31"/>
@@ -6366,7 +6573,7 @@
       <c r="CA38" s="31"/>
       <c r="CB38" s="31"/>
     </row>
-    <row r="39" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:80">
       <c r="B39" s="31"/>
       <c r="C39" s="31"/>
       <c r="D39" s="31"/>
@@ -6447,7 +6654,7 @@
       <c r="CA39" s="31"/>
       <c r="CB39" s="31"/>
     </row>
-    <row r="40" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:80">
       <c r="B40" s="31"/>
       <c r="C40" s="31"/>
       <c r="D40" s="31"/>
@@ -6528,7 +6735,7 @@
       <c r="CA40" s="31"/>
       <c r="CB40" s="31"/>
     </row>
-    <row r="41" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:80">
       <c r="B41" s="31"/>
       <c r="C41" s="31"/>
       <c r="D41" s="31"/>
@@ -6609,7 +6816,7 @@
       <c r="CA41" s="31"/>
       <c r="CB41" s="31"/>
     </row>
-    <row r="42" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:80">
       <c r="B42" s="31"/>
       <c r="C42" s="31"/>
       <c r="D42" s="31"/>
@@ -6690,7 +6897,7 @@
       <c r="CA42" s="31"/>
       <c r="CB42" s="31"/>
     </row>
-    <row r="43" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:80">
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
       <c r="D43" s="31"/>
@@ -6771,7 +6978,7 @@
       <c r="CA43" s="31"/>
       <c r="CB43" s="31"/>
     </row>
-    <row r="44" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:80">
       <c r="B44" s="31"/>
       <c r="C44" s="31"/>
       <c r="D44" s="31"/>
@@ -6852,7 +7059,7 @@
       <c r="CA44" s="31"/>
       <c r="CB44" s="31"/>
     </row>
-    <row r="45" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:80">
       <c r="B45" s="31"/>
       <c r="C45" s="31"/>
       <c r="D45" s="31"/>
@@ -6933,7 +7140,7 @@
       <c r="CA45" s="31"/>
       <c r="CB45" s="31"/>
     </row>
-    <row r="46" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:80">
       <c r="B46" s="31"/>
       <c r="C46" s="31"/>
       <c r="D46" s="31"/>
@@ -7014,7 +7221,7 @@
       <c r="CA46" s="31"/>
       <c r="CB46" s="31"/>
     </row>
-    <row r="47" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:80">
       <c r="B47" s="31"/>
       <c r="C47" s="31"/>
       <c r="D47" s="31"/>
@@ -7095,7 +7302,7 @@
       <c r="CA47" s="31"/>
       <c r="CB47" s="31"/>
     </row>
-    <row r="48" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:80">
       <c r="B48" s="31"/>
       <c r="C48" s="31"/>
       <c r="D48" s="31"/>
@@ -7176,7 +7383,7 @@
       <c r="CA48" s="31"/>
       <c r="CB48" s="31"/>
     </row>
-    <row r="49" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:80">
       <c r="B49" s="31"/>
       <c r="C49" s="31"/>
       <c r="D49" s="31"/>
@@ -7257,7 +7464,7 @@
       <c r="CA49" s="31"/>
       <c r="CB49" s="31"/>
     </row>
-    <row r="50" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:80">
       <c r="B50" s="31"/>
       <c r="C50" s="31"/>
       <c r="D50" s="31"/>
@@ -7338,7 +7545,7 @@
       <c r="CA50" s="31"/>
       <c r="CB50" s="31"/>
     </row>
-    <row r="51" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:80">
       <c r="B51" s="31"/>
       <c r="C51" s="31"/>
       <c r="D51" s="31"/>
@@ -7419,7 +7626,7 @@
       <c r="CA51" s="31"/>
       <c r="CB51" s="31"/>
     </row>
-    <row r="52" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:80">
       <c r="B52" s="31"/>
       <c r="C52" s="31"/>
       <c r="D52" s="31"/>
@@ -7500,7 +7707,7 @@
       <c r="CA52" s="31"/>
       <c r="CB52" s="31"/>
     </row>
-    <row r="53" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:80">
       <c r="B53" s="31"/>
       <c r="C53" s="31"/>
       <c r="D53" s="31"/>
@@ -7581,7 +7788,7 @@
       <c r="CA53" s="31"/>
       <c r="CB53" s="31"/>
     </row>
-    <row r="54" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:80">
       <c r="B54" s="31"/>
       <c r="C54" s="31"/>
       <c r="D54" s="31"/>
@@ -7662,7 +7869,7 @@
       <c r="CA54" s="31"/>
       <c r="CB54" s="31"/>
     </row>
-    <row r="55" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:80">
       <c r="B55" s="31"/>
       <c r="C55" s="31"/>
       <c r="D55" s="31"/>
@@ -7743,7 +7950,7 @@
       <c r="CA55" s="31"/>
       <c r="CB55" s="31"/>
     </row>
-    <row r="56" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:80">
       <c r="B56" s="31"/>
       <c r="C56" s="31"/>
       <c r="D56" s="31"/>
@@ -7824,7 +8031,7 @@
       <c r="CA56" s="31"/>
       <c r="CB56" s="31"/>
     </row>
-    <row r="57" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:80">
       <c r="B57" s="31"/>
       <c r="C57" s="31"/>
       <c r="D57" s="31"/>
@@ -7905,7 +8112,7 @@
       <c r="CA57" s="31"/>
       <c r="CB57" s="31"/>
     </row>
-    <row r="58" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:80">
       <c r="B58" s="31"/>
       <c r="C58" s="31"/>
       <c r="D58" s="31"/>
@@ -7986,7 +8193,7 @@
       <c r="CA58" s="31"/>
       <c r="CB58" s="31"/>
     </row>
-    <row r="59" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:80">
       <c r="B59" s="31"/>
       <c r="C59" s="31"/>
       <c r="D59" s="31"/>
@@ -8067,7 +8274,7 @@
       <c r="CA59" s="31"/>
       <c r="CB59" s="31"/>
     </row>
-    <row r="60" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:80">
       <c r="B60" s="31"/>
       <c r="C60" s="31"/>
       <c r="D60" s="31"/>
@@ -8148,7 +8355,7 @@
       <c r="CA60" s="31"/>
       <c r="CB60" s="31"/>
     </row>
-    <row r="61" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:80">
       <c r="B61" s="31"/>
       <c r="C61" s="31"/>
       <c r="D61" s="31"/>
@@ -8229,7 +8436,7 @@
       <c r="CA61" s="31"/>
       <c r="CB61" s="31"/>
     </row>
-    <row r="62" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:80">
       <c r="B62" s="31"/>
       <c r="C62" s="31"/>
       <c r="D62" s="31"/>
@@ -8310,7 +8517,7 @@
       <c r="CA62" s="31"/>
       <c r="CB62" s="31"/>
     </row>
-    <row r="63" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:80">
       <c r="B63" s="31"/>
       <c r="C63" s="31"/>
       <c r="D63" s="31"/>
@@ -8391,7 +8598,7 @@
       <c r="CA63" s="31"/>
       <c r="CB63" s="31"/>
     </row>
-    <row r="64" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:80">
       <c r="B64" s="31"/>
       <c r="C64" s="31"/>
       <c r="D64" s="31"/>
@@ -8472,7 +8679,7 @@
       <c r="CA64" s="31"/>
       <c r="CB64" s="31"/>
     </row>
-    <row r="65" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:80">
       <c r="B65" s="31"/>
       <c r="C65" s="31"/>
       <c r="D65" s="31"/>
@@ -8553,7 +8760,7 @@
       <c r="CA65" s="31"/>
       <c r="CB65" s="31"/>
     </row>
-    <row r="66" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:80">
       <c r="B66" s="31"/>
       <c r="C66" s="31"/>
       <c r="D66" s="31"/>
@@ -8634,7 +8841,7 @@
       <c r="CA66" s="31"/>
       <c r="CB66" s="31"/>
     </row>
-    <row r="67" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:80">
       <c r="B67" s="31"/>
       <c r="C67" s="31"/>
       <c r="D67" s="31"/>
@@ -8715,7 +8922,7 @@
       <c r="CA67" s="31"/>
       <c r="CB67" s="31"/>
     </row>
-    <row r="68" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:80">
       <c r="B68" s="31"/>
       <c r="C68" s="31"/>
       <c r="D68" s="31"/>
@@ -8796,7 +9003,7 @@
       <c r="CA68" s="31"/>
       <c r="CB68" s="31"/>
     </row>
-    <row r="69" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:80">
       <c r="B69" s="31"/>
       <c r="C69" s="31"/>
       <c r="D69" s="31"/>
@@ -8877,7 +9084,7 @@
       <c r="CA69" s="31"/>
       <c r="CB69" s="31"/>
     </row>
-    <row r="70" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:80">
       <c r="B70" s="31"/>
       <c r="C70" s="31"/>
       <c r="D70" s="31"/>
@@ -8958,7 +9165,7 @@
       <c r="CA70" s="31"/>
       <c r="CB70" s="31"/>
     </row>
-    <row r="71" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:80">
       <c r="B71" s="31"/>
       <c r="C71" s="31"/>
       <c r="D71" s="31"/>
@@ -9039,7 +9246,7 @@
       <c r="CA71" s="31"/>
       <c r="CB71" s="31"/>
     </row>
-    <row r="72" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:80">
       <c r="B72" s="31"/>
       <c r="C72" s="31"/>
       <c r="D72" s="31"/>
@@ -9120,7 +9327,7 @@
       <c r="CA72" s="31"/>
       <c r="CB72" s="31"/>
     </row>
-    <row r="73" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:80">
       <c r="B73" s="31"/>
       <c r="C73" s="31"/>
       <c r="D73" s="31"/>
@@ -9201,7 +9408,7 @@
       <c r="CA73" s="31"/>
       <c r="CB73" s="31"/>
     </row>
-    <row r="74" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:80">
       <c r="B74" s="31"/>
       <c r="C74" s="31"/>
       <c r="D74" s="31"/>
@@ -9282,7 +9489,7 @@
       <c r="CA74" s="31"/>
       <c r="CB74" s="31"/>
     </row>
-    <row r="75" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:80">
       <c r="B75" s="31"/>
       <c r="C75" s="31"/>
       <c r="D75" s="31"/>
@@ -9363,7 +9570,7 @@
       <c r="CA75" s="31"/>
       <c r="CB75" s="31"/>
     </row>
-    <row r="76" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:80">
       <c r="B76" s="31"/>
       <c r="C76" s="31"/>
       <c r="D76" s="31"/>
@@ -9444,7 +9651,7 @@
       <c r="CA76" s="31"/>
       <c r="CB76" s="31"/>
     </row>
-    <row r="77" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:80">
       <c r="B77" s="31"/>
       <c r="C77" s="31"/>
       <c r="D77" s="31"/>
@@ -9525,7 +9732,7 @@
       <c r="CA77" s="31"/>
       <c r="CB77" s="31"/>
     </row>
-    <row r="78" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:80">
       <c r="B78" s="31"/>
       <c r="C78" s="31"/>
       <c r="D78" s="31"/>
@@ -9606,7 +9813,7 @@
       <c r="CA78" s="31"/>
       <c r="CB78" s="31"/>
     </row>
-    <row r="79" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:80">
       <c r="B79" s="31"/>
       <c r="C79" s="31"/>
       <c r="D79" s="31"/>
@@ -9687,7 +9894,7 @@
       <c r="CA79" s="31"/>
       <c r="CB79" s="31"/>
     </row>
-    <row r="80" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:80">
       <c r="B80" s="31"/>
       <c r="C80" s="31"/>
       <c r="D80" s="31"/>
@@ -9768,7 +9975,7 @@
       <c r="CA80" s="31"/>
       <c r="CB80" s="31"/>
     </row>
-    <row r="81" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:80">
       <c r="B81" s="31"/>
       <c r="C81" s="31"/>
       <c r="D81" s="31"/>
@@ -9849,7 +10056,7 @@
       <c r="CA81" s="31"/>
       <c r="CB81" s="31"/>
     </row>
-    <row r="82" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:80">
       <c r="B82" s="31"/>
       <c r="C82" s="31"/>
       <c r="D82" s="31"/>
@@ -9930,7 +10137,7 @@
       <c r="CA82" s="31"/>
       <c r="CB82" s="31"/>
     </row>
-    <row r="83" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:80">
       <c r="B83" s="31"/>
       <c r="C83" s="31"/>
       <c r="D83" s="31"/>
@@ -10011,7 +10218,7 @@
       <c r="CA83" s="31"/>
       <c r="CB83" s="31"/>
     </row>
-    <row r="84" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:80">
       <c r="B84" s="31"/>
       <c r="C84" s="31"/>
       <c r="D84" s="31"/>
@@ -10092,7 +10299,7 @@
       <c r="CA84" s="31"/>
       <c r="CB84" s="31"/>
     </row>
-    <row r="85" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:80">
       <c r="B85" s="31"/>
       <c r="C85" s="31"/>
       <c r="D85" s="31"/>
@@ -10173,7 +10380,7 @@
       <c r="CA85" s="31"/>
       <c r="CB85" s="31"/>
     </row>
-    <row r="86" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:80">
       <c r="B86" s="31"/>
       <c r="C86" s="31"/>
       <c r="D86" s="31"/>
@@ -10254,7 +10461,7 @@
       <c r="CA86" s="31"/>
       <c r="CB86" s="31"/>
     </row>
-    <row r="87" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:80">
       <c r="B87" s="31"/>
       <c r="C87" s="31"/>
       <c r="D87" s="31"/>
@@ -10335,7 +10542,7 @@
       <c r="CA87" s="31"/>
       <c r="CB87" s="31"/>
     </row>
-    <row r="88" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:80">
       <c r="B88" s="31"/>
       <c r="C88" s="31"/>
       <c r="D88" s="31"/>
@@ -10416,7 +10623,7 @@
       <c r="CA88" s="31"/>
       <c r="CB88" s="31"/>
     </row>
-    <row r="89" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:80">
       <c r="B89" s="31"/>
       <c r="C89" s="31"/>
       <c r="D89" s="31"/>
@@ -10497,7 +10704,7 @@
       <c r="CA89" s="31"/>
       <c r="CB89" s="31"/>
     </row>
-    <row r="90" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:80">
       <c r="B90" s="31"/>
       <c r="C90" s="31"/>
       <c r="D90" s="31"/>
@@ -10578,7 +10785,7 @@
       <c r="CA90" s="31"/>
       <c r="CB90" s="31"/>
     </row>
-    <row r="91" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:80">
       <c r="B91" s="31"/>
       <c r="C91" s="31"/>
       <c r="D91" s="31"/>
@@ -10659,7 +10866,7 @@
       <c r="CA91" s="31"/>
       <c r="CB91" s="31"/>
     </row>
-    <row r="92" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:80">
       <c r="B92" s="31"/>
       <c r="C92" s="31"/>
       <c r="D92" s="31"/>
@@ -10740,7 +10947,7 @@
       <c r="CA92" s="31"/>
       <c r="CB92" s="31"/>
     </row>
-    <row r="93" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:80">
       <c r="B93" s="31"/>
       <c r="C93" s="31"/>
       <c r="D93" s="31"/>
@@ -10821,7 +11028,7 @@
       <c r="CA93" s="31"/>
       <c r="CB93" s="31"/>
     </row>
-    <row r="94" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:80">
       <c r="B94" s="31"/>
       <c r="C94" s="31"/>
       <c r="D94" s="31"/>
@@ -10902,7 +11109,7 @@
       <c r="CA94" s="31"/>
       <c r="CB94" s="31"/>
     </row>
-    <row r="95" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:80">
       <c r="B95" s="31"/>
       <c r="C95" s="31"/>
       <c r="D95" s="31"/>
@@ -10983,7 +11190,7 @@
       <c r="CA95" s="31"/>
       <c r="CB95" s="31"/>
     </row>
-    <row r="96" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:80">
       <c r="B96" s="31"/>
       <c r="C96" s="31"/>
       <c r="D96" s="31"/>
@@ -11064,7 +11271,7 @@
       <c r="CA96" s="31"/>
       <c r="CB96" s="31"/>
     </row>
-    <row r="97" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:80">
       <c r="B97" s="31"/>
       <c r="C97" s="31"/>
       <c r="D97" s="31"/>
@@ -11145,7 +11352,7 @@
       <c r="CA97" s="31"/>
       <c r="CB97" s="31"/>
     </row>
-    <row r="98" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:80">
       <c r="B98" s="31"/>
       <c r="C98" s="31"/>
       <c r="D98" s="31"/>
@@ -11226,7 +11433,7 @@
       <c r="CA98" s="31"/>
       <c r="CB98" s="31"/>
     </row>
-    <row r="99" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:80">
       <c r="B99" s="31"/>
       <c r="C99" s="31"/>
       <c r="D99" s="31"/>
@@ -11307,7 +11514,7 @@
       <c r="CA99" s="31"/>
       <c r="CB99" s="31"/>
     </row>
-    <row r="100" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:80">
       <c r="B100" s="31"/>
       <c r="C100" s="31"/>
       <c r="D100" s="31"/>
@@ -11388,7 +11595,7 @@
       <c r="CA100" s="31"/>
       <c r="CB100" s="31"/>
     </row>
-    <row r="101" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:80">
       <c r="B101" s="31"/>
       <c r="C101" s="31"/>
       <c r="D101" s="31"/>
@@ -11469,7 +11676,7 @@
       <c r="CA101" s="31"/>
       <c r="CB101" s="31"/>
     </row>
-    <row r="102" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:80">
       <c r="B102" s="31"/>
       <c r="C102" s="31"/>
       <c r="D102" s="31"/>
@@ -11550,7 +11757,7 @@
       <c r="CA102" s="31"/>
       <c r="CB102" s="31"/>
     </row>
-    <row r="103" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:80">
       <c r="B103" s="31"/>
       <c r="C103" s="31"/>
       <c r="D103" s="31"/>
@@ -11631,7 +11838,7 @@
       <c r="CA103" s="31"/>
       <c r="CB103" s="31"/>
     </row>
-    <row r="104" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:80">
       <c r="B104" s="31"/>
       <c r="C104" s="31"/>
       <c r="D104" s="31"/>
@@ -11712,7 +11919,7 @@
       <c r="CA104" s="31"/>
       <c r="CB104" s="31"/>
     </row>
-    <row r="105" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:80">
       <c r="B105" s="31"/>
       <c r="C105" s="31"/>
       <c r="D105" s="31"/>
@@ -11793,7 +12000,7 @@
       <c r="CA105" s="31"/>
       <c r="CB105" s="31"/>
     </row>
-    <row r="106" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:80">
       <c r="B106" s="31"/>
       <c r="C106" s="31"/>
       <c r="D106" s="31"/>
@@ -11874,7 +12081,7 @@
       <c r="CA106" s="31"/>
       <c r="CB106" s="31"/>
     </row>
-    <row r="107" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:80">
       <c r="B107" s="31"/>
       <c r="C107" s="31"/>
       <c r="D107" s="31"/>
@@ -11955,7 +12162,7 @@
       <c r="CA107" s="31"/>
       <c r="CB107" s="31"/>
     </row>
-    <row r="108" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:80">
       <c r="B108" s="31"/>
       <c r="C108" s="31"/>
       <c r="D108" s="31"/>
@@ -12036,7 +12243,7 @@
       <c r="CA108" s="31"/>
       <c r="CB108" s="31"/>
     </row>
-    <row r="109" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:80">
       <c r="B109" s="31"/>
       <c r="C109" s="31"/>
       <c r="D109" s="31"/>
@@ -12117,7 +12324,7 @@
       <c r="CA109" s="31"/>
       <c r="CB109" s="31"/>
     </row>
-    <row r="110" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:80">
       <c r="B110" s="31"/>
       <c r="C110" s="31"/>
       <c r="D110" s="31"/>
@@ -12198,7 +12405,7 @@
       <c r="CA110" s="31"/>
       <c r="CB110" s="31"/>
     </row>
-    <row r="111" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:80">
       <c r="B111" s="31"/>
       <c r="C111" s="31"/>
       <c r="D111" s="31"/>
@@ -12279,7 +12486,7 @@
       <c r="CA111" s="31"/>
       <c r="CB111" s="31"/>
     </row>
-    <row r="112" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:80">
       <c r="B112" s="31"/>
       <c r="C112" s="31"/>
       <c r="D112" s="31"/>
@@ -12360,7 +12567,7 @@
       <c r="CA112" s="31"/>
       <c r="CB112" s="31"/>
     </row>
-    <row r="113" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:80">
       <c r="B113" s="31"/>
       <c r="C113" s="31"/>
       <c r="D113" s="31"/>
@@ -12441,7 +12648,7 @@
       <c r="CA113" s="31"/>
       <c r="CB113" s="31"/>
     </row>
-    <row r="114" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:80">
       <c r="B114" s="31"/>
       <c r="C114" s="31"/>
       <c r="D114" s="31"/>
@@ -12522,7 +12729,7 @@
       <c r="CA114" s="31"/>
       <c r="CB114" s="31"/>
     </row>
-    <row r="115" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:80">
       <c r="B115" s="31"/>
       <c r="C115" s="31"/>
       <c r="D115" s="31"/>
@@ -12603,7 +12810,7 @@
       <c r="CA115" s="31"/>
       <c r="CB115" s="31"/>
     </row>
-    <row r="116" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:80">
       <c r="B116" s="31"/>
       <c r="C116" s="31"/>
       <c r="D116" s="31"/>
@@ -12684,7 +12891,7 @@
       <c r="CA116" s="31"/>
       <c r="CB116" s="31"/>
     </row>
-    <row r="117" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:80">
       <c r="B117" s="31"/>
       <c r="C117" s="31"/>
       <c r="D117" s="31"/>
@@ -12765,7 +12972,7 @@
       <c r="CA117" s="31"/>
       <c r="CB117" s="31"/>
     </row>
-    <row r="118" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:80">
       <c r="B118" s="31"/>
       <c r="C118" s="31"/>
       <c r="D118" s="31"/>
@@ -12846,7 +13053,7 @@
       <c r="CA118" s="31"/>
       <c r="CB118" s="31"/>
     </row>
-    <row r="119" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:80">
       <c r="B119" s="31"/>
       <c r="C119" s="31"/>
       <c r="D119" s="31"/>
@@ -12927,7 +13134,7 @@
       <c r="CA119" s="31"/>
       <c r="CB119" s="31"/>
     </row>
-    <row r="120" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:80">
       <c r="B120" s="31"/>
       <c r="C120" s="31"/>
       <c r="D120" s="31"/>
@@ -13008,7 +13215,7 @@
       <c r="CA120" s="31"/>
       <c r="CB120" s="31"/>
     </row>
-    <row r="121" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:80">
       <c r="B121" s="31"/>
       <c r="C121" s="31"/>
       <c r="D121" s="31"/>
@@ -13089,7 +13296,7 @@
       <c r="CA121" s="31"/>
       <c r="CB121" s="31"/>
     </row>
-    <row r="122" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:80">
       <c r="B122" s="31"/>
       <c r="C122" s="31"/>
       <c r="D122" s="31"/>
@@ -13170,7 +13377,7 @@
       <c r="CA122" s="31"/>
       <c r="CB122" s="31"/>
     </row>
-    <row r="123" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:80">
       <c r="B123" s="31"/>
       <c r="C123" s="31"/>
       <c r="D123" s="31"/>
@@ -13251,7 +13458,7 @@
       <c r="CA123" s="31"/>
       <c r="CB123" s="31"/>
     </row>
-    <row r="124" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:80">
       <c r="B124" s="31"/>
       <c r="C124" s="31"/>
       <c r="D124" s="31"/>
@@ -13332,7 +13539,7 @@
       <c r="CA124" s="31"/>
       <c r="CB124" s="31"/>
     </row>
-    <row r="125" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:80">
       <c r="B125" s="31"/>
       <c r="C125" s="31"/>
       <c r="D125" s="31"/>
@@ -13413,7 +13620,7 @@
       <c r="CA125" s="31"/>
       <c r="CB125" s="31"/>
     </row>
-    <row r="126" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:80">
       <c r="B126" s="31"/>
       <c r="C126" s="31"/>
       <c r="D126" s="31"/>
@@ -13494,7 +13701,7 @@
       <c r="CA126" s="31"/>
       <c r="CB126" s="31"/>
     </row>
-    <row r="127" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:80">
       <c r="B127" s="31"/>
       <c r="C127" s="31"/>
       <c r="D127" s="31"/>
@@ -13575,7 +13782,7 @@
       <c r="CA127" s="31"/>
       <c r="CB127" s="31"/>
     </row>
-    <row r="128" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:80">
       <c r="B128" s="31"/>
       <c r="C128" s="31"/>
       <c r="D128" s="31"/>
@@ -13656,7 +13863,7 @@
       <c r="CA128" s="31"/>
       <c r="CB128" s="31"/>
     </row>
-    <row r="129" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:80">
       <c r="B129" s="31"/>
       <c r="C129" s="31"/>
       <c r="D129" s="31"/>
@@ -13737,7 +13944,7 @@
       <c r="CA129" s="31"/>
       <c r="CB129" s="31"/>
     </row>
-    <row r="130" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:80">
       <c r="B130" s="31"/>
       <c r="C130" s="31"/>
       <c r="D130" s="31"/>
@@ -13818,7 +14025,7 @@
       <c r="CA130" s="31"/>
       <c r="CB130" s="31"/>
     </row>
-    <row r="131" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:80">
       <c r="B131" s="31"/>
       <c r="C131" s="31"/>
       <c r="D131" s="31"/>
@@ -13899,7 +14106,7 @@
       <c r="CA131" s="31"/>
       <c r="CB131" s="31"/>
     </row>
-    <row r="132" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:80">
       <c r="B132" s="31"/>
       <c r="C132" s="31"/>
       <c r="D132" s="31"/>
@@ -13980,7 +14187,7 @@
       <c r="CA132" s="31"/>
       <c r="CB132" s="31"/>
     </row>
-    <row r="133" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:80">
       <c r="B133" s="31"/>
       <c r="C133" s="31"/>
       <c r="D133" s="31"/>
@@ -14061,7 +14268,7 @@
       <c r="CA133" s="31"/>
       <c r="CB133" s="31"/>
     </row>
-    <row r="134" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:80">
       <c r="B134" s="31"/>
       <c r="C134" s="31"/>
       <c r="D134" s="31"/>
@@ -14142,7 +14349,7 @@
       <c r="CA134" s="31"/>
       <c r="CB134" s="31"/>
     </row>
-    <row r="135" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:80">
       <c r="B135" s="31"/>
       <c r="C135" s="31"/>
       <c r="D135" s="31"/>
@@ -14223,7 +14430,7 @@
       <c r="CA135" s="31"/>
       <c r="CB135" s="31"/>
     </row>
-    <row r="136" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:80">
       <c r="B136" s="31"/>
       <c r="C136" s="31"/>
       <c r="D136" s="31"/>
@@ -14304,7 +14511,7 @@
       <c r="CA136" s="31"/>
       <c r="CB136" s="31"/>
     </row>
-    <row r="137" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:80">
       <c r="B137" s="31"/>
       <c r="C137" s="31"/>
       <c r="D137" s="31"/>
@@ -14385,7 +14592,7 @@
       <c r="CA137" s="31"/>
       <c r="CB137" s="31"/>
     </row>
-    <row r="138" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:80">
       <c r="B138" s="31"/>
       <c r="C138" s="31"/>
       <c r="D138" s="31"/>
@@ -14466,7 +14673,7 @@
       <c r="CA138" s="31"/>
       <c r="CB138" s="31"/>
     </row>
-    <row r="139" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:80">
       <c r="B139" s="31"/>
       <c r="C139" s="31"/>
       <c r="D139" s="31"/>
@@ -14547,7 +14754,7 @@
       <c r="CA139" s="31"/>
       <c r="CB139" s="31"/>
     </row>
-    <row r="140" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:80">
       <c r="B140" s="31"/>
       <c r="C140" s="31"/>
       <c r="D140" s="31"/>
@@ -14628,7 +14835,7 @@
       <c r="CA140" s="31"/>
       <c r="CB140" s="31"/>
     </row>
-    <row r="141" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:80">
       <c r="B141" s="31"/>
       <c r="C141" s="31"/>
       <c r="D141" s="31"/>
@@ -14709,7 +14916,7 @@
       <c r="CA141" s="31"/>
       <c r="CB141" s="31"/>
     </row>
-    <row r="142" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:80">
       <c r="B142" s="31"/>
       <c r="C142" s="31"/>
       <c r="D142" s="31"/>
@@ -14790,7 +14997,7 @@
       <c r="CA142" s="31"/>
       <c r="CB142" s="31"/>
     </row>
-    <row r="143" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:80">
       <c r="B143" s="31"/>
       <c r="C143" s="31"/>
       <c r="D143" s="31"/>
@@ -14871,7 +15078,7 @@
       <c r="CA143" s="31"/>
       <c r="CB143" s="31"/>
     </row>
-    <row r="144" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:80">
       <c r="B144" s="31"/>
       <c r="C144" s="31"/>
       <c r="D144" s="31"/>
@@ -14952,7 +15159,7 @@
       <c r="CA144" s="31"/>
       <c r="CB144" s="31"/>
     </row>
-    <row r="145" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:80">
       <c r="B145" s="31"/>
       <c r="C145" s="31"/>
       <c r="D145" s="31"/>
@@ -15033,7 +15240,7 @@
       <c r="CA145" s="31"/>
       <c r="CB145" s="31"/>
     </row>
-    <row r="146" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:80">
       <c r="B146" s="31"/>
       <c r="C146" s="31"/>
       <c r="D146" s="31"/>
@@ -15114,7 +15321,7 @@
       <c r="CA146" s="31"/>
       <c r="CB146" s="31"/>
     </row>
-    <row r="147" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:80">
       <c r="B147" s="31"/>
       <c r="C147" s="31"/>
       <c r="D147" s="31"/>
@@ -15195,7 +15402,7 @@
       <c r="CA147" s="31"/>
       <c r="CB147" s="31"/>
     </row>
-    <row r="148" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:80">
       <c r="B148" s="31"/>
       <c r="C148" s="31"/>
       <c r="D148" s="31"/>
@@ -15276,7 +15483,7 @@
       <c r="CA148" s="31"/>
       <c r="CB148" s="31"/>
     </row>
-    <row r="149" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:80">
       <c r="B149" s="31"/>
       <c r="C149" s="31"/>
       <c r="D149" s="31"/>
@@ -15357,7 +15564,7 @@
       <c r="CA149" s="31"/>
       <c r="CB149" s="31"/>
     </row>
-    <row r="150" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:80">
       <c r="B150" s="31"/>
       <c r="C150" s="31"/>
       <c r="D150" s="31"/>
@@ -15438,7 +15645,7 @@
       <c r="CA150" s="31"/>
       <c r="CB150" s="31"/>
     </row>
-    <row r="151" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:80">
       <c r="B151" s="31"/>
       <c r="C151" s="31"/>
       <c r="D151" s="31"/>
@@ -15519,7 +15726,7 @@
       <c r="CA151" s="31"/>
       <c r="CB151" s="31"/>
     </row>
-    <row r="152" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:80">
       <c r="B152" s="31"/>
       <c r="C152" s="31"/>
       <c r="D152" s="31"/>
@@ -15600,7 +15807,7 @@
       <c r="CA152" s="31"/>
       <c r="CB152" s="31"/>
     </row>
-    <row r="153" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:80">
       <c r="B153" s="31"/>
       <c r="C153" s="31"/>
       <c r="D153" s="31"/>
@@ -15681,7 +15888,7 @@
       <c r="CA153" s="31"/>
       <c r="CB153" s="31"/>
     </row>
-    <row r="154" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:80">
       <c r="B154" s="31"/>
       <c r="C154" s="31"/>
       <c r="D154" s="31"/>
@@ -15762,7 +15969,7 @@
       <c r="CA154" s="31"/>
       <c r="CB154" s="31"/>
     </row>
-    <row r="155" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:80">
       <c r="B155" s="31"/>
       <c r="C155" s="31"/>
       <c r="D155" s="31"/>
@@ -15843,7 +16050,7 @@
       <c r="CA155" s="31"/>
       <c r="CB155" s="31"/>
     </row>
-    <row r="156" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:80">
       <c r="B156" s="31"/>
       <c r="C156" s="31"/>
       <c r="D156" s="31"/>
@@ -15924,7 +16131,7 @@
       <c r="CA156" s="31"/>
       <c r="CB156" s="31"/>
     </row>
-    <row r="157" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:80">
       <c r="B157" s="31"/>
       <c r="C157" s="31"/>
       <c r="D157" s="31"/>
@@ -16005,7 +16212,7 @@
       <c r="CA157" s="31"/>
       <c r="CB157" s="31"/>
     </row>
-    <row r="158" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:80">
       <c r="B158" s="31"/>
       <c r="C158" s="31"/>
       <c r="D158" s="31"/>
@@ -16086,7 +16293,7 @@
       <c r="CA158" s="31"/>
       <c r="CB158" s="31"/>
     </row>
-    <row r="159" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:80">
       <c r="B159" s="31"/>
       <c r="C159" s="31"/>
       <c r="D159" s="31"/>
@@ -16167,7 +16374,7 @@
       <c r="CA159" s="31"/>
       <c r="CB159" s="31"/>
     </row>
-    <row r="160" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:80">
       <c r="B160" s="31"/>
       <c r="C160" s="31"/>
       <c r="D160" s="31"/>
@@ -16248,7 +16455,7 @@
       <c r="CA160" s="31"/>
       <c r="CB160" s="31"/>
     </row>
-    <row r="161" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:80">
       <c r="B161" s="31"/>
       <c r="C161" s="31"/>
       <c r="D161" s="31"/>
@@ -16329,7 +16536,7 @@
       <c r="CA161" s="31"/>
       <c r="CB161" s="31"/>
     </row>
-    <row r="162" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:80">
       <c r="B162" s="31"/>
       <c r="C162" s="31"/>
       <c r="D162" s="31"/>
@@ -16410,7 +16617,7 @@
       <c r="CA162" s="31"/>
       <c r="CB162" s="31"/>
     </row>
-    <row r="163" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:80">
       <c r="B163" s="31"/>
       <c r="C163" s="31"/>
       <c r="D163" s="31"/>
@@ -16491,7 +16698,7 @@
       <c r="CA163" s="31"/>
       <c r="CB163" s="31"/>
     </row>
-    <row r="164" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:80">
       <c r="B164" s="31"/>
       <c r="C164" s="31"/>
       <c r="D164" s="31"/>
@@ -16572,7 +16779,7 @@
       <c r="CA164" s="31"/>
       <c r="CB164" s="31"/>
     </row>
-    <row r="165" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:80">
       <c r="B165" s="31"/>
       <c r="C165" s="31"/>
       <c r="D165" s="31"/>
@@ -16653,7 +16860,7 @@
       <c r="CA165" s="31"/>
       <c r="CB165" s="31"/>
     </row>
-    <row r="166" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:80">
       <c r="B166" s="31"/>
       <c r="C166" s="31"/>
       <c r="D166" s="31"/>
@@ -16734,7 +16941,7 @@
       <c r="CA166" s="31"/>
       <c r="CB166" s="31"/>
     </row>
-    <row r="167" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:80">
       <c r="B167" s="31"/>
       <c r="C167" s="31"/>
       <c r="D167" s="31"/>
@@ -16815,7 +17022,7 @@
       <c r="CA167" s="31"/>
       <c r="CB167" s="31"/>
     </row>
-    <row r="168" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:80">
       <c r="B168" s="31"/>
       <c r="C168" s="31"/>
       <c r="D168" s="31"/>
@@ -16896,7 +17103,7 @@
       <c r="CA168" s="31"/>
       <c r="CB168" s="31"/>
     </row>
-    <row r="169" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:80">
       <c r="B169" s="31"/>
       <c r="C169" s="31"/>
       <c r="D169" s="31"/>
@@ -16977,7 +17184,7 @@
       <c r="CA169" s="31"/>
       <c r="CB169" s="31"/>
     </row>
-    <row r="170" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:80">
       <c r="B170" s="31"/>
       <c r="C170" s="31"/>
       <c r="D170" s="31"/>
@@ -17058,7 +17265,7 @@
       <c r="CA170" s="31"/>
       <c r="CB170" s="31"/>
     </row>
-    <row r="171" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:80">
       <c r="B171" s="31"/>
       <c r="C171" s="31"/>
       <c r="D171" s="31"/>
@@ -17139,7 +17346,7 @@
       <c r="CA171" s="31"/>
       <c r="CB171" s="31"/>
     </row>
-    <row r="172" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:80">
       <c r="B172" s="31"/>
       <c r="C172" s="31"/>
       <c r="D172" s="31"/>
@@ -17220,7 +17427,7 @@
       <c r="CA172" s="31"/>
       <c r="CB172" s="31"/>
     </row>
-    <row r="173" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:80">
       <c r="B173" s="31"/>
       <c r="C173" s="31"/>
       <c r="D173" s="31"/>
@@ -17301,7 +17508,7 @@
       <c r="CA173" s="31"/>
       <c r="CB173" s="31"/>
     </row>
-    <row r="174" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:80">
       <c r="B174" s="31"/>
       <c r="C174" s="31"/>
       <c r="D174" s="31"/>
@@ -17382,7 +17589,7 @@
       <c r="CA174" s="31"/>
       <c r="CB174" s="31"/>
     </row>
-    <row r="175" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:80">
       <c r="B175" s="31"/>
       <c r="C175" s="31"/>
       <c r="D175" s="31"/>
@@ -17463,7 +17670,7 @@
       <c r="CA175" s="31"/>
       <c r="CB175" s="31"/>
     </row>
-    <row r="176" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:80">
       <c r="B176" s="31"/>
       <c r="C176" s="31"/>
       <c r="D176" s="31"/>
@@ -17544,7 +17751,7 @@
       <c r="CA176" s="31"/>
       <c r="CB176" s="31"/>
     </row>
-    <row r="177" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:80">
       <c r="B177" s="31"/>
       <c r="C177" s="31"/>
       <c r="D177" s="31"/>
@@ -17625,7 +17832,7 @@
       <c r="CA177" s="31"/>
       <c r="CB177" s="31"/>
     </row>
-    <row r="178" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:80">
       <c r="B178" s="31"/>
       <c r="C178" s="31"/>
       <c r="D178" s="31"/>
@@ -17706,7 +17913,7 @@
       <c r="CA178" s="31"/>
       <c r="CB178" s="31"/>
     </row>
-    <row r="179" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:80">
       <c r="B179" s="31"/>
       <c r="C179" s="31"/>
       <c r="D179" s="31"/>
@@ -17787,7 +17994,7 @@
       <c r="CA179" s="31"/>
       <c r="CB179" s="31"/>
     </row>
-    <row r="180" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:80">
       <c r="B180" s="31"/>
       <c r="C180" s="31"/>
       <c r="D180" s="31"/>
@@ -17868,7 +18075,7 @@
       <c r="CA180" s="31"/>
       <c r="CB180" s="31"/>
     </row>
-    <row r="181" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:80">
       <c r="B181" s="31"/>
       <c r="C181" s="31"/>
       <c r="D181" s="31"/>
@@ -17949,7 +18156,7 @@
       <c r="CA181" s="31"/>
       <c r="CB181" s="31"/>
     </row>
-    <row r="182" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:80">
       <c r="B182" s="31"/>
       <c r="C182" s="31"/>
       <c r="D182" s="31"/>
@@ -18030,7 +18237,7 @@
       <c r="CA182" s="31"/>
       <c r="CB182" s="31"/>
     </row>
-    <row r="183" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:80">
       <c r="B183" s="31"/>
       <c r="C183" s="31"/>
       <c r="D183" s="31"/>
@@ -18111,7 +18318,7 @@
       <c r="CA183" s="31"/>
       <c r="CB183" s="31"/>
     </row>
-    <row r="184" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:80">
       <c r="B184" s="31"/>
       <c r="C184" s="31"/>
       <c r="D184" s="31"/>
@@ -18192,7 +18399,7 @@
       <c r="CA184" s="31"/>
       <c r="CB184" s="31"/>
     </row>
-    <row r="185" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:80">
       <c r="B185" s="31"/>
       <c r="C185" s="31"/>
       <c r="D185" s="31"/>
@@ -18273,7 +18480,7 @@
       <c r="CA185" s="31"/>
       <c r="CB185" s="31"/>
     </row>
-    <row r="186" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:80">
       <c r="B186" s="31"/>
       <c r="C186" s="31"/>
       <c r="D186" s="31"/>
@@ -18354,7 +18561,7 @@
       <c r="CA186" s="31"/>
       <c r="CB186" s="31"/>
     </row>
-    <row r="187" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:80">
       <c r="B187" s="31"/>
       <c r="C187" s="31"/>
       <c r="D187" s="31"/>
@@ -18435,7 +18642,7 @@
       <c r="CA187" s="31"/>
       <c r="CB187" s="31"/>
     </row>
-    <row r="188" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:80">
       <c r="B188" s="31"/>
       <c r="C188" s="31"/>
       <c r="D188" s="31"/>
@@ -18516,7 +18723,7 @@
       <c r="CA188" s="31"/>
       <c r="CB188" s="31"/>
     </row>
-    <row r="189" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:80">
       <c r="B189" s="31"/>
       <c r="C189" s="31"/>
       <c r="D189" s="31"/>
@@ -18597,7 +18804,7 @@
       <c r="CA189" s="31"/>
       <c r="CB189" s="31"/>
     </row>
-    <row r="190" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:80">
       <c r="B190" s="31"/>
       <c r="C190" s="31"/>
       <c r="D190" s="31"/>
@@ -18678,7 +18885,7 @@
       <c r="CA190" s="31"/>
       <c r="CB190" s="31"/>
     </row>
-    <row r="191" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:80">
       <c r="B191" s="31"/>
       <c r="C191" s="31"/>
       <c r="D191" s="31"/>
@@ -18759,7 +18966,7 @@
       <c r="CA191" s="31"/>
       <c r="CB191" s="31"/>
     </row>
-    <row r="192" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:80">
       <c r="B192" s="31"/>
       <c r="C192" s="31"/>
       <c r="D192" s="31"/>
@@ -18840,7 +19047,7 @@
       <c r="CA192" s="31"/>
       <c r="CB192" s="31"/>
     </row>
-    <row r="193" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:80">
       <c r="B193" s="31"/>
       <c r="C193" s="31"/>
       <c r="D193" s="31"/>
@@ -18921,7 +19128,7 @@
       <c r="CA193" s="31"/>
       <c r="CB193" s="31"/>
     </row>
-    <row r="194" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:80">
       <c r="B194" s="31"/>
       <c r="C194" s="31"/>
       <c r="D194" s="31"/>
@@ -19002,7 +19209,7 @@
       <c r="CA194" s="31"/>
       <c r="CB194" s="31"/>
     </row>
-    <row r="195" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:80">
       <c r="B195" s="31"/>
       <c r="C195" s="31"/>
       <c r="D195" s="31"/>
@@ -19083,7 +19290,7 @@
       <c r="CA195" s="31"/>
       <c r="CB195" s="31"/>
     </row>
-    <row r="196" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:80">
       <c r="B196" s="31"/>
       <c r="C196" s="31"/>
       <c r="D196" s="31"/>
@@ -19164,7 +19371,7 @@
       <c r="CA196" s="31"/>
       <c r="CB196" s="31"/>
     </row>
-    <row r="197" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:80">
       <c r="B197" s="31"/>
       <c r="C197" s="31"/>
       <c r="D197" s="31"/>
@@ -19245,7 +19452,7 @@
       <c r="CA197" s="31"/>
       <c r="CB197" s="31"/>
     </row>
-    <row r="198" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:80">
       <c r="B198" s="31"/>
       <c r="C198" s="31"/>
       <c r="D198" s="31"/>
@@ -19326,7 +19533,7 @@
       <c r="CA198" s="31"/>
       <c r="CB198" s="31"/>
     </row>
-    <row r="199" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:80">
       <c r="B199" s="31"/>
       <c r="C199" s="31"/>
       <c r="D199" s="31"/>
@@ -19407,7 +19614,7 @@
       <c r="CA199" s="31"/>
       <c r="CB199" s="31"/>
     </row>
-    <row r="200" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:80">
       <c r="B200" s="31"/>
       <c r="C200" s="31"/>
       <c r="D200" s="31"/>
@@ -19488,7 +19695,7 @@
       <c r="CA200" s="31"/>
       <c r="CB200" s="31"/>
     </row>
-    <row r="201" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:80">
       <c r="B201" s="31"/>
       <c r="C201" s="31"/>
       <c r="D201" s="31"/>
@@ -19569,7 +19776,7 @@
       <c r="CA201" s="31"/>
       <c r="CB201" s="31"/>
     </row>
-    <row r="202" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:80">
       <c r="B202" s="31"/>
       <c r="C202" s="31"/>
       <c r="D202" s="31"/>
@@ -19650,7 +19857,7 @@
       <c r="CA202" s="31"/>
       <c r="CB202" s="31"/>
     </row>
-    <row r="203" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:80">
       <c r="B203" s="31"/>
       <c r="C203" s="31"/>
       <c r="D203" s="31"/>
@@ -19731,7 +19938,7 @@
       <c r="CA203" s="31"/>
       <c r="CB203" s="31"/>
     </row>
-    <row r="204" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:80">
       <c r="B204" s="31"/>
       <c r="C204" s="31"/>
       <c r="D204" s="31"/>
@@ -19812,7 +20019,7 @@
       <c r="CA204" s="31"/>
       <c r="CB204" s="31"/>
     </row>
-    <row r="205" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:80">
       <c r="B205" s="31"/>
       <c r="C205" s="31"/>
       <c r="D205" s="31"/>
@@ -19893,7 +20100,7 @@
       <c r="CA205" s="31"/>
       <c r="CB205" s="31"/>
     </row>
-    <row r="206" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:80">
       <c r="B206" s="31"/>
       <c r="C206" s="31"/>
       <c r="D206" s="31"/>
@@ -19974,7 +20181,7 @@
       <c r="CA206" s="31"/>
       <c r="CB206" s="31"/>
     </row>
-    <row r="207" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:80">
       <c r="B207" s="31"/>
       <c r="C207" s="31"/>
       <c r="D207" s="31"/>
@@ -20055,7 +20262,7 @@
       <c r="CA207" s="31"/>
       <c r="CB207" s="31"/>
     </row>
-    <row r="208" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:80">
       <c r="B208" s="31"/>
       <c r="C208" s="31"/>
       <c r="D208" s="31"/>
@@ -20136,7 +20343,7 @@
       <c r="CA208" s="31"/>
       <c r="CB208" s="31"/>
     </row>
-    <row r="209" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:80">
       <c r="B209" s="31"/>
       <c r="C209" s="31"/>
       <c r="D209" s="31"/>
@@ -20217,7 +20424,7 @@
       <c r="CA209" s="31"/>
       <c r="CB209" s="31"/>
     </row>
-    <row r="210" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:80">
       <c r="B210" s="31"/>
       <c r="C210" s="31"/>
       <c r="D210" s="31"/>
@@ -20298,7 +20505,7 @@
       <c r="CA210" s="31"/>
       <c r="CB210" s="31"/>
     </row>
-    <row r="211" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:80">
       <c r="B211" s="31"/>
       <c r="C211" s="31"/>
       <c r="D211" s="31"/>
@@ -20379,7 +20586,7 @@
       <c r="CA211" s="31"/>
       <c r="CB211" s="31"/>
     </row>
-    <row r="212" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:80">
       <c r="B212" s="31"/>
       <c r="C212" s="31"/>
       <c r="D212" s="31"/>
@@ -20460,7 +20667,7 @@
       <c r="CA212" s="31"/>
       <c r="CB212" s="31"/>
     </row>
-    <row r="213" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:80">
       <c r="B213" s="31"/>
       <c r="C213" s="31"/>
       <c r="D213" s="31"/>
@@ -20541,7 +20748,7 @@
       <c r="CA213" s="31"/>
       <c r="CB213" s="31"/>
     </row>
-    <row r="214" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:80">
       <c r="B214" s="31"/>
       <c r="C214" s="31"/>
       <c r="D214" s="31"/>
@@ -20622,7 +20829,7 @@
       <c r="CA214" s="31"/>
       <c r="CB214" s="31"/>
     </row>
-    <row r="215" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:80">
       <c r="B215" s="31"/>
       <c r="C215" s="31"/>
       <c r="D215" s="31"/>
@@ -20703,7 +20910,7 @@
       <c r="CA215" s="31"/>
       <c r="CB215" s="31"/>
     </row>
-    <row r="216" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:80">
       <c r="B216" s="31"/>
       <c r="C216" s="31"/>
       <c r="D216" s="31"/>
@@ -20784,7 +20991,7 @@
       <c r="CA216" s="31"/>
       <c r="CB216" s="31"/>
     </row>
-    <row r="217" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:80">
       <c r="B217" s="31"/>
       <c r="C217" s="31"/>
       <c r="D217" s="31"/>
@@ -20865,7 +21072,7 @@
       <c r="CA217" s="31"/>
       <c r="CB217" s="31"/>
     </row>
-    <row r="218" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:80">
       <c r="B218" s="31"/>
       <c r="C218" s="31"/>
       <c r="D218" s="31"/>
@@ -20946,7 +21153,7 @@
       <c r="CA218" s="31"/>
       <c r="CB218" s="31"/>
     </row>
-    <row r="219" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:80">
       <c r="B219" s="31"/>
       <c r="C219" s="31"/>
       <c r="D219" s="31"/>
@@ -21027,7 +21234,7 @@
       <c r="CA219" s="31"/>
       <c r="CB219" s="31"/>
     </row>
-    <row r="220" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:80">
       <c r="B220" s="31"/>
       <c r="C220" s="31"/>
       <c r="D220" s="31"/>
@@ -21108,7 +21315,7 @@
       <c r="CA220" s="31"/>
       <c r="CB220" s="31"/>
     </row>
-    <row r="221" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:80">
       <c r="B221" s="31"/>
       <c r="C221" s="31"/>
       <c r="D221" s="31"/>
@@ -21189,7 +21396,7 @@
       <c r="CA221" s="31"/>
       <c r="CB221" s="31"/>
     </row>
-    <row r="222" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:80">
       <c r="B222" s="31"/>
       <c r="C222" s="31"/>
       <c r="D222" s="31"/>
@@ -21270,7 +21477,7 @@
       <c r="CA222" s="31"/>
       <c r="CB222" s="31"/>
     </row>
-    <row r="223" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:80">
       <c r="B223" s="31"/>
       <c r="C223" s="31"/>
       <c r="D223" s="31"/>
@@ -21351,7 +21558,7 @@
       <c r="CA223" s="31"/>
       <c r="CB223" s="31"/>
     </row>
-    <row r="224" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:80">
       <c r="B224" s="31"/>
       <c r="C224" s="31"/>
       <c r="D224" s="31"/>
@@ -21432,7 +21639,7 @@
       <c r="CA224" s="31"/>
       <c r="CB224" s="31"/>
     </row>
-    <row r="225" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:80">
       <c r="B225" s="31"/>
       <c r="C225" s="31"/>
       <c r="D225" s="31"/>
@@ -21513,7 +21720,7 @@
       <c r="CA225" s="31"/>
       <c r="CB225" s="31"/>
     </row>
-    <row r="226" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:80">
       <c r="B226" s="31"/>
       <c r="C226" s="31"/>
       <c r="D226" s="31"/>
@@ -21594,7 +21801,7 @@
       <c r="CA226" s="31"/>
       <c r="CB226" s="31"/>
     </row>
-    <row r="227" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:80">
       <c r="B227" s="31"/>
       <c r="C227" s="31"/>
       <c r="D227" s="31"/>
@@ -21675,7 +21882,7 @@
       <c r="CA227" s="31"/>
       <c r="CB227" s="31"/>
     </row>
-    <row r="228" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:80">
       <c r="B228" s="31"/>
       <c r="C228" s="31"/>
       <c r="D228" s="31"/>
@@ -21756,7 +21963,7 @@
       <c r="CA228" s="31"/>
       <c r="CB228" s="31"/>
     </row>
-    <row r="229" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:80">
       <c r="B229" s="31"/>
       <c r="C229" s="31"/>
       <c r="D229" s="31"/>
@@ -21837,7 +22044,7 @@
       <c r="CA229" s="31"/>
       <c r="CB229" s="31"/>
     </row>
-    <row r="230" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:80">
       <c r="B230" s="31"/>
       <c r="C230" s="31"/>
       <c r="D230" s="31"/>
@@ -21918,7 +22125,7 @@
       <c r="CA230" s="31"/>
       <c r="CB230" s="31"/>
     </row>
-    <row r="231" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:80">
       <c r="B231" s="31"/>
       <c r="C231" s="31"/>
       <c r="D231" s="31"/>
@@ -21999,7 +22206,7 @@
       <c r="CA231" s="31"/>
       <c r="CB231" s="31"/>
     </row>
-    <row r="232" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:80">
       <c r="B232" s="31"/>
       <c r="C232" s="31"/>
       <c r="D232" s="31"/>
@@ -22080,7 +22287,7 @@
       <c r="CA232" s="31"/>
       <c r="CB232" s="31"/>
     </row>
-    <row r="233" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:80">
       <c r="B233" s="31"/>
       <c r="C233" s="31"/>
       <c r="D233" s="31"/>
@@ -22161,7 +22368,7 @@
       <c r="CA233" s="31"/>
       <c r="CB233" s="31"/>
     </row>
-    <row r="234" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:80">
       <c r="B234" s="31"/>
       <c r="C234" s="31"/>
       <c r="D234" s="31"/>
@@ -22242,7 +22449,7 @@
       <c r="CA234" s="31"/>
       <c r="CB234" s="31"/>
     </row>
-    <row r="235" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:80">
       <c r="B235" s="31"/>
       <c r="C235" s="31"/>
       <c r="D235" s="31"/>
@@ -22323,7 +22530,7 @@
       <c r="CA235" s="31"/>
       <c r="CB235" s="31"/>
     </row>
-    <row r="236" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:80">
       <c r="B236" s="31"/>
       <c r="C236" s="31"/>
       <c r="D236" s="31"/>
@@ -22404,7 +22611,7 @@
       <c r="CA236" s="31"/>
       <c r="CB236" s="31"/>
     </row>
-    <row r="237" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:80">
       <c r="B237" s="31"/>
       <c r="C237" s="31"/>
       <c r="D237" s="31"/>
@@ -22485,7 +22692,7 @@
       <c r="CA237" s="31"/>
       <c r="CB237" s="31"/>
     </row>
-    <row r="238" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:80">
       <c r="B238" s="31"/>
       <c r="C238" s="31"/>
       <c r="D238" s="31"/>
@@ -22566,7 +22773,7 @@
       <c r="CA238" s="31"/>
       <c r="CB238" s="31"/>
     </row>
-    <row r="239" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:80">
       <c r="B239" s="31"/>
       <c r="C239" s="31"/>
       <c r="D239" s="31"/>
@@ -22647,7 +22854,7 @@
       <c r="CA239" s="31"/>
       <c r="CB239" s="31"/>
     </row>
-    <row r="240" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:80">
       <c r="B240" s="31"/>
       <c r="C240" s="31"/>
       <c r="D240" s="31"/>
@@ -22728,7 +22935,7 @@
       <c r="CA240" s="31"/>
       <c r="CB240" s="31"/>
     </row>
-    <row r="241" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:80">
       <c r="B241" s="31"/>
       <c r="C241" s="31"/>
       <c r="D241" s="31"/>
@@ -22809,7 +23016,7 @@
       <c r="CA241" s="31"/>
       <c r="CB241" s="31"/>
     </row>
-    <row r="242" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:80">
       <c r="B242" s="31"/>
       <c r="C242" s="31"/>
       <c r="D242" s="31"/>
@@ -22890,7 +23097,7 @@
       <c r="CA242" s="31"/>
       <c r="CB242" s="31"/>
     </row>
-    <row r="243" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:80">
       <c r="B243" s="31"/>
       <c r="C243" s="31"/>
       <c r="D243" s="31"/>
@@ -22971,7 +23178,7 @@
       <c r="CA243" s="31"/>
       <c r="CB243" s="31"/>
     </row>
-    <row r="244" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:80">
       <c r="B244" s="31"/>
       <c r="C244" s="31"/>
       <c r="D244" s="31"/>
@@ -23052,7 +23259,7 @@
       <c r="CA244" s="31"/>
       <c r="CB244" s="31"/>
     </row>
-    <row r="245" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:80">
       <c r="B245" s="31"/>
       <c r="C245" s="31"/>
       <c r="D245" s="31"/>
@@ -23133,7 +23340,7 @@
       <c r="CA245" s="31"/>
       <c r="CB245" s="31"/>
     </row>
-    <row r="246" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:80">
       <c r="B246" s="31"/>
       <c r="C246" s="31"/>
       <c r="D246" s="31"/>
@@ -23214,7 +23421,7 @@
       <c r="CA246" s="31"/>
       <c r="CB246" s="31"/>
     </row>
-    <row r="247" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:80">
       <c r="B247" s="31"/>
       <c r="C247" s="31"/>
       <c r="D247" s="31"/>
@@ -23295,7 +23502,7 @@
       <c r="CA247" s="31"/>
       <c r="CB247" s="31"/>
     </row>
-    <row r="248" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:80">
       <c r="B248" s="31"/>
       <c r="C248" s="31"/>
       <c r="D248" s="31"/>
@@ -23376,7 +23583,7 @@
       <c r="CA248" s="31"/>
       <c r="CB248" s="31"/>
     </row>
-    <row r="249" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:80">
       <c r="B249" s="31"/>
       <c r="C249" s="31"/>
       <c r="D249" s="31"/>
@@ -23457,7 +23664,7 @@
       <c r="CA249" s="31"/>
       <c r="CB249" s="31"/>
     </row>
-    <row r="250" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:80">
       <c r="B250" s="31"/>
       <c r="C250" s="31"/>
       <c r="D250" s="31"/>
@@ -23538,7 +23745,7 @@
       <c r="CA250" s="31"/>
       <c r="CB250" s="31"/>
     </row>
-    <row r="251" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:80">
       <c r="B251" s="31"/>
       <c r="C251" s="31"/>
       <c r="D251" s="31"/>
@@ -23619,7 +23826,7 @@
       <c r="CA251" s="31"/>
       <c r="CB251" s="31"/>
     </row>
-    <row r="252" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:80">
       <c r="B252" s="31"/>
       <c r="C252" s="31"/>
       <c r="D252" s="31"/>
@@ -23700,7 +23907,7 @@
       <c r="CA252" s="31"/>
       <c r="CB252" s="31"/>
     </row>
-    <row r="253" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:80">
       <c r="B253" s="31"/>
       <c r="C253" s="31"/>
       <c r="D253" s="31"/>
@@ -23781,7 +23988,7 @@
       <c r="CA253" s="31"/>
       <c r="CB253" s="31"/>
     </row>
-    <row r="254" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:80">
       <c r="B254" s="31"/>
       <c r="C254" s="31"/>
       <c r="D254" s="31"/>
@@ -23862,7 +24069,7 @@
       <c r="CA254" s="31"/>
       <c r="CB254" s="31"/>
     </row>
-    <row r="255" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:80">
       <c r="B255" s="31"/>
       <c r="C255" s="31"/>
       <c r="D255" s="31"/>
@@ -23943,7 +24150,7 @@
       <c r="CA255" s="31"/>
       <c r="CB255" s="31"/>
     </row>
-    <row r="256" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:80">
       <c r="B256" s="31"/>
       <c r="C256" s="31"/>
       <c r="D256" s="31"/>
@@ -24024,7 +24231,7 @@
       <c r="CA256" s="31"/>
       <c r="CB256" s="31"/>
     </row>
-    <row r="257" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:80">
       <c r="B257" s="31"/>
       <c r="C257" s="31"/>
       <c r="D257" s="31"/>
@@ -24105,7 +24312,7 @@
       <c r="CA257" s="31"/>
       <c r="CB257" s="31"/>
     </row>
-    <row r="258" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:80">
       <c r="B258" s="31"/>
       <c r="C258" s="31"/>
       <c r="D258" s="31"/>
@@ -24186,7 +24393,7 @@
       <c r="CA258" s="31"/>
       <c r="CB258" s="31"/>
     </row>
-    <row r="259" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:80">
       <c r="B259" s="31"/>
       <c r="C259" s="31"/>
       <c r="D259" s="31"/>
@@ -24267,7 +24474,7 @@
       <c r="CA259" s="31"/>
       <c r="CB259" s="31"/>
     </row>
-    <row r="260" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:80">
       <c r="B260" s="31"/>
       <c r="C260" s="31"/>
       <c r="D260" s="31"/>
@@ -24348,7 +24555,7 @@
       <c r="CA260" s="31"/>
       <c r="CB260" s="31"/>
     </row>
-    <row r="261" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:80">
       <c r="B261" s="31"/>
       <c r="C261" s="31"/>
       <c r="D261" s="31"/>
@@ -24429,7 +24636,7 @@
       <c r="CA261" s="31"/>
       <c r="CB261" s="31"/>
     </row>
-    <row r="262" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:80">
       <c r="B262" s="31"/>
       <c r="C262" s="31"/>
       <c r="D262" s="31"/>
@@ -24510,7 +24717,7 @@
       <c r="CA262" s="31"/>
       <c r="CB262" s="31"/>
     </row>
-    <row r="263" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:80">
       <c r="B263" s="31"/>
       <c r="C263" s="31"/>
       <c r="D263" s="31"/>
@@ -24591,7 +24798,7 @@
       <c r="CA263" s="31"/>
       <c r="CB263" s="31"/>
     </row>
-    <row r="264" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:80">
       <c r="B264" s="31"/>
       <c r="C264" s="31"/>
       <c r="D264" s="31"/>
@@ -24672,7 +24879,7 @@
       <c r="CA264" s="31"/>
       <c r="CB264" s="31"/>
     </row>
-    <row r="265" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:80">
       <c r="B265" s="31"/>
       <c r="C265" s="31"/>
       <c r="D265" s="31"/>
@@ -24753,7 +24960,7 @@
       <c r="CA265" s="31"/>
       <c r="CB265" s="31"/>
     </row>
-    <row r="266" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:80">
       <c r="B266" s="31"/>
       <c r="C266" s="31"/>
       <c r="D266" s="31"/>
@@ -24834,7 +25041,7 @@
       <c r="CA266" s="31"/>
       <c r="CB266" s="31"/>
     </row>
-    <row r="267" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:80">
       <c r="B267" s="31"/>
       <c r="C267" s="31"/>
       <c r="D267" s="31"/>
@@ -24915,7 +25122,7 @@
       <c r="CA267" s="31"/>
       <c r="CB267" s="31"/>
     </row>
-    <row r="268" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:80">
       <c r="B268" s="31"/>
       <c r="C268" s="31"/>
       <c r="D268" s="31"/>
@@ -24996,7 +25203,7 @@
       <c r="CA268" s="31"/>
       <c r="CB268" s="31"/>
     </row>
-    <row r="269" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:80">
       <c r="B269" s="31"/>
       <c r="C269" s="31"/>
       <c r="D269" s="31"/>
@@ -25077,7 +25284,7 @@
       <c r="CA269" s="31"/>
       <c r="CB269" s="31"/>
     </row>
-    <row r="270" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:80">
       <c r="B270" s="31"/>
       <c r="C270" s="31"/>
       <c r="D270" s="31"/>
@@ -25158,7 +25365,7 @@
       <c r="CA270" s="31"/>
       <c r="CB270" s="31"/>
     </row>
-    <row r="271" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:80">
       <c r="B271" s="31"/>
       <c r="C271" s="31"/>
       <c r="D271" s="31"/>
@@ -25239,7 +25446,7 @@
       <c r="CA271" s="31"/>
       <c r="CB271" s="31"/>
     </row>
-    <row r="272" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:80">
       <c r="B272" s="31"/>
       <c r="C272" s="31"/>
       <c r="D272" s="31"/>
@@ -25320,7 +25527,7 @@
       <c r="CA272" s="31"/>
       <c r="CB272" s="31"/>
     </row>
-    <row r="273" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:80">
       <c r="B273" s="31"/>
       <c r="C273" s="31"/>
       <c r="D273" s="31"/>
@@ -25401,7 +25608,7 @@
       <c r="CA273" s="31"/>
       <c r="CB273" s="31"/>
     </row>
-    <row r="274" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:80">
       <c r="B274" s="31"/>
       <c r="C274" s="31"/>
       <c r="D274" s="31"/>
@@ -25482,7 +25689,7 @@
       <c r="CA274" s="31"/>
       <c r="CB274" s="31"/>
     </row>
-    <row r="275" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:80">
       <c r="B275" s="31"/>
       <c r="C275" s="31"/>
       <c r="D275" s="31"/>
@@ -25563,7 +25770,7 @@
       <c r="CA275" s="31"/>
       <c r="CB275" s="31"/>
     </row>
-    <row r="276" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:80">
       <c r="B276" s="31"/>
       <c r="C276" s="31"/>
       <c r="D276" s="31"/>
@@ -25644,7 +25851,7 @@
       <c r="CA276" s="31"/>
       <c r="CB276" s="31"/>
     </row>
-    <row r="277" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:80">
       <c r="B277" s="31"/>
       <c r="C277" s="31"/>
       <c r="D277" s="31"/>
@@ -25725,7 +25932,7 @@
       <c r="CA277" s="31"/>
       <c r="CB277" s="31"/>
     </row>
-    <row r="278" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:80">
       <c r="B278" s="31"/>
       <c r="C278" s="31"/>
       <c r="D278" s="31"/>
@@ -25806,7 +26013,7 @@
       <c r="CA278" s="31"/>
       <c r="CB278" s="31"/>
     </row>
-    <row r="279" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:80">
       <c r="B279" s="31"/>
       <c r="C279" s="31"/>
       <c r="D279" s="31"/>
@@ -25887,7 +26094,7 @@
       <c r="CA279" s="31"/>
       <c r="CB279" s="31"/>
     </row>
-    <row r="280" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:80">
       <c r="B280" s="31"/>
       <c r="C280" s="31"/>
       <c r="D280" s="31"/>
@@ -25968,7 +26175,7 @@
       <c r="CA280" s="31"/>
       <c r="CB280" s="31"/>
     </row>
-    <row r="281" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:80">
       <c r="B281" s="31"/>
       <c r="C281" s="31"/>
       <c r="D281" s="31"/>
@@ -26049,7 +26256,7 @@
       <c r="CA281" s="31"/>
       <c r="CB281" s="31"/>
     </row>
-    <row r="282" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:80">
       <c r="B282" s="31"/>
       <c r="C282" s="31"/>
       <c r="D282" s="31"/>
@@ -26130,7 +26337,7 @@
       <c r="CA282" s="31"/>
       <c r="CB282" s="31"/>
     </row>
-    <row r="283" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:80">
       <c r="B283" s="31"/>
       <c r="C283" s="31"/>
       <c r="D283" s="31"/>
@@ -26211,7 +26418,7 @@
       <c r="CA283" s="31"/>
       <c r="CB283" s="31"/>
     </row>
-    <row r="284" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:80">
       <c r="B284" s="31"/>
       <c r="C284" s="31"/>
       <c r="D284" s="31"/>
@@ -26292,7 +26499,7 @@
       <c r="CA284" s="31"/>
       <c r="CB284" s="31"/>
     </row>
-    <row r="285" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:80">
       <c r="B285" s="31"/>
       <c r="C285" s="31"/>
       <c r="D285" s="31"/>
@@ -26373,7 +26580,7 @@
       <c r="CA285" s="31"/>
       <c r="CB285" s="31"/>
     </row>
-    <row r="286" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:80">
       <c r="B286" s="31"/>
       <c r="C286" s="31"/>
       <c r="D286" s="31"/>
@@ -26454,7 +26661,7 @@
       <c r="CA286" s="31"/>
       <c r="CB286" s="31"/>
     </row>
-    <row r="287" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:80">
       <c r="B287" s="31"/>
       <c r="C287" s="31"/>
       <c r="D287" s="31"/>
@@ -26535,7 +26742,7 @@
       <c r="CA287" s="31"/>
       <c r="CB287" s="31"/>
     </row>
-    <row r="288" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:80">
       <c r="B288" s="31"/>
       <c r="C288" s="31"/>
       <c r="D288" s="31"/>
@@ -26616,7 +26823,7 @@
       <c r="CA288" s="31"/>
       <c r="CB288" s="31"/>
     </row>
-    <row r="289" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:80">
       <c r="B289" s="31"/>
       <c r="C289" s="31"/>
       <c r="D289" s="31"/>
@@ -26697,7 +26904,7 @@
       <c r="CA289" s="31"/>
       <c r="CB289" s="31"/>
     </row>
-    <row r="290" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:80">
       <c r="B290" s="31"/>
       <c r="C290" s="31"/>
       <c r="D290" s="31"/>
@@ -26778,7 +26985,7 @@
       <c r="CA290" s="31"/>
       <c r="CB290" s="31"/>
     </row>
-    <row r="291" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:80">
       <c r="B291" s="31"/>
       <c r="C291" s="31"/>
       <c r="D291" s="31"/>
@@ -26859,7 +27066,7 @@
       <c r="CA291" s="31"/>
       <c r="CB291" s="31"/>
     </row>
-    <row r="292" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:80">
       <c r="B292" s="31"/>
       <c r="C292" s="31"/>
       <c r="D292" s="31"/>
@@ -26940,7 +27147,7 @@
       <c r="CA292" s="31"/>
       <c r="CB292" s="31"/>
     </row>
-    <row r="293" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:80">
       <c r="B293" s="31"/>
       <c r="C293" s="31"/>
       <c r="D293" s="31"/>
@@ -27021,7 +27228,7 @@
       <c r="CA293" s="31"/>
       <c r="CB293" s="31"/>
     </row>
-    <row r="294" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:80">
       <c r="B294" s="31"/>
       <c r="C294" s="31"/>
       <c r="D294" s="31"/>
@@ -27102,7 +27309,7 @@
       <c r="CA294" s="31"/>
       <c r="CB294" s="31"/>
     </row>
-    <row r="295" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:80">
       <c r="B295" s="31"/>
       <c r="C295" s="31"/>
       <c r="D295" s="31"/>
@@ -27183,7 +27390,7 @@
       <c r="CA295" s="31"/>
       <c r="CB295" s="31"/>
     </row>
-    <row r="296" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:80">
       <c r="B296" s="31"/>
       <c r="C296" s="31"/>
       <c r="D296" s="31"/>
@@ -27264,7 +27471,7 @@
       <c r="CA296" s="31"/>
       <c r="CB296" s="31"/>
     </row>
-    <row r="297" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:80">
       <c r="B297" s="31"/>
       <c r="C297" s="31"/>
       <c r="D297" s="31"/>
@@ -27345,7 +27552,7 @@
       <c r="CA297" s="31"/>
       <c r="CB297" s="31"/>
     </row>
-    <row r="298" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:80">
       <c r="B298" s="31"/>
       <c r="C298" s="31"/>
       <c r="D298" s="31"/>
@@ -27426,7 +27633,7 @@
       <c r="CA298" s="31"/>
       <c r="CB298" s="31"/>
     </row>
-    <row r="299" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:80">
       <c r="B299" s="31"/>
       <c r="C299" s="31"/>
       <c r="D299" s="31"/>
@@ -27507,7 +27714,7 @@
       <c r="CA299" s="31"/>
       <c r="CB299" s="31"/>
     </row>
-    <row r="300" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:80">
       <c r="B300" s="31"/>
       <c r="C300" s="31"/>
       <c r="D300" s="31"/>
@@ -27588,7 +27795,7 @@
       <c r="CA300" s="31"/>
       <c r="CB300" s="31"/>
     </row>
-    <row r="301" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:80">
       <c r="B301" s="31"/>
       <c r="C301" s="31"/>
       <c r="D301" s="31"/>
@@ -27669,7 +27876,7 @@
       <c r="CA301" s="31"/>
       <c r="CB301" s="31"/>
     </row>
-    <row r="302" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:80">
       <c r="B302" s="31"/>
       <c r="C302" s="31"/>
       <c r="D302" s="31"/>
@@ -27750,7 +27957,7 @@
       <c r="CA302" s="31"/>
       <c r="CB302" s="31"/>
     </row>
-    <row r="303" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:80">
       <c r="B303" s="31"/>
       <c r="C303" s="31"/>
       <c r="D303" s="31"/>
@@ -27831,7 +28038,7 @@
       <c r="CA303" s="31"/>
       <c r="CB303" s="31"/>
     </row>
-    <row r="304" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:80">
       <c r="B304" s="31"/>
       <c r="C304" s="31"/>
       <c r="D304" s="31"/>
@@ -27912,7 +28119,7 @@
       <c r="CA304" s="31"/>
       <c r="CB304" s="31"/>
     </row>
-    <row r="305" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:80">
       <c r="B305" s="31"/>
       <c r="C305" s="31"/>
       <c r="D305" s="31"/>
@@ -27993,7 +28200,7 @@
       <c r="CA305" s="31"/>
       <c r="CB305" s="31"/>
     </row>
-    <row r="306" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:80">
       <c r="B306" s="31"/>
       <c r="C306" s="31"/>
       <c r="D306" s="31"/>
@@ -28074,7 +28281,7 @@
       <c r="CA306" s="31"/>
       <c r="CB306" s="31"/>
     </row>
-    <row r="307" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:80">
       <c r="B307" s="31"/>
       <c r="C307" s="31"/>
       <c r="D307" s="31"/>
@@ -28155,7 +28362,7 @@
       <c r="CA307" s="31"/>
       <c r="CB307" s="31"/>
     </row>
-    <row r="308" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:80">
       <c r="B308" s="31"/>
       <c r="C308" s="31"/>
       <c r="D308" s="31"/>
@@ -28236,7 +28443,7 @@
       <c r="CA308" s="31"/>
       <c r="CB308" s="31"/>
     </row>
-    <row r="309" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:80">
       <c r="B309" s="31"/>
       <c r="C309" s="31"/>
       <c r="D309" s="31"/>
@@ -28317,7 +28524,7 @@
       <c r="CA309" s="31"/>
       <c r="CB309" s="31"/>
     </row>
-    <row r="310" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:80">
       <c r="B310" s="31"/>
       <c r="C310" s="31"/>
       <c r="D310" s="31"/>
@@ -28398,7 +28605,7 @@
       <c r="CA310" s="31"/>
       <c r="CB310" s="31"/>
     </row>
-    <row r="311" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:80">
       <c r="B311" s="31"/>
       <c r="C311" s="31"/>
       <c r="D311" s="31"/>
@@ -28479,7 +28686,7 @@
       <c r="CA311" s="31"/>
       <c r="CB311" s="31"/>
     </row>
-    <row r="312" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:80">
       <c r="B312" s="31"/>
       <c r="C312" s="31"/>
       <c r="D312" s="31"/>
@@ -28560,7 +28767,7 @@
       <c r="CA312" s="31"/>
       <c r="CB312" s="31"/>
     </row>
-    <row r="313" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:80">
       <c r="B313" s="31"/>
       <c r="C313" s="31"/>
       <c r="D313" s="31"/>
@@ -28641,7 +28848,7 @@
       <c r="CA313" s="31"/>
       <c r="CB313" s="31"/>
     </row>
-    <row r="314" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:80">
       <c r="B314" s="31"/>
       <c r="C314" s="31"/>
       <c r="D314" s="31"/>
@@ -28722,7 +28929,7 @@
       <c r="CA314" s="31"/>
       <c r="CB314" s="31"/>
     </row>
-    <row r="315" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:80">
       <c r="B315" s="31"/>
       <c r="C315" s="31"/>
       <c r="D315" s="31"/>
@@ -28803,7 +29010,7 @@
       <c r="CA315" s="31"/>
       <c r="CB315" s="31"/>
     </row>
-    <row r="316" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:80">
       <c r="B316" s="31"/>
       <c r="C316" s="31"/>
       <c r="D316" s="31"/>
@@ -28884,7 +29091,7 @@
       <c r="CA316" s="31"/>
       <c r="CB316" s="31"/>
     </row>
-    <row r="317" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:80">
       <c r="B317" s="31"/>
       <c r="C317" s="31"/>
       <c r="D317" s="31"/>
@@ -28965,7 +29172,7 @@
       <c r="CA317" s="31"/>
       <c r="CB317" s="31"/>
     </row>
-    <row r="318" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:80">
       <c r="B318" s="31"/>
       <c r="C318" s="31"/>
       <c r="D318" s="31"/>
@@ -29046,7 +29253,7 @@
       <c r="CA318" s="31"/>
       <c r="CB318" s="31"/>
     </row>
-    <row r="319" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:80">
       <c r="B319" s="31"/>
       <c r="C319" s="31"/>
       <c r="D319" s="31"/>
@@ -29127,7 +29334,7 @@
       <c r="CA319" s="31"/>
       <c r="CB319" s="31"/>
     </row>
-    <row r="320" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:80">
       <c r="B320" s="31"/>
       <c r="C320" s="31"/>
       <c r="D320" s="31"/>
@@ -29208,7 +29415,7 @@
       <c r="CA320" s="31"/>
       <c r="CB320" s="31"/>
     </row>
-    <row r="321" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:80">
       <c r="B321" s="31"/>
       <c r="C321" s="31"/>
       <c r="D321" s="31"/>
@@ -29289,7 +29496,7 @@
       <c r="CA321" s="31"/>
       <c r="CB321" s="31"/>
     </row>
-    <row r="322" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:80">
       <c r="B322" s="31"/>
       <c r="C322" s="31"/>
       <c r="D322" s="31"/>
@@ -29370,7 +29577,7 @@
       <c r="CA322" s="31"/>
       <c r="CB322" s="31"/>
     </row>
-    <row r="323" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:80">
       <c r="B323" s="31"/>
       <c r="C323" s="31"/>
       <c r="D323" s="31"/>
@@ -29451,7 +29658,7 @@
       <c r="CA323" s="31"/>
       <c r="CB323" s="31"/>
     </row>
-    <row r="324" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:80">
       <c r="B324" s="31"/>
       <c r="C324" s="31"/>
       <c r="D324" s="31"/>
@@ -29532,7 +29739,7 @@
       <c r="CA324" s="31"/>
       <c r="CB324" s="31"/>
     </row>
-    <row r="325" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:80">
       <c r="B325" s="31"/>
       <c r="C325" s="31"/>
       <c r="D325" s="31"/>
@@ -29613,7 +29820,7 @@
       <c r="CA325" s="31"/>
       <c r="CB325" s="31"/>
     </row>
-    <row r="326" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:80">
       <c r="B326" s="31"/>
       <c r="C326" s="31"/>
       <c r="D326" s="31"/>
@@ -29694,7 +29901,7 @@
       <c r="CA326" s="31"/>
       <c r="CB326" s="31"/>
     </row>
-    <row r="327" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:80">
       <c r="B327" s="31"/>
       <c r="C327" s="31"/>
       <c r="D327" s="31"/>
@@ -29775,7 +29982,7 @@
       <c r="CA327" s="31"/>
       <c r="CB327" s="31"/>
     </row>
-    <row r="328" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:80">
       <c r="B328" s="31"/>
       <c r="C328" s="31"/>
       <c r="D328" s="31"/>
@@ -29856,7 +30063,7 @@
       <c r="CA328" s="31"/>
       <c r="CB328" s="31"/>
     </row>
-    <row r="329" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:80">
       <c r="B329" s="31"/>
       <c r="C329" s="31"/>
       <c r="D329" s="31"/>
@@ -29937,7 +30144,7 @@
       <c r="CA329" s="31"/>
       <c r="CB329" s="31"/>
     </row>
-    <row r="330" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:80">
       <c r="B330" s="31"/>
       <c r="C330" s="31"/>
       <c r="D330" s="31"/>
@@ -30018,7 +30225,7 @@
       <c r="CA330" s="31"/>
       <c r="CB330" s="31"/>
     </row>
-    <row r="331" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:80">
       <c r="B331" s="31"/>
       <c r="C331" s="31"/>
       <c r="D331" s="31"/>
@@ -30099,7 +30306,7 @@
       <c r="CA331" s="31"/>
       <c r="CB331" s="31"/>
     </row>
-    <row r="332" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:80">
       <c r="B332" s="31"/>
       <c r="C332" s="31"/>
       <c r="D332" s="31"/>
@@ -30180,7 +30387,7 @@
       <c r="CA332" s="31"/>
       <c r="CB332" s="31"/>
     </row>
-    <row r="333" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:80">
       <c r="B333" s="31"/>
       <c r="C333" s="31"/>
       <c r="D333" s="31"/>
@@ -30261,7 +30468,7 @@
       <c r="CA333" s="31"/>
       <c r="CB333" s="31"/>
     </row>
-    <row r="334" spans="2:80" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:80">
       <c r="B334" s="31"/>
       <c r="C334" s="31"/>
       <c r="D334" s="31"/>

--- a/Watchlist .xlsx
+++ b/Watchlist .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA0E0DC-229D-4AAF-93F4-BA88D4939769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4E429F-41D0-4BD1-A55F-FAF361D2B4DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
+    <workbookView xWindow="225" yWindow="2340" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="100">
   <si>
     <t>Watchlist</t>
   </si>
@@ -369,6 +369,12 @@
   <si>
     <t>ASML</t>
   </si>
+  <si>
+    <t>Lululemon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sports </t>
+  </si>
 </sst>
 </file>
 
@@ -378,13 +384,19 @@
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -517,98 +529,102 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="17" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -690,22 +706,22 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="H3">
-            <v>46.15</v>
+            <v>47.45</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>100930.05</v>
+            <v>104105.3</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>3827</v>
+            <v>2518</v>
           </cell>
         </row>
         <row r="7">
           <cell r="H7">
-            <v>35070</v>
+            <v>35063</v>
           </cell>
         </row>
       </sheetData>
@@ -715,7 +731,7 @@
       <sheetData sheetId="4">
         <row r="4">
           <cell r="J4">
-            <v>42.245377497915634</v>
+            <v>55.220363038811023</v>
           </cell>
         </row>
       </sheetData>
@@ -743,22 +759,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>136.34</v>
+            <v>121.86</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>6774.6866083200002</v>
+            <v>5842.5868395000007</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>130.881</v>
+            <v>170.27600000000001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>1335.8209999999999</v>
+            <v>1307.6579999999999</v>
           </cell>
         </row>
       </sheetData>
@@ -768,7 +784,7 @@
       <sheetData sheetId="4">
         <row r="4">
           <cell r="J4">
-            <v>149.81272597413047</v>
+            <v>156.58897026472911</v>
           </cell>
         </row>
       </sheetData>
@@ -796,22 +812,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>55.35</v>
+            <v>58.7</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>48824.539037549999</v>
+            <v>52066.9</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>9342</v>
+            <v>11256</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>9409</v>
+            <v>13400</v>
           </cell>
         </row>
       </sheetData>
@@ -821,7 +837,7 @@
       <sheetData sheetId="4">
         <row r="4">
           <cell r="J4">
-            <v>93.627712741650726</v>
+            <v>90.720141570568231</v>
           </cell>
         </row>
       </sheetData>
@@ -993,22 +1009,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>245.3</v>
+            <v>250.5</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>30074.960383599999</v>
+            <v>30716.233848</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>4313</v>
+            <v>8480</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>12562</v>
+            <v>11804</v>
           </cell>
         </row>
       </sheetData>
@@ -1020,7 +1036,7 @@
       <sheetData sheetId="6">
         <row r="4">
           <cell r="J4">
-            <v>339.64481512044307</v>
+            <v>379.40823731776692</v>
           </cell>
         </row>
       </sheetData>
@@ -1216,22 +1232,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>81.2</v>
+            <v>87.92</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>5521.0864911999997</v>
+            <v>5978.0039939199996</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>203.84100000000001</v>
+            <v>180.76900000000001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>396.62300000000005</v>
+            <v>399.72299999999996</v>
           </cell>
         </row>
       </sheetData>
@@ -2049,19 +2065,19 @@
       </c>
       <c r="E10" s="9">
         <f>+[6]Main!$J$2</f>
-        <v>81.2</v>
+        <v>87.92</v>
       </c>
       <c r="F10" s="12">
         <f>+([6]Main!$J$4)*FX!C2</f>
-        <v>6459.6711947039994</v>
+        <v>6994.2646728863992</v>
       </c>
       <c r="G10" s="12">
         <f>+([6]Main!$J$6-[6]Main!$J$5)*FX!C2</f>
-        <v>225.55494000000004</v>
+        <v>256.17617999999993</v>
       </c>
       <c r="H10" s="12">
         <f t="shared" si="0"/>
-        <v>6685.2261347039994</v>
+        <v>7250.4408528863987</v>
       </c>
       <c r="I10" s="22" t="s">
         <v>18</v>
@@ -2077,7 +2093,7 @@
       </c>
       <c r="M10" s="18">
         <f t="shared" si="1"/>
-        <v>-4.8065650644783076E-2</v>
+        <v>3.071512309495894E-2</v>
       </c>
       <c r="O10" s="21" t="s">
         <v>47</v>
@@ -2276,7 +2292,7 @@
       <c r="I15" s="8"/>
       <c r="M15" s="19">
         <f>+AVERAGE(M5:M13)</f>
-        <v>-0.14903283946893209</v>
+        <v>-0.14027942016451631</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -2969,19 +2985,19 @@
       </c>
       <c r="E5" s="9">
         <f>+[10]Main!$H$3</f>
-        <v>46.15</v>
+        <v>47.45</v>
       </c>
       <c r="F5" s="12">
         <f>+[10]Main!$H$5*FX!C11</f>
-        <v>118088.15849999999</v>
+        <v>121803.201</v>
       </c>
       <c r="G5" s="12">
         <f>+([10]Main!$H$7-[10]Main!$H$6)*FX!C11</f>
-        <v>36554.31</v>
+        <v>38077.649999999994</v>
       </c>
       <c r="H5" s="12">
-        <f t="shared" ref="H5:H11" si="0">+F5+G5</f>
-        <v>154642.46849999999</v>
+        <f t="shared" ref="H5:H12" si="0">+F5+G5</f>
+        <v>159880.851</v>
       </c>
       <c r="I5" s="42" t="s">
         <v>95</v>
@@ -2997,19 +3013,19 @@
       </c>
       <c r="M5" s="38">
         <f>+FX!C11*Portfolio!E5</f>
-        <v>53.995499999999993</v>
+        <v>55.516500000000001</v>
       </c>
       <c r="N5" s="18">
         <f>+M5/L5-1</f>
-        <v>0.66062844647563734</v>
+        <v>0.70740671257354304</v>
       </c>
       <c r="O5" s="33">
         <f>+[10]DCF!$J$4</f>
-        <v>42.245377497915634</v>
+        <v>55.220363038811023</v>
       </c>
       <c r="P5" s="34">
         <f>+O5/E5-1</f>
-        <v>-8.4607204812228942E-2</v>
+        <v>0.16375896815197089</v>
       </c>
       <c r="Q5" s="35" t="s">
         <v>87</v>
@@ -3031,19 +3047,19 @@
       </c>
       <c r="E6" s="9">
         <f>+[11]Main!$H$2</f>
-        <v>136.34</v>
+        <v>121.86</v>
       </c>
       <c r="F6" s="12">
         <f>+[11]Main!$H$4*FX!C12</f>
-        <v>5961.7242153216002</v>
+        <v>5141.4764187600003</v>
       </c>
       <c r="G6" s="12">
         <f>+([11]Main!$H$6-[11]Main!$H$5)*FX!C12</f>
-        <v>1060.3471999999999</v>
+        <v>1000.8961599999999</v>
       </c>
       <c r="H6" s="12">
         <f t="shared" si="0"/>
-        <v>7022.0714153216004</v>
+        <v>6142.3725787600006</v>
       </c>
       <c r="I6" s="45" t="s">
         <v>40</v>
@@ -3059,19 +3075,19 @@
       </c>
       <c r="M6" s="39">
         <f>+FX!C12*Portfolio!E6</f>
-        <v>119.97920000000001</v>
+        <v>107.2368</v>
       </c>
       <c r="N6" s="18">
         <f t="shared" ref="N6:N11" si="1">+M6/L6-1</f>
-        <v>0.58954954954954952</v>
+        <v>0.42073131955484899</v>
       </c>
       <c r="O6" s="33">
         <f>+[11]DCF!$J$4</f>
-        <v>149.81272597413047</v>
+        <v>156.58897026472911</v>
       </c>
       <c r="P6" s="34">
         <f>+O6/E6-1</f>
-        <v>9.8817118777544843E-2</v>
+        <v>0.28499072923624746</v>
       </c>
       <c r="Q6" s="35" t="s">
         <v>88</v>
@@ -3093,19 +3109,19 @@
       </c>
       <c r="E7" s="9">
         <f>+[12]Main!$I$2</f>
-        <v>55.35</v>
+        <v>58.7</v>
       </c>
       <c r="F7" s="12">
         <f>+[12]Main!$I$4*FX!C12</f>
-        <v>42965.594353043998</v>
+        <v>45818.872000000003</v>
       </c>
       <c r="G7" s="12">
         <f>+([12]Main!$I$6-[12]Main!$I$5)*FX!C12</f>
-        <v>58.96</v>
+        <v>1886.72</v>
       </c>
       <c r="H7" s="12">
         <f t="shared" si="0"/>
-        <v>43024.554353043997</v>
+        <v>47705.592000000004</v>
       </c>
       <c r="I7" s="40" t="s">
         <v>40</v>
@@ -3121,19 +3137,19 @@
       </c>
       <c r="M7" s="38">
         <f>+E7*FX!C12</f>
-        <v>48.707999999999998</v>
+        <v>51.656000000000006</v>
       </c>
       <c r="N7" s="18">
         <f t="shared" si="1"/>
-        <v>-9.7122202140970337E-2</v>
+        <v>-4.2476481764678442E-2</v>
       </c>
       <c r="O7" s="33">
         <f>+[12]DCF!$J$4</f>
-        <v>93.627712741650726</v>
+        <v>90.720141570568231</v>
       </c>
       <c r="P7" s="34">
         <f>+O7/E7-1</f>
-        <v>0.69155759244174742</v>
+        <v>0.54548793135550633</v>
       </c>
       <c r="Q7" s="35" t="s">
         <v>89</v>
@@ -3340,19 +3356,19 @@
       </c>
       <c r="E11" s="9">
         <f>+[16]Main!$H$2</f>
-        <v>245.3</v>
+        <v>250.5</v>
       </c>
       <c r="F11" s="12">
         <f>+[16]Main!$H$4</f>
-        <v>30074.960383599999</v>
+        <v>30716.233848</v>
       </c>
       <c r="G11" s="12">
         <f>+[16]Main!$H$6-[16]Main!$H$5</f>
-        <v>8249</v>
+        <v>3324</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" si="0"/>
-        <v>38323.960383600002</v>
+        <v>34040.233848000003</v>
       </c>
       <c r="I11" s="43" t="s">
         <v>40</v>
@@ -3368,19 +3384,19 @@
       </c>
       <c r="M11" s="9">
         <f>+[16]Main!$H$2</f>
-        <v>245.3</v>
+        <v>250.5</v>
       </c>
       <c r="N11" s="18">
         <f t="shared" si="1"/>
-        <v>8.1140640839173273E-2</v>
+        <v>0.10405923575300813</v>
       </c>
       <c r="O11" s="9">
         <f>+[16]DCF!$J$4</f>
-        <v>339.64481512044307</v>
+        <v>379.40823731776692</v>
       </c>
       <c r="P11" s="34">
         <f>+O11/E11-1</f>
-        <v>0.3846099271114678</v>
+        <v>0.51460374178749269</v>
       </c>
       <c r="Q11" s="35" t="s">
         <v>88</v>
@@ -3392,18 +3408,41 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="24"/>
+      <c r="B12" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="9">
+        <f>+[3]Main!$I$2</f>
+        <v>110.86</v>
+      </c>
+      <c r="F12" s="12">
+        <f>+[3]Main!$I$4</f>
+        <v>12021.43191302</v>
+      </c>
+      <c r="G12" s="12">
+        <f>+[3]Main!$I$6-[3]Main!$I$5</f>
+        <v>-1514.729</v>
+      </c>
+      <c r="H12" s="12">
+        <f t="shared" si="0"/>
+        <v>10506.702913020001</v>
+      </c>
+      <c r="I12" s="47" t="s">
+        <v>40</v>
+      </c>
       <c r="J12" s="25"/>
       <c r="K12" s="13"/>
       <c r="N12" s="18"/>
       <c r="P12" s="26"/>
-      <c r="Q12" s="14"/>
+      <c r="Q12" s="46" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="13" spans="1:19" s="9" customFormat="1" ht="12.75">
       <c r="A13" s="11">
@@ -3446,9 +3485,10 @@
     <hyperlink ref="B7" r:id="rId5" xr:uid="{018DBD35-7DB3-46D1-A0AA-358A16A16D4A}"/>
     <hyperlink ref="B6" r:id="rId6" xr:uid="{DA19B0B3-37EC-4843-A572-3E9DFACEFCA4}"/>
     <hyperlink ref="B5" r:id="rId7" xr:uid="{91117BF7-0788-4B43-ADAF-699E0F21AEC2}"/>
+    <hyperlink ref="B12" r:id="rId8" xr:uid="{94C4823C-98CB-4C18-A807-39999389542E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId8"/>
+  <legacyDrawing r:id="rId9"/>
 </worksheet>
 </file>
 

--- a/Watchlist .xlsx
+++ b/Watchlist .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4E429F-41D0-4BD1-A55F-FAF361D2B4DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{493808E5-B68B-42A3-9C80-6FFB625C3D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="2340" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
   </bookViews>
@@ -33,7 +33,6 @@
     <externalReference r:id="rId16"/>
     <externalReference r:id="rId17"/>
     <externalReference r:id="rId18"/>
-    <externalReference r:id="rId19"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -74,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="98">
   <si>
     <t>Watchlist</t>
   </si>
@@ -268,9 +267,6 @@
     <t>BAT</t>
   </si>
   <si>
-    <t>Crocs</t>
-  </si>
-  <si>
     <t>PayPal</t>
   </si>
   <si>
@@ -311,9 +307,6 @@
   </si>
   <si>
     <t>US</t>
-  </si>
-  <si>
-    <t>CROX</t>
   </si>
   <si>
     <t>UK</t>
@@ -384,13 +377,19 @@
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -529,102 +528,102 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="17" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="17" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="16" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -647,48 +646,6 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Quarters"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>66.3</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>1333.3824387</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>315.70799999999997</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>449.74</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -740,6 +697,52 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="CoC"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>59.96</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>9165.7399503199995</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>752.101</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>1994.925</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -750,51 +753,197 @@
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="Coc"/>
-      <sheetName val="DCF"/>
-      <sheetName val="Data"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="H2">
-            <v>121.86</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>5842.5868395000007</v>
+          <cell r="J2">
+            <v>111</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="H5">
-            <v>170.27600000000001</v>
+          <cell r="J5">
+            <v>1937593.7999999998</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="H6">
-            <v>1307.6579999999999</v>
+          <cell r="J6">
+            <v>374857</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="J7">
+            <v>75503</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4">
-        <row r="4">
-          <cell r="J4">
-            <v>156.58897026472911</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="5"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>87.92</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>5978.0039939199996</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>180.76900000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>399.72299999999996</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>160.9</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>213851.54640000002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>13765.710999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>113.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>50394</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>2919</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>6746</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>50.7</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>27269.090670900005</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1068</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>30199</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -846,7 +995,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -863,22 +1012,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>70</v>
+            <v>71.599999999999994</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>5511.87</v>
+            <v>5629.192</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>13.5</v>
+            <v>61.6</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>4770.6000000000004</v>
+            <v>4941.8999999999996</v>
           </cell>
         </row>
       </sheetData>
@@ -887,7 +1036,7 @@
       <sheetData sheetId="3">
         <row r="4">
           <cell r="J4">
-            <v>110.50341825100335</v>
+            <v>108.99870635334247</v>
           </cell>
         </row>
       </sheetData>
@@ -896,7 +1045,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -936,7 +1085,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -987,7 +1136,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1047,47 +1196,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>4.42</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>7599.5650606200006</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>2993.377</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>3537.8890000000001</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1131,172 +1240,6 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="CoC"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>59.96</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>9165.7399503199995</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>752.101</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>1994.925</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>111</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>1937593.7999999998</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>374857</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="J7">
-            <v>75503</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>87.92</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>5978.0039939199996</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>180.76900000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>399.72299999999996</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>160.9</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>213851.54640000002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>13765.710999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -1306,32 +1249,34 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
+      <sheetName val="Quarters"/>
       <sheetName val="Model"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="H2">
-            <v>107.58</v>
+          <cell r="J2">
+            <v>66.3</v>
           </cell>
         </row>
         <row r="4">
-          <cell r="H4">
-            <v>48195.839999999997</v>
+          <cell r="J4">
+            <v>1333.3824387</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="H5">
-            <v>2919</v>
+          <cell r="J5">
+            <v>315.70799999999997</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="H6">
-            <v>6746</v>
+          <cell r="J6">
+            <v>449.74</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1352,22 +1297,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>50.7</v>
+            <v>5.29</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>27269.090670900005</v>
+            <v>8946.4358964800012</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>1068</v>
+            <v>2659.7579999999998</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>30199</v>
+            <v>3534.607</v>
           </cell>
         </row>
       </sheetData>
@@ -1796,15 +1741,15 @@
         <v>16</v>
       </c>
       <c r="E5" s="9">
-        <f>+[1]Main!$J$2</f>
+        <f>+[8]Main!$J$2</f>
         <v>66.3</v>
       </c>
       <c r="F5" s="12">
-        <f>+[1]Main!$J$4*FX!C2</f>
+        <f>+[8]Main!$J$4*FX!C2</f>
         <v>1560.0574532789999</v>
       </c>
       <c r="G5" s="12">
-        <f>(+[1]Main!$J$6-[1]Main!$J$5)*FX!C2</f>
+        <f>(+[8]Main!$J$6-[8]Main!$J$5)*FX!C2</f>
         <v>156.81744000000003</v>
       </c>
       <c r="H5" s="12">
@@ -1849,20 +1794,20 @@
         <v>24</v>
       </c>
       <c r="E6" s="9">
-        <f>+[2]Main!$I$2</f>
-        <v>4.42</v>
+        <f>+[9]Main!$I$2</f>
+        <v>5.29</v>
       </c>
       <c r="F6" s="12">
-        <f>+[2]Main!$I$4</f>
-        <v>7599.5650606200006</v>
+        <f>+[9]Main!$I$4</f>
+        <v>8946.4358964800012</v>
       </c>
       <c r="G6" s="12">
-        <f>+[2]Main!$I$6-[2]Main!$I$5</f>
-        <v>544.51200000000017</v>
+        <f>+[9]Main!$I$6-[9]Main!$I$5</f>
+        <v>874.84900000000016</v>
       </c>
       <c r="H6" s="12">
         <f t="shared" si="0"/>
-        <v>8144.0770606200003</v>
+        <v>9821.2848964800014</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>18</v>
@@ -1878,7 +1823,7 @@
       </c>
       <c r="M6" s="18">
         <f t="shared" ref="M6:M10" si="1">+E6/L6-1</f>
-        <v>-0.40591397849462374</v>
+        <v>-0.28897849462365599</v>
       </c>
       <c r="O6" s="10" t="s">
         <v>36</v>
@@ -1905,15 +1850,15 @@
         <v>29</v>
       </c>
       <c r="E7" s="9">
-        <f>+[3]Main!$I$2</f>
+        <f>+[7]Main!$I$2</f>
         <v>110.86</v>
       </c>
       <c r="F7" s="12">
-        <f>+[3]Main!$I$4</f>
+        <f>+[7]Main!$I$4</f>
         <v>12021.43191302</v>
       </c>
       <c r="G7" s="12">
-        <f>+[3]Main!$I$6-[3]Main!$I$5</f>
+        <f>+[7]Main!$I$6-[7]Main!$I$5</f>
         <v>-1514.729</v>
       </c>
       <c r="H7" s="12">
@@ -1958,15 +1903,15 @@
         <v>24</v>
       </c>
       <c r="E8" s="9">
-        <f>+[4]Main!$H$2</f>
+        <f>+[10]Main!$H$2</f>
         <v>59.96</v>
       </c>
       <c r="F8" s="12">
-        <f>+[4]Main!$H$4</f>
+        <f>+[10]Main!$H$4</f>
         <v>9165.7399503199995</v>
       </c>
       <c r="G8" s="12">
-        <f>+[4]Main!$H$6-[4]Main!$H$5</f>
+        <f>+[10]Main!$H$6-[10]Main!$H$5</f>
         <v>1242.8240000000001</v>
       </c>
       <c r="H8" s="12">
@@ -2011,15 +1956,15 @@
         <v>39</v>
       </c>
       <c r="E9" s="9">
-        <f>+[5]Main!$J$2</f>
+        <f>+[11]Main!$J$2</f>
         <v>111</v>
       </c>
       <c r="F9" s="12">
-        <f>+[5]Main!$J$5*FX!C3</f>
+        <f>+[11]Main!$J$5*FX!C3</f>
         <v>271263.13199999998</v>
       </c>
       <c r="G9" s="12">
-        <f>+([5]Main!$J$7-[5]Main!$J$6)*FX!C3</f>
+        <f>+([11]Main!$J$7-[11]Main!$J$6)*FX!C3</f>
         <v>-41909.560000000005</v>
       </c>
       <c r="H9" s="12">
@@ -2064,15 +2009,15 @@
         <v>45</v>
       </c>
       <c r="E10" s="9">
-        <f>+[6]Main!$J$2</f>
+        <f>+[12]Main!$J$2</f>
         <v>87.92</v>
       </c>
       <c r="F10" s="12">
-        <f>+([6]Main!$J$4)*FX!C2</f>
+        <f>+([12]Main!$J$4)*FX!C2</f>
         <v>6994.2646728863992</v>
       </c>
       <c r="G10" s="12">
-        <f>+([6]Main!$J$6-[6]Main!$J$5)*FX!C2</f>
+        <f>+([12]Main!$J$6-[12]Main!$J$5)*FX!C2</f>
         <v>256.17617999999993</v>
       </c>
       <c r="H10" s="12">
@@ -2120,15 +2065,15 @@
         <v>51</v>
       </c>
       <c r="E11" s="9">
-        <f>+[7]Main!$I$2</f>
+        <f>+[13]Main!$I$2</f>
         <v>160.9</v>
       </c>
       <c r="F11" s="12">
-        <f>+[7]Main!$I$4*FX!C3</f>
+        <f>+[13]Main!$I$4*FX!C3</f>
         <v>29939.216496000005</v>
       </c>
       <c r="G11" s="12">
-        <f>+([7]Main!$I$6-[7]Main!$I$5)*FX!C3</f>
+        <f>+([13]Main!$I$6-[13]Main!$I$5)*FX!C3</f>
         <v>-1927.1995400000001</v>
       </c>
       <c r="H11" s="12">
@@ -2176,20 +2121,20 @@
         <v>24</v>
       </c>
       <c r="E12" s="9">
-        <f>+[8]Main!$H$2</f>
-        <v>107.58</v>
+        <f>+[14]Main!$H$2</f>
+        <v>113.5</v>
       </c>
       <c r="F12" s="12">
-        <f>+[8]Main!$H$4</f>
-        <v>48195.839999999997</v>
+        <f>+[14]Main!$H$4</f>
+        <v>50394</v>
       </c>
       <c r="G12" s="12">
-        <f>+([8]Main!$H$6-[8]Main!$H$5)</f>
+        <f>+([14]Main!$H$6-[14]Main!$H$5)</f>
         <v>3827</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="0"/>
-        <v>52022.84</v>
+        <v>54221</v>
       </c>
       <c r="I12" s="24" t="s">
         <v>18</v>
@@ -2205,7 +2150,7 @@
       </c>
       <c r="M12" s="18">
         <f>+E12/L12-1</f>
-        <v>0.16719105999783013</v>
+        <v>0.23142020180101985</v>
       </c>
       <c r="O12" s="26" t="s">
         <v>55</v>
@@ -2229,15 +2174,15 @@
         <v>24</v>
       </c>
       <c r="E13" s="9">
-        <f>+[9]Main!$I$2</f>
+        <f>+[15]Main!$I$2</f>
         <v>50.7</v>
       </c>
       <c r="F13" s="12">
-        <f>+[9]Main!$I$4</f>
+        <f>+[15]Main!$I$4</f>
         <v>27269.090670900005</v>
       </c>
       <c r="G13" s="12">
-        <f>+[9]Main!$I$6-[9]Main!$I$5</f>
+        <f>+[15]Main!$I$6-[15]Main!$I$5</f>
         <v>29131</v>
       </c>
       <c r="H13" s="12">
@@ -2273,7 +2218,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="12"/>
@@ -2292,7 +2237,7 @@
       <c r="I15" s="8"/>
       <c r="M15" s="19">
         <f>+AVERAGE(M5:M13)</f>
-        <v>-0.14027942016451631</v>
+        <v>-0.12015001731183217</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -2890,7 +2835,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8328D887-56C2-45D2-86E7-3AD60D640181}">
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -2905,7 +2850,7 @@
     </row>
     <row r="2" spans="1:19" s="9" customFormat="1" ht="12.75">
       <c r="A2" s="31" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N2" s="19"/>
       <c r="P2" s="10"/>
@@ -2951,7 +2896,7 @@
         <v>62</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>43</v>
@@ -2960,7 +2905,7 @@
         <v>19</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q4" s="6" t="s">
         <v>32</v>
@@ -2978,29 +2923,29 @@
         <v>63</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E5" s="9">
-        <f>+[10]Main!$H$3</f>
+        <f>+[1]Main!$H$3</f>
         <v>47.45</v>
       </c>
       <c r="F5" s="12">
-        <f>+[10]Main!$H$5*FX!C11</f>
+        <f>+[1]Main!$H$5*FX!C11</f>
         <v>121803.201</v>
       </c>
       <c r="G5" s="12">
-        <f>+([10]Main!$H$7-[10]Main!$H$6)*FX!C11</f>
+        <f>+([1]Main!$H$7-[1]Main!$H$6)*FX!C11</f>
         <v>38077.649999999994</v>
       </c>
       <c r="H5" s="12">
-        <f t="shared" ref="H5:H12" si="0">+F5+G5</f>
+        <f t="shared" ref="H5:H11" si="0">+F5+G5</f>
         <v>159880.851</v>
       </c>
       <c r="I5" s="42" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J5" s="41">
         <v>46233</v>
@@ -3020,7 +2965,7 @@
         <v>0.70740671257354304</v>
       </c>
       <c r="O5" s="33">
-        <f>+[10]DCF!$J$4</f>
+        <f>+[1]DCF!$J$4</f>
         <v>55.220363038811023</v>
       </c>
       <c r="P5" s="34">
@@ -3028,7 +2973,7 @@
         <v>0.16375896815197089</v>
       </c>
       <c r="Q5" s="35" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:19" s="9" customFormat="1" ht="12.75">
@@ -3040,119 +2985,119 @@
         <v>64</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E6" s="9">
-        <f>+[11]Main!$H$2</f>
-        <v>121.86</v>
+        <f>+[2]Main!$I$2</f>
+        <v>58.7</v>
       </c>
       <c r="F6" s="12">
-        <f>+[11]Main!$H$4*FX!C12</f>
-        <v>5141.4764187600003</v>
+        <f>+[2]Main!$I$4*FX!C12</f>
+        <v>45818.872000000003</v>
       </c>
       <c r="G6" s="12">
-        <f>+([11]Main!$H$6-[11]Main!$H$5)*FX!C12</f>
-        <v>1000.8961599999999</v>
+        <f>+([2]Main!$I$6-[2]Main!$I$5)*FX!C12</f>
+        <v>1886.72</v>
       </c>
       <c r="H6" s="12">
         <f t="shared" si="0"/>
-        <v>6142.3725787600006</v>
-      </c>
-      <c r="I6" s="45" t="s">
+        <v>47705.592000000004</v>
+      </c>
+      <c r="I6" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="J6" s="44">
-        <v>46240</v>
+      <c r="J6" s="13">
+        <v>46231</v>
       </c>
       <c r="K6" s="13">
-        <v>45764</v>
-      </c>
-      <c r="L6" s="39">
-        <v>75.48</v>
-      </c>
-      <c r="M6" s="39">
-        <f>+FX!C12*Portfolio!E6</f>
-        <v>107.2368</v>
+        <v>45755</v>
+      </c>
+      <c r="L6" s="38">
+        <v>53.947499999999998</v>
+      </c>
+      <c r="M6" s="38">
+        <f>+E6*FX!C12</f>
+        <v>51.656000000000006</v>
       </c>
       <c r="N6" s="18">
-        <f t="shared" ref="N6:N11" si="1">+M6/L6-1</f>
-        <v>0.42073131955484899</v>
+        <f t="shared" ref="N6:N10" si="1">+M6/L6-1</f>
+        <v>-4.2476481764678442E-2</v>
       </c>
       <c r="O6" s="33">
-        <f>+[11]DCF!$J$4</f>
-        <v>156.58897026472911</v>
+        <f>+[2]DCF!$J$4</f>
+        <v>90.720141570568231</v>
       </c>
       <c r="P6" s="34">
         <f>+O6/E6-1</f>
-        <v>0.28499072923624746</v>
+        <v>0.54548793135550633</v>
       </c>
       <c r="Q6" s="35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:19" s="9" customFormat="1" ht="12.75">
       <c r="A7" s="11">
-        <f t="shared" ref="A7:A14" si="2">+A6+1</f>
+        <f t="shared" ref="A7:A13" si="2">+A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E7" s="9">
-        <f>+[12]Main!$I$2</f>
-        <v>58.7</v>
+        <f>+[3]Main!$J$2</f>
+        <v>71.599999999999994</v>
       </c>
       <c r="F7" s="12">
-        <f>+[12]Main!$I$4*FX!C12</f>
-        <v>45818.872000000003</v>
+        <f>+[3]Main!$J$4*FX!C13</f>
+        <v>731.79496000000006</v>
       </c>
       <c r="G7" s="12">
-        <f>+([12]Main!$I$6-[12]Main!$I$5)*FX!C12</f>
-        <v>1886.72</v>
+        <f>+([3]Main!$J$6-[3]Main!$J$5)*FX!C13</f>
+        <v>634.43899999999996</v>
       </c>
       <c r="H7" s="12">
         <f t="shared" si="0"/>
-        <v>47705.592000000004</v>
-      </c>
-      <c r="I7" s="40" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="13">
-        <v>46231</v>
+        <v>1366.23396</v>
+      </c>
+      <c r="I7" s="47" t="s">
+        <v>92</v>
+      </c>
+      <c r="J7" s="41">
+        <v>46338</v>
       </c>
       <c r="K7" s="13">
-        <v>45755</v>
+        <v>45972</v>
       </c>
       <c r="L7" s="38">
-        <v>53.947499999999998</v>
+        <v>11.895</v>
       </c>
       <c r="M7" s="38">
-        <f>+E7*FX!C12</f>
-        <v>51.656000000000006</v>
+        <f>+E7*FX!C13</f>
+        <v>9.3079999999999998</v>
       </c>
       <c r="N7" s="18">
         <f t="shared" si="1"/>
-        <v>-4.2476481764678442E-2</v>
+        <v>-0.2174863387978142</v>
       </c>
       <c r="O7" s="33">
-        <f>+[12]DCF!$J$4</f>
-        <v>90.720141570568231</v>
+        <f>+[3]DCF!$J$4</f>
+        <v>108.99870635334247</v>
       </c>
       <c r="P7" s="34">
         <f>+O7/E7-1</f>
-        <v>0.54548793135550633</v>
+        <v>0.52232830102433625</v>
       </c>
       <c r="Q7" s="35" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:19" s="9" customFormat="1" ht="12.75">
@@ -3164,57 +3109,55 @@
         <v>66</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="E8" s="9">
-        <f>+[13]Main!$J$2</f>
-        <v>70</v>
+        <f>+[4]Main!$I$3</f>
+        <v>38.979999999999997</v>
       </c>
       <c r="F8" s="12">
-        <f>+[13]Main!$J$4*FX!C13</f>
-        <v>716.54309999999998</v>
+        <f>+[4]Main!$I$5</f>
+        <v>11937.624999999998</v>
       </c>
       <c r="G8" s="12">
-        <f>+([13]Main!$J$6-[13]Main!$J$5)*FX!C13</f>
-        <v>618.42300000000012</v>
+        <f>+[4]Main!$I$7-[4]Main!$I$6</f>
+        <v>5880</v>
       </c>
       <c r="H8" s="12">
         <f t="shared" si="0"/>
-        <v>1334.9661000000001</v>
-      </c>
-      <c r="I8" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="J8" s="41">
-        <v>46260</v>
+        <v>17817.625</v>
+      </c>
+      <c r="I8" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="J8" s="40" t="s">
+        <v>94</v>
       </c>
       <c r="K8" s="13">
-        <v>45972</v>
-      </c>
-      <c r="L8" s="38">
-        <v>11.895</v>
-      </c>
-      <c r="M8" s="38">
-        <f>+E8*FX!C13</f>
-        <v>9.1</v>
+        <v>45084</v>
+      </c>
+      <c r="L8" s="39">
+        <v>56.9</v>
+      </c>
+      <c r="M8" s="9">
+        <f>+[4]Main!$I$3</f>
+        <v>38.979999999999997</v>
       </c>
       <c r="N8" s="18">
         <f t="shared" si="1"/>
-        <v>-0.23497267759562845</v>
-      </c>
-      <c r="O8" s="33">
-        <f>+[13]DCF!$J$4</f>
-        <v>110.50341825100335</v>
-      </c>
-      <c r="P8" s="34">
-        <f>+O8/E8-1</f>
-        <v>0.57862026072861927</v>
+        <v>-0.3149384885764499</v>
+      </c>
+      <c r="O8" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="P8" s="36" t="s">
+        <v>88</v>
       </c>
       <c r="Q8" s="35" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:19" s="9" customFormat="1" ht="12.75">
@@ -3226,56 +3169,59 @@
         <v>67</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D9" s="31" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="9">
-        <f>+[14]Main!$I$3</f>
-        <v>38.979999999999997</v>
+        <f>+[5]Main!$H$2</f>
+        <v>101.5</v>
       </c>
       <c r="F9" s="12">
-        <f>+[14]Main!$I$5</f>
-        <v>11937.624999999998</v>
+        <f>+[5]Main!$H$4</f>
+        <v>691.47869700000001</v>
       </c>
       <c r="G9" s="12">
-        <f>+[14]Main!$I$7-[14]Main!$I$6</f>
-        <v>5880</v>
+        <f>+[5]Main!$H$6</f>
+        <v>15.463999999999999</v>
       </c>
       <c r="H9" s="12">
         <f t="shared" si="0"/>
-        <v>17817.625</v>
+        <v>706.94269699999995</v>
       </c>
       <c r="I9" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="J9" s="40" t="s">
-        <v>96</v>
+        <v>92</v>
+      </c>
+      <c r="J9" s="41">
+        <v>46186</v>
       </c>
       <c r="K9" s="13">
-        <v>45084</v>
+        <v>45698</v>
       </c>
       <c r="L9" s="39">
-        <v>56.9</v>
+        <v>74.495000000000005</v>
       </c>
       <c r="M9" s="9">
-        <f>+[14]Main!$I$3</f>
-        <v>38.979999999999997</v>
+        <f>+[5]Main!$H$2</f>
+        <v>101.5</v>
       </c>
       <c r="N9" s="18">
         <f t="shared" si="1"/>
-        <v>-0.3149384885764499</v>
-      </c>
-      <c r="O9" s="36" t="s">
-        <v>90</v>
-      </c>
-      <c r="P9" s="36" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q9" s="35" t="s">
+        <v>0.36250755084233832</v>
+      </c>
+      <c r="O9" s="33">
+        <f>+[5]DCF!$J$3</f>
+        <v>97.40723155701005</v>
+      </c>
+      <c r="P9" s="34">
+        <f>+O9/E9-1</f>
+        <v>-4.0322841802856613E-2</v>
+      </c>
+      <c r="Q9" s="37" t="s">
         <v>91</v>
       </c>
+      <c r="R9" s="20"/>
     </row>
     <row r="10" spans="1:19" s="9" customFormat="1" ht="12.75">
       <c r="A10" s="11">
@@ -3286,57 +3232,57 @@
         <v>68</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="E10" s="9">
-        <f>+[15]Main!$H$2</f>
-        <v>101.5</v>
+        <f>+[6]Main!$H$2</f>
+        <v>250.5</v>
       </c>
       <c r="F10" s="12">
-        <f>+[15]Main!$H$4</f>
-        <v>691.47869700000001</v>
+        <f>+[6]Main!$H$4</f>
+        <v>30716.233848</v>
       </c>
       <c r="G10" s="12">
-        <f>+[15]Main!$H$6</f>
-        <v>15.463999999999999</v>
+        <f>+[6]Main!$H$6-[6]Main!$H$5</f>
+        <v>3324</v>
       </c>
       <c r="H10" s="12">
         <f t="shared" si="0"/>
-        <v>706.94269699999995</v>
-      </c>
-      <c r="I10" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="J10" s="41">
-        <v>46186</v>
+        <v>34040.233848000003</v>
+      </c>
+      <c r="I10" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="J10" s="44">
+        <v>46231</v>
       </c>
       <c r="K10" s="13">
-        <v>45698</v>
+        <v>45580</v>
       </c>
       <c r="L10" s="39">
-        <v>74.495000000000005</v>
+        <v>226.89</v>
       </c>
       <c r="M10" s="9">
-        <f>+[15]Main!$H$2</f>
-        <v>101.5</v>
+        <f>+[6]Main!$H$2</f>
+        <v>250.5</v>
       </c>
       <c r="N10" s="18">
         <f t="shared" si="1"/>
-        <v>0.36250755084233832</v>
-      </c>
-      <c r="O10" s="33">
-        <f>+[15]DCF!$J$3</f>
-        <v>97.40723155701005</v>
+        <v>0.10405923575300813</v>
+      </c>
+      <c r="O10" s="9">
+        <f>+[6]DCF!$J$4</f>
+        <v>379.40823731776692</v>
       </c>
       <c r="P10" s="34">
         <f>+O10/E10-1</f>
-        <v>-4.0322841802856613E-2</v>
-      </c>
-      <c r="Q10" s="37" t="s">
-        <v>93</v>
+        <v>0.51460374178749269</v>
+      </c>
+      <c r="Q10" s="35" t="s">
+        <v>86</v>
       </c>
       <c r="R10" s="20"/>
     </row>
@@ -3346,103 +3292,60 @@
         <v>7</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>72</v>
+        <v>96</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="45" t="s">
+        <v>77</v>
       </c>
       <c r="E11" s="9">
-        <f>+[16]Main!$H$2</f>
-        <v>250.5</v>
+        <f>+[7]Main!$I$2</f>
+        <v>110.86</v>
       </c>
       <c r="F11" s="12">
-        <f>+[16]Main!$H$4</f>
-        <v>30716.233848</v>
+        <f>+[7]Main!$I$4</f>
+        <v>12021.43191302</v>
       </c>
       <c r="G11" s="12">
-        <f>+[16]Main!$H$6-[16]Main!$H$5</f>
-        <v>3324</v>
+        <f>+[7]Main!$I$6-[7]Main!$I$5</f>
+        <v>-1514.729</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" si="0"/>
-        <v>34040.233848000003</v>
-      </c>
-      <c r="I11" s="43" t="s">
+        <v>10506.702913020001</v>
+      </c>
+      <c r="I11" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="J11" s="44">
-        <v>46231</v>
-      </c>
-      <c r="K11" s="13">
-        <v>45580</v>
-      </c>
-      <c r="L11" s="39">
-        <v>226.89</v>
-      </c>
-      <c r="M11" s="9">
-        <f>+[16]Main!$H$2</f>
-        <v>250.5</v>
-      </c>
-      <c r="N11" s="18">
-        <f t="shared" si="1"/>
-        <v>0.10405923575300813</v>
-      </c>
-      <c r="O11" s="9">
-        <f>+[16]DCF!$J$4</f>
-        <v>379.40823731776692</v>
-      </c>
-      <c r="P11" s="34">
-        <f>+O11/E11-1</f>
-        <v>0.51460374178749269</v>
-      </c>
-      <c r="Q11" s="35" t="s">
-        <v>88</v>
-      </c>
-      <c r="R11" s="20"/>
+      <c r="J11" s="25">
+        <v>46268</v>
+      </c>
+      <c r="K11" s="13"/>
+      <c r="N11" s="18"/>
+      <c r="P11" s="26"/>
+      <c r="Q11" s="45" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="12" spans="1:19" s="9" customFormat="1" ht="12.75">
       <c r="A12" s="11">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C12" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="46" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="9">
-        <f>+[3]Main!$I$2</f>
-        <v>110.86</v>
-      </c>
-      <c r="F12" s="12">
-        <f>+[3]Main!$I$4</f>
-        <v>12021.43191302</v>
-      </c>
-      <c r="G12" s="12">
-        <f>+[3]Main!$I$6-[3]Main!$I$5</f>
-        <v>-1514.729</v>
-      </c>
-      <c r="H12" s="12">
-        <f t="shared" si="0"/>
-        <v>10506.702913020001</v>
-      </c>
-      <c r="I12" s="47" t="s">
-        <v>40</v>
-      </c>
-      <c r="J12" s="25"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="29"/>
       <c r="K12" s="13"/>
       <c r="N12" s="18"/>
-      <c r="P12" s="26"/>
-      <c r="Q12" s="46" t="s">
-        <v>99</v>
-      </c>
+      <c r="P12" s="30"/>
+      <c r="Q12" s="14"/>
+      <c r="R12" s="28"/>
     </row>
     <row r="13" spans="1:19" s="9" customFormat="1" ht="12.75">
       <c r="A13" s="11">
@@ -3450,45 +3353,26 @@
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
       <c r="F13" s="12"/>
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
-      <c r="I13" s="29"/>
-      <c r="K13" s="13"/>
-      <c r="N13" s="18"/>
-      <c r="P13" s="30"/>
+      <c r="I13" s="8"/>
+      <c r="P13" s="10"/>
       <c r="Q13" s="14"/>
-      <c r="R13" s="28"/>
-    </row>
-    <row r="14" spans="1:19" s="9" customFormat="1" ht="12.75">
-      <c r="A14" s="11">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="8"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="14"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{1794CFC6-2AEA-4E11-A9BA-3889D0D75F94}"/>
-    <hyperlink ref="B11" r:id="rId1" xr:uid="{A820B1DA-C5FE-45E5-B57D-CD4E2C400A5A}"/>
-    <hyperlink ref="B10" r:id="rId2" xr:uid="{547B0603-1275-4D29-869A-D4EBA76FFD25}"/>
-    <hyperlink ref="B9" r:id="rId3" xr:uid="{321210F2-65AA-4E53-885E-71ECFD1CB23B}"/>
-    <hyperlink ref="B8" r:id="rId4" xr:uid="{1BC137DB-A3DF-4798-841A-BD61751FCC08}"/>
-    <hyperlink ref="B7" r:id="rId5" xr:uid="{018DBD35-7DB3-46D1-A0AA-358A16A16D4A}"/>
-    <hyperlink ref="B6" r:id="rId6" xr:uid="{DA19B0B3-37EC-4843-A572-3E9DFACEFCA4}"/>
-    <hyperlink ref="B5" r:id="rId7" xr:uid="{91117BF7-0788-4B43-ADAF-699E0F21AEC2}"/>
-    <hyperlink ref="B12" r:id="rId8" xr:uid="{94C4823C-98CB-4C18-A807-39999389542E}"/>
+    <hyperlink ref="B10" r:id="rId1" xr:uid="{A820B1DA-C5FE-45E5-B57D-CD4E2C400A5A}"/>
+    <hyperlink ref="B9" r:id="rId2" xr:uid="{547B0603-1275-4D29-869A-D4EBA76FFD25}"/>
+    <hyperlink ref="B8" r:id="rId3" xr:uid="{321210F2-65AA-4E53-885E-71ECFD1CB23B}"/>
+    <hyperlink ref="B7" r:id="rId4" xr:uid="{1BC137DB-A3DF-4798-841A-BD61751FCC08}"/>
+    <hyperlink ref="B6" r:id="rId5" xr:uid="{018DBD35-7DB3-46D1-A0AA-358A16A16D4A}"/>
+    <hyperlink ref="B5" r:id="rId6" xr:uid="{91117BF7-0788-4B43-ADAF-699E0F21AEC2}"/>
+    <hyperlink ref="B11" r:id="rId7" xr:uid="{94C4823C-98CB-4C18-A807-39999389542E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId9"/>
+  <legacyDrawing r:id="rId8"/>
 </worksheet>
 </file>
 
@@ -4252,7 +4136,7 @@
     </row>
     <row r="10" spans="1:80">
       <c r="B10" s="32" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C10" s="31"/>
       <c r="D10" s="31"/>
@@ -4335,7 +4219,7 @@
     </row>
     <row r="11" spans="1:80">
       <c r="B11" s="31" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C11" s="31">
         <v>1.17</v>
@@ -4420,7 +4304,7 @@
     </row>
     <row r="12" spans="1:80">
       <c r="B12" s="31" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C12" s="31">
         <v>0.88</v>
@@ -4505,7 +4389,7 @@
     </row>
     <row r="13" spans="1:80">
       <c r="B13" s="31" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C13" s="31">
         <v>0.13</v>
